--- a/report_info.xlsx
+++ b/report_info.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ЭтаКнига" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\05.PYTHON\Projects\san_report_automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4393F57E-B5B7-4134-AA45-1B7F6DA72C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26AB7955-B783-42D4-B36A-3CEBD9EFEB3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,6 +35,9 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -43,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2757" uniqueCount="1025">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2877" uniqueCount="1086">
   <si>
     <t>Contents</t>
   </si>
@@ -2322,9 +2325,6 @@
     <t>device_rack_path</t>
   </si>
   <si>
-    <t>SAN_Drawings_template_RT.vsdm</t>
-  </si>
-  <si>
     <t>D:\Documents\01.CUSTOMERS\MTS\SAN Assessment\JAN2022\mts_msc</t>
   </si>
   <si>
@@ -3118,6 +3118,192 @@
   </si>
   <si>
     <t>D:\Documents\06.CONFIGS\DataLine\Metrocluster\JAN2025\ssave</t>
+  </si>
+  <si>
+    <t>VC8</t>
+  </si>
+  <si>
+    <t>D:\Documents\01.CUSTOMERS\DataLine\SAN OST\VC8\JAN2025</t>
+  </si>
+  <si>
+    <t>D:\Documents\06.CONFIGS\DataLine\OST\VC8\JAN2025\ssave</t>
+  </si>
+  <si>
+    <t>D:\Documents\06.CONFIGS\DataLine\OST\VC8\JAN2025\huawei</t>
+  </si>
+  <si>
+    <t>Cloud152 Nord</t>
+  </si>
+  <si>
+    <t>D:\Documents\01.CUSTOMERS\DataLine\SAN NORD\Cloud152\JAN2025</t>
+  </si>
+  <si>
+    <t>D:\Documents\06.CONFIGS\DataLine\NORD\Cloud152\JAN2025\huawei</t>
+  </si>
+  <si>
+    <t>D:\Documents\06.CONFIGS\DataLine\NORD\Cloud152\JAN2025\ssave</t>
+  </si>
+  <si>
+    <t>VC01</t>
+  </si>
+  <si>
+    <t>D:\Documents\06.CONFIGS\DataLine\OST\VC01\MAR2025\ssave</t>
+  </si>
+  <si>
+    <t>D:\Documents\06.CONFIGS\DataLine\OST\VC01\MAR2025\huawei</t>
+  </si>
+  <si>
+    <t>D:\Documents\01.CUSTOMERS\DataLine\SAN OST\VC01\MAR2025</t>
+  </si>
+  <si>
+    <t>D:\Documents\01.CUSTOMERS\Coca-Cola\MAR2025</t>
+  </si>
+  <si>
+    <t>D:\Documents\06.CONFIGS\Coca-Cola\MAR2025\ssave</t>
+  </si>
+  <si>
+    <t>D:\Documents\06.CONFIGS\Coca-Cola\MAR2025\huawei</t>
+  </si>
+  <si>
+    <t>VC02</t>
+  </si>
+  <si>
+    <t>D:\Documents\01.CUSTOMERS\DataLine\SAN NORD\VC02\MAR2025</t>
+  </si>
+  <si>
+    <t>D:\Documents\06.CONFIGS\DataLine\NORD\VC02\MAR2025\ssave</t>
+  </si>
+  <si>
+    <t>D:\Documents\06.CONFIGS\DataLine\NORD\VC02\MAR2025\huawei</t>
+  </si>
+  <si>
+    <t>D:\Documents\06.CONFIGS\Locotech\MAR2025\nsshow</t>
+  </si>
+  <si>
+    <t>D:\Documents\06.CONFIGS\Locotech\MAR2025\ssave</t>
+  </si>
+  <si>
+    <t>D:\Documents\01.CUSTOMERS\Locotech\SAN\MAR2025</t>
+  </si>
+  <si>
+    <t>D:\Documents\06.CONFIGS\Locotech\MAR2025\huawei</t>
+  </si>
+  <si>
+    <t>D:\Documents\01.CUSTOMERS\Ruexce\SAN\APR2025</t>
+  </si>
+  <si>
+    <t>D:\Documents\06.CONFIGS\Ruexce\APR2025\ssave</t>
+  </si>
+  <si>
+    <t>D:\Documents\06.CONFIGS\Ruexce\APR2025\huawei</t>
+  </si>
+  <si>
+    <t>D:\Documents\01.CUSTOMERS\DataLine\SAN NORD\VC02\APR2025</t>
+  </si>
+  <si>
+    <t>D:\Documents\06.CONFIGS\DataLine\NORD\VC02\APR2025\ssave</t>
+  </si>
+  <si>
+    <t>D:\Documents\06.CONFIGS\DataLine\NORD\VC02\APR2025\huawei</t>
+  </si>
+  <si>
+    <t>D:\Documents\01.CUSTOMERS\DataLine\SAN MetroCluster\APR2025</t>
+  </si>
+  <si>
+    <t>D:\Documents\06.CONFIGS\DataLine\Metrocluster\APR2025\huawei</t>
+  </si>
+  <si>
+    <t>D:\Documents\06.CONFIGS\DataLine\Metrocluster\APR2025\ssave</t>
+  </si>
+  <si>
+    <t>D:\Documents\01.CUSTOMERS\DataLine\SAN STG\NORD\MAY2025</t>
+  </si>
+  <si>
+    <t>D:\Documents\06.CONFIGS\DataLine\STG\NORD\MAY2025\ssave</t>
+  </si>
+  <si>
+    <t>STG Nord</t>
+  </si>
+  <si>
+    <t>F:\Documents\01.CUSTOMERS\DataLine\SAN NSK\JUN2025</t>
+  </si>
+  <si>
+    <t>Nsk</t>
+  </si>
+  <si>
+    <t>F:\Documents\06.CONFIGS\DataLine\NSK\JUN2025\ssave</t>
+  </si>
+  <si>
+    <t>F:\Documents\06.CONFIGS\DataLine\NSK\JUN2025\huawei</t>
+  </si>
+  <si>
+    <t>F:\Documents\06.CONFIGS\DataLine\NSK\JUN2025\nsshow</t>
+  </si>
+  <si>
+    <t>SPb</t>
+  </si>
+  <si>
+    <t>F:\Documents\01.CUSTOMERS\DataLine\SAN SPB\JUN2025</t>
+  </si>
+  <si>
+    <t>F:\Documents\06.CONFIGS\DataLine\SPB\JUN2025\ssave</t>
+  </si>
+  <si>
+    <t>F:\Documents\06.CONFIGS\DataLine\SPB\JUN2025\huawei</t>
+  </si>
+  <si>
+    <t>Internal Nord</t>
+  </si>
+  <si>
+    <t>F:\Documents\06.CONFIGS\DataLine\Internal\JUL2025\ssave</t>
+  </si>
+  <si>
+    <t>F:\Documents\06.CONFIGS\DataLine\Internal\JUL2025\blade</t>
+  </si>
+  <si>
+    <t>F:\Documents\01.CUSTOMERS\DataLine\SAN Internal\JUL2025</t>
+  </si>
+  <si>
+    <t>SAN_Drawings_template_Turbo.vsdm</t>
+  </si>
+  <si>
+    <t>F:\Documents\01.CUSTOMERS\DataLine\SAN OST\VC4\MAR2026</t>
+  </si>
+  <si>
+    <t>F:\Documents\06.CONFIGS\DataLine\OST\VC4\MAR2026\ssave</t>
+  </si>
+  <si>
+    <t>F:\Documents\06.CONFIGS\DataLine\OST\VC4\MAR2026\huawei</t>
+  </si>
+  <si>
+    <t>F:\Documents\01.CUSTOMERS\DataLine\SAN OST\VC8\MAR2026</t>
+  </si>
+  <si>
+    <t>F:\Documents\06.CONFIGS\DataLine\OST\VC8\MAR2026\ssave</t>
+  </si>
+  <si>
+    <t>F:\Documents\06.CONFIGS\DataLine\OST\VC8\MAR2026\huawei</t>
+  </si>
+  <si>
+    <t>F:\Documents\01.CUSTOMERS\Delimobil\SAN\MAR2026</t>
+  </si>
+  <si>
+    <t>F:\Documents\06.CONFIGS\Delimobil\MAR2026\ssave</t>
+  </si>
+  <si>
+    <t>F:\Documents\06.CONFIGS\Delimobil\MAR2026\huawei</t>
+  </si>
+  <si>
+    <t>Novosibirsk</t>
+  </si>
+  <si>
+    <t>F:\Documents\01.CUSTOMERS\DataLine\SAN NSK\MAR2026</t>
+  </si>
+  <si>
+    <t>F:\Documents\06.CONFIGS\DataLine\NSK\MAR2026\ssave</t>
+  </si>
+  <si>
+    <t>F:\Documents\06.CONFIGS\DataLine\NSK\MAR2026\huawei</t>
   </si>
 </sst>
 </file>
@@ -3830,91 +4016,94 @@
     <hyperlink ref="A6" location="software!A1" display="software" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Лист2"/>
-  <dimension ref="A1:ED19"/>
+  <dimension ref="A1:EU19"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.7109375" customWidth="1"/>
-    <col min="2" max="2" width="66.7109375" style="40" customWidth="1"/>
-    <col min="3" max="9" width="116.28515625" customWidth="1"/>
-    <col min="10" max="11" width="70" customWidth="1"/>
-    <col min="12" max="20" width="116.28515625" customWidth="1"/>
-    <col min="21" max="21" width="90" customWidth="1"/>
-    <col min="22" max="23" width="116.28515625" customWidth="1"/>
-    <col min="24" max="24" width="70" customWidth="1"/>
-    <col min="25" max="25" width="105.28515625" customWidth="1"/>
-    <col min="26" max="27" width="70" customWidth="1"/>
-    <col min="28" max="29" width="116.28515625" customWidth="1"/>
-    <col min="30" max="32" width="70" customWidth="1"/>
-    <col min="33" max="33" width="105.28515625" customWidth="1"/>
-    <col min="34" max="34" width="70" customWidth="1"/>
-    <col min="35" max="45" width="116.28515625" customWidth="1"/>
-    <col min="46" max="48" width="70" customWidth="1"/>
-    <col min="49" max="51" width="96.7109375" customWidth="1"/>
-    <col min="52" max="52" width="70" customWidth="1"/>
-    <col min="53" max="58" width="96.7109375" customWidth="1"/>
-    <col min="59" max="70" width="70" customWidth="1"/>
-    <col min="71" max="73" width="96.7109375" customWidth="1"/>
-    <col min="74" max="74" width="70" customWidth="1"/>
-    <col min="75" max="75" width="116.28515625" customWidth="1"/>
-    <col min="76" max="80" width="70" customWidth="1"/>
-    <col min="81" max="83" width="116.28515625" customWidth="1"/>
-    <col min="84" max="84" width="120.85546875" customWidth="1"/>
-    <col min="85" max="85" width="109.42578125" customWidth="1"/>
-    <col min="86" max="86" width="116.7109375" customWidth="1"/>
-    <col min="87" max="87" width="128.5703125" customWidth="1"/>
-    <col min="88" max="88" width="120.28515625" customWidth="1"/>
-    <col min="89" max="89" width="126.5703125" customWidth="1"/>
-    <col min="90" max="90" width="151.28515625" customWidth="1"/>
-    <col min="91" max="91" width="120.42578125" customWidth="1"/>
-    <col min="92" max="92" width="112.42578125" customWidth="1"/>
-    <col min="93" max="93" width="158.5703125" customWidth="1"/>
-    <col min="94" max="94" width="103.7109375" customWidth="1"/>
-    <col min="95" max="95" width="91.85546875" customWidth="1"/>
-    <col min="96" max="96" width="70" customWidth="1"/>
-    <col min="97" max="97" width="124.42578125" customWidth="1"/>
-    <col min="98" max="98" width="139.5703125" customWidth="1"/>
-    <col min="99" max="99" width="48.85546875" customWidth="1"/>
-    <col min="100" max="100" width="76.85546875" customWidth="1"/>
-    <col min="101" max="101" width="80.140625" customWidth="1"/>
-    <col min="102" max="102" width="35.7109375" customWidth="1"/>
-    <col min="103" max="104" width="122.7109375" customWidth="1"/>
-    <col min="105" max="105" width="98" customWidth="1"/>
-    <col min="106" max="106" width="29.7109375" customWidth="1"/>
-    <col min="107" max="107" width="80.140625" customWidth="1"/>
-    <col min="108" max="108" width="68.5703125" customWidth="1"/>
-    <col min="109" max="109" width="109.28515625" customWidth="1"/>
-    <col min="110" max="110" width="62" customWidth="1"/>
-    <col min="111" max="111" width="89.5703125" customWidth="1"/>
-    <col min="112" max="112" width="108.28515625" customWidth="1"/>
-    <col min="113" max="113" width="89.5703125" customWidth="1"/>
-    <col min="114" max="114" width="69.85546875" customWidth="1"/>
-    <col min="115" max="115" width="52.140625" customWidth="1"/>
-    <col min="116" max="116" width="73.140625" customWidth="1"/>
-    <col min="117" max="117" width="29.7109375" customWidth="1"/>
-    <col min="118" max="119" width="76" customWidth="1"/>
-    <col min="120" max="120" width="72.28515625" customWidth="1"/>
-    <col min="121" max="121" width="61.7109375" customWidth="1"/>
-    <col min="122" max="122" width="60" customWidth="1"/>
-    <col min="123" max="123" width="38.140625" customWidth="1"/>
-    <col min="124" max="124" width="69" customWidth="1"/>
-    <col min="125" max="125" width="72.42578125" customWidth="1"/>
-    <col min="126" max="126" width="111.5703125" customWidth="1"/>
-    <col min="127" max="127" width="72.5703125" customWidth="1"/>
-    <col min="128" max="128" width="86.85546875" customWidth="1"/>
-    <col min="129" max="130" width="64.7109375" customWidth="1"/>
-    <col min="131" max="131" width="54.5703125" customWidth="1"/>
-    <col min="132" max="132" width="75.42578125" customWidth="1"/>
-    <col min="133" max="133" width="58.140625" customWidth="1"/>
+    <col min="2" max="5" width="66.7109375" style="40" customWidth="1"/>
+    <col min="6" max="6" width="96.85546875" style="40" customWidth="1"/>
+    <col min="7" max="9" width="151" customWidth="1"/>
+    <col min="10" max="26" width="116.28515625" customWidth="1"/>
+    <col min="27" max="28" width="70" customWidth="1"/>
+    <col min="29" max="37" width="116.28515625" customWidth="1"/>
+    <col min="38" max="38" width="90" customWidth="1"/>
+    <col min="39" max="40" width="116.28515625" customWidth="1"/>
+    <col min="41" max="41" width="70" customWidth="1"/>
+    <col min="42" max="42" width="105.28515625" customWidth="1"/>
+    <col min="43" max="44" width="70" customWidth="1"/>
+    <col min="45" max="46" width="116.28515625" customWidth="1"/>
+    <col min="47" max="49" width="70" customWidth="1"/>
+    <col min="50" max="50" width="105.28515625" customWidth="1"/>
+    <col min="51" max="51" width="70" customWidth="1"/>
+    <col min="52" max="62" width="116.28515625" customWidth="1"/>
+    <col min="63" max="65" width="70" customWidth="1"/>
+    <col min="66" max="68" width="96.7109375" customWidth="1"/>
+    <col min="69" max="69" width="70" customWidth="1"/>
+    <col min="70" max="75" width="96.7109375" customWidth="1"/>
+    <col min="76" max="86" width="70" customWidth="1"/>
+    <col min="87" max="87" width="105" customWidth="1"/>
+    <col min="88" max="90" width="96.7109375" customWidth="1"/>
+    <col min="91" max="91" width="70" customWidth="1"/>
+    <col min="92" max="92" width="116.28515625" customWidth="1"/>
+    <col min="93" max="97" width="70" customWidth="1"/>
+    <col min="98" max="100" width="116.28515625" customWidth="1"/>
+    <col min="101" max="101" width="120.85546875" customWidth="1"/>
+    <col min="102" max="102" width="109.42578125" customWidth="1"/>
+    <col min="103" max="103" width="116.7109375" customWidth="1"/>
+    <col min="104" max="104" width="128.5703125" customWidth="1"/>
+    <col min="105" max="105" width="120.28515625" customWidth="1"/>
+    <col min="106" max="106" width="126.5703125" customWidth="1"/>
+    <col min="107" max="107" width="151.28515625" customWidth="1"/>
+    <col min="108" max="108" width="120.42578125" customWidth="1"/>
+    <col min="109" max="109" width="112.42578125" customWidth="1"/>
+    <col min="110" max="110" width="158.5703125" customWidth="1"/>
+    <col min="111" max="111" width="103.7109375" customWidth="1"/>
+    <col min="112" max="112" width="91.85546875" customWidth="1"/>
+    <col min="113" max="113" width="70" customWidth="1"/>
+    <col min="114" max="114" width="124.42578125" customWidth="1"/>
+    <col min="115" max="115" width="139.5703125" customWidth="1"/>
+    <col min="116" max="116" width="48.85546875" customWidth="1"/>
+    <col min="117" max="117" width="76.85546875" customWidth="1"/>
+    <col min="118" max="118" width="80.140625" customWidth="1"/>
+    <col min="119" max="119" width="35.7109375" customWidth="1"/>
+    <col min="120" max="121" width="122.7109375" customWidth="1"/>
+    <col min="122" max="122" width="98" customWidth="1"/>
+    <col min="123" max="123" width="29.7109375" customWidth="1"/>
+    <col min="124" max="124" width="80.140625" customWidth="1"/>
+    <col min="125" max="125" width="68.5703125" customWidth="1"/>
+    <col min="126" max="126" width="109.28515625" customWidth="1"/>
+    <col min="127" max="127" width="62" customWidth="1"/>
+    <col min="128" max="128" width="89.5703125" customWidth="1"/>
+    <col min="129" max="129" width="108.28515625" customWidth="1"/>
+    <col min="130" max="130" width="89.5703125" customWidth="1"/>
+    <col min="131" max="131" width="69.85546875" customWidth="1"/>
+    <col min="132" max="132" width="52.140625" customWidth="1"/>
+    <col min="133" max="133" width="73.140625" customWidth="1"/>
+    <col min="134" max="134" width="29.7109375" customWidth="1"/>
+    <col min="135" max="136" width="76" customWidth="1"/>
+    <col min="137" max="137" width="72.28515625" customWidth="1"/>
+    <col min="138" max="138" width="61.7109375" customWidth="1"/>
+    <col min="139" max="139" width="60" customWidth="1"/>
+    <col min="140" max="140" width="38.140625" customWidth="1"/>
+    <col min="141" max="141" width="69" customWidth="1"/>
+    <col min="142" max="142" width="72.42578125" customWidth="1"/>
+    <col min="143" max="143" width="111.5703125" customWidth="1"/>
+    <col min="144" max="144" width="72.5703125" customWidth="1"/>
+    <col min="145" max="145" width="86.85546875" customWidth="1"/>
+    <col min="146" max="147" width="64.7109375" customWidth="1"/>
+    <col min="148" max="148" width="54.5703125" customWidth="1"/>
+    <col min="149" max="149" width="75.42578125" customWidth="1"/>
+    <col min="150" max="150" width="58.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:134" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3940,8 +4129,12 @@
       <c r="I1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
+      <c r="J1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="L1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3969,26 +4162,26 @@
       <c r="T1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="U1" s="1"/>
+      <c r="U1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="V1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="X1" s="1"/>
+      <c r="X1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="Y1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AA1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
       <c r="AC1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4016,18 +4209,14 @@
       <c r="AK1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AL1" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="AL1" s="1"/>
       <c r="AM1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="AN1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AO1" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="AO1" s="1"/>
       <c r="AP1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4040,23 +4229,57 @@
       <c r="AS1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AT1" s="1"/>
-      <c r="AU1" s="1"/>
-      <c r="AV1" s="1"/>
-      <c r="AW1" s="1"/>
-      <c r="AX1" s="1"/>
-      <c r="AY1" s="1"/>
-      <c r="AZ1" s="1"/>
-      <c r="BA1" s="1"/>
-      <c r="BB1" s="1"/>
-      <c r="BC1" s="1"/>
-      <c r="BD1" s="1"/>
-      <c r="BE1" s="1"/>
-      <c r="BF1" s="1"/>
-      <c r="BG1" s="1"/>
-      <c r="BH1" s="1"/>
-      <c r="BI1" s="1"/>
-      <c r="BJ1" s="1"/>
+      <c r="AT1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
       <c r="BM1" s="1"/>
@@ -4069,65 +4292,31 @@
       <c r="BT1" s="1"/>
       <c r="BU1" s="1"/>
       <c r="BV1" s="1"/>
-      <c r="BW1" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="BW1" s="1"/>
       <c r="BX1" s="1"/>
       <c r="BY1" s="1"/>
       <c r="BZ1" s="1"/>
       <c r="CA1" s="1"/>
       <c r="CB1" s="1"/>
-      <c r="CC1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CD1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CE1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CF1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CG1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CH1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CI1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CJ1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CK1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CL1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CM1" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="CC1" s="1"/>
+      <c r="CD1" s="1"/>
+      <c r="CE1" s="1"/>
+      <c r="CF1" s="1"/>
+      <c r="CG1" s="1"/>
+      <c r="CH1" s="1"/>
+      <c r="CI1" s="1"/>
+      <c r="CJ1" s="1"/>
+      <c r="CK1" s="1"/>
+      <c r="CL1" s="1"/>
+      <c r="CM1" s="1"/>
       <c r="CN1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="CO1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CP1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CQ1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CR1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CS1" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="CO1" s="1"/>
+      <c r="CP1" s="1"/>
+      <c r="CQ1" s="1"/>
+      <c r="CR1" s="1"/>
+      <c r="CS1" s="1"/>
       <c r="CT1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4239,14 +4428,69 @@
       <c r="ED1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:134" x14ac:dyDescent="0.25">
+      <c r="EE1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="EF1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="EG1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="EH1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="EI1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="EJ1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="EK1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="EL1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="EM1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="EN1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="EO1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="EP1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="EQ1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="ER1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="ES1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="ET1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="EU1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="39"/>
-    </row>
-    <row r="3" spans="1:134" x14ac:dyDescent="0.25">
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -4254,757 +4498,859 @@
       <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="AJ3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="AS3" s="39"/>
-    </row>
-    <row r="4" spans="1:134" x14ac:dyDescent="0.25">
+      <c r="BJ3" s="39"/>
+    </row>
+    <row r="4" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="39"/>
       <c r="C4" t="s">
-        <v>1021</v>
+        <v>1082</v>
       </c>
       <c r="D4" t="s">
-        <v>1017</v>
+        <v>771</v>
       </c>
       <c r="E4" t="s">
-        <v>1014</v>
+        <v>1024</v>
       </c>
       <c r="F4" t="s">
-        <v>1009</v>
+        <v>1016</v>
       </c>
       <c r="G4" t="s">
-        <v>1005</v>
+        <v>1068</v>
       </c>
       <c r="H4" t="s">
-        <v>1001</v>
+        <v>1064</v>
       </c>
       <c r="I4" t="s">
-        <v>851</v>
+        <v>1060</v>
       </c>
       <c r="J4" t="s">
-        <v>995</v>
+        <v>1058</v>
       </c>
       <c r="K4" t="s">
-        <v>763</v>
+        <v>1020</v>
       </c>
       <c r="L4" t="s">
-        <v>851</v>
+        <v>1039</v>
       </c>
       <c r="M4" t="s">
-        <v>938</v>
+        <v>789</v>
       </c>
       <c r="N4" t="s">
-        <v>839</v>
+        <v>769</v>
       </c>
       <c r="O4" t="s">
-        <v>980</v>
+        <v>1039</v>
       </c>
       <c r="P4" t="s">
-        <v>815</v>
+        <v>994</v>
       </c>
       <c r="Q4" t="s">
-        <v>851</v>
+        <v>1032</v>
       </c>
       <c r="R4" t="s">
-        <v>851</v>
+        <v>1028</v>
       </c>
       <c r="S4" t="s">
-        <v>907</v>
+        <v>1024</v>
       </c>
       <c r="T4" t="s">
-        <v>851</v>
+        <v>1020</v>
       </c>
       <c r="U4" t="s">
-        <v>917</v>
+        <v>1016</v>
       </c>
       <c r="V4" t="s">
-        <v>839</v>
+        <v>1013</v>
       </c>
       <c r="W4" t="s">
-        <v>895</v>
+        <v>1008</v>
       </c>
       <c r="X4" t="s">
-        <v>763</v>
+        <v>1004</v>
       </c>
       <c r="Y4" t="s">
-        <v>921</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="s">
-        <v>946</v>
+        <v>850</v>
       </c>
       <c r="AA4" t="s">
+        <v>994</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>762</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>850</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>937</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>838</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>979</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>814</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>850</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>850</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>906</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>850</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>916</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>838</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>894</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>762</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>920</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>945</v>
+      </c>
+      <c r="AR4" t="s">
         <v>731</v>
       </c>
-      <c r="AB4" t="s">
-        <v>938</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>839</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>763</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>927</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>917</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>921</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>917</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>907</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>772</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>907</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>839</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>900</v>
-      </c>
-      <c r="AN4" t="s">
-        <v>895</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>891</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>847</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>877</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>763</v>
-      </c>
       <c r="AS4" t="s">
-        <v>851</v>
+        <v>937</v>
       </c>
       <c r="AT4" t="s">
-        <v>847</v>
+        <v>838</v>
       </c>
       <c r="AU4" t="s">
-        <v>839</v>
+        <v>762</v>
       </c>
       <c r="AV4" t="s">
-        <v>836</v>
+        <v>926</v>
       </c>
       <c r="AW4" t="s">
+        <v>916</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>920</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>916</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>906</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>771</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>906</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>838</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>899</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>894</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>890</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>846</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>876</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>762</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>850</v>
+      </c>
+      <c r="BK4" t="s">
+        <v>846</v>
+      </c>
+      <c r="BL4" t="s">
+        <v>838</v>
+      </c>
+      <c r="BM4" t="s">
         <v>835</v>
       </c>
-      <c r="AX4" t="s">
-        <v>830</v>
-      </c>
-      <c r="AY4" t="s">
-        <v>815</v>
-      </c>
-      <c r="AZ4" t="s">
+      <c r="BN4" t="s">
+        <v>834</v>
+      </c>
+      <c r="BO4" t="s">
+        <v>829</v>
+      </c>
+      <c r="BP4" t="s">
+        <v>814</v>
+      </c>
+      <c r="BQ4" t="s">
         <v>746</v>
       </c>
-      <c r="BA4" t="s">
-        <v>819</v>
-      </c>
-      <c r="BB4" t="s">
-        <v>819</v>
-      </c>
-      <c r="BC4" t="s">
-        <v>815</v>
-      </c>
-      <c r="BD4" t="s">
-        <v>812</v>
-      </c>
-      <c r="BE4" t="s">
-        <v>809</v>
-      </c>
-      <c r="BF4" t="s">
-        <v>763</v>
-      </c>
-      <c r="BG4" t="s">
-        <v>804</v>
-      </c>
-      <c r="BH4" t="s">
-        <v>800</v>
-      </c>
-      <c r="BI4" t="s">
-        <v>796</v>
-      </c>
-      <c r="BJ4" t="s">
-        <v>793</v>
-      </c>
-      <c r="BK4" t="s">
-        <v>790</v>
-      </c>
-      <c r="BL4" t="s">
-        <v>787</v>
-      </c>
-      <c r="BM4" t="s">
-        <v>784</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>782</v>
-      </c>
-      <c r="BO4" t="s">
-        <v>778</v>
-      </c>
-      <c r="BP4" t="s">
-        <v>776</v>
-      </c>
-      <c r="BQ4" t="s">
-        <v>772</v>
-      </c>
       <c r="BR4" t="s">
-        <v>770</v>
+        <v>818</v>
       </c>
       <c r="BS4" t="s">
-        <v>766</v>
+        <v>818</v>
       </c>
       <c r="BT4" t="s">
-        <v>763</v>
+        <v>814</v>
       </c>
       <c r="BU4" t="s">
+        <v>811</v>
+      </c>
+      <c r="BV4" t="s">
+        <v>808</v>
+      </c>
+      <c r="BW4" t="s">
+        <v>762</v>
+      </c>
+      <c r="BX4" t="s">
+        <v>803</v>
+      </c>
+      <c r="BY4" t="s">
+        <v>799</v>
+      </c>
+      <c r="BZ4" t="s">
+        <v>795</v>
+      </c>
+      <c r="CA4" t="s">
+        <v>792</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>789</v>
+      </c>
+      <c r="CC4" t="s">
+        <v>786</v>
+      </c>
+      <c r="CD4" t="s">
+        <v>783</v>
+      </c>
+      <c r="CE4" t="s">
+        <v>781</v>
+      </c>
+      <c r="CF4" t="s">
+        <v>777</v>
+      </c>
+      <c r="CG4" t="s">
+        <v>775</v>
+      </c>
+      <c r="CH4" t="s">
+        <v>771</v>
+      </c>
+      <c r="CI4" t="s">
+        <v>769</v>
+      </c>
+      <c r="CJ4" t="s">
+        <v>765</v>
+      </c>
+      <c r="CK4" t="s">
+        <v>762</v>
+      </c>
+      <c r="CL4" t="s">
         <v>654</v>
       </c>
-      <c r="BV4" t="s">
+      <c r="CM4" t="s">
         <v>746</v>
       </c>
-      <c r="BW4" t="s">
+      <c r="CN4" t="s">
         <v>15</v>
       </c>
-      <c r="BX4" t="s">
+      <c r="CO4" t="s">
         <v>733</v>
       </c>
-      <c r="BY4" t="s">
+      <c r="CP4" t="s">
         <v>731</v>
       </c>
-      <c r="BZ4" t="s">
+      <c r="CQ4" t="s">
         <v>723</v>
       </c>
-      <c r="CA4" t="s">
+      <c r="CR4" t="s">
         <v>655</v>
       </c>
-      <c r="CB4" t="s">
+      <c r="CS4" t="s">
         <v>654</v>
       </c>
-      <c r="CC4" t="s">
+      <c r="CT4" t="s">
         <v>15</v>
       </c>
-      <c r="CD4" t="s">
+      <c r="CU4" t="s">
         <v>16</v>
       </c>
-      <c r="CE4" t="s">
+      <c r="CV4" t="s">
         <v>16</v>
-      </c>
-      <c r="CF4" t="s">
-        <v>17</v>
-      </c>
-      <c r="CG4" t="s">
-        <v>18</v>
-      </c>
-      <c r="CH4" t="s">
-        <v>19</v>
-      </c>
-      <c r="CI4" t="s">
-        <v>20</v>
-      </c>
-      <c r="CJ4" t="s">
-        <v>21</v>
-      </c>
-      <c r="CK4" t="s">
-        <v>22</v>
-      </c>
-      <c r="CL4" t="s">
-        <v>19</v>
-      </c>
-      <c r="CM4" t="s">
-        <v>23</v>
-      </c>
-      <c r="CN4" t="s">
-        <v>24</v>
-      </c>
-      <c r="CO4" t="s">
-        <v>25</v>
-      </c>
-      <c r="CP4" t="s">
-        <v>26</v>
-      </c>
-      <c r="CQ4" t="s">
-        <v>26</v>
-      </c>
-      <c r="CR4" t="s">
-        <v>27</v>
-      </c>
-      <c r="CS4" t="s">
-        <v>27</v>
-      </c>
-      <c r="CT4" t="s">
-        <v>16</v>
-      </c>
-      <c r="CU4" t="s">
-        <v>28</v>
-      </c>
-      <c r="CV4" t="s">
-        <v>27</v>
       </c>
       <c r="CW4" t="s">
         <v>17</v>
       </c>
       <c r="CX4" t="s">
+        <v>18</v>
+      </c>
+      <c r="CY4" t="s">
+        <v>19</v>
+      </c>
+      <c r="CZ4" t="s">
+        <v>20</v>
+      </c>
+      <c r="DA4" t="s">
+        <v>21</v>
+      </c>
+      <c r="DB4" t="s">
+        <v>22</v>
+      </c>
+      <c r="DC4" t="s">
+        <v>19</v>
+      </c>
+      <c r="DD4" t="s">
+        <v>23</v>
+      </c>
+      <c r="DE4" t="s">
+        <v>24</v>
+      </c>
+      <c r="DF4" t="s">
+        <v>25</v>
+      </c>
+      <c r="DG4" t="s">
+        <v>26</v>
+      </c>
+      <c r="DH4" t="s">
+        <v>26</v>
+      </c>
+      <c r="DI4" t="s">
+        <v>27</v>
+      </c>
+      <c r="DJ4" t="s">
+        <v>27</v>
+      </c>
+      <c r="DK4" t="s">
+        <v>16</v>
+      </c>
+      <c r="DL4" t="s">
+        <v>28</v>
+      </c>
+      <c r="DM4" t="s">
+        <v>27</v>
+      </c>
+      <c r="DN4" t="s">
+        <v>17</v>
+      </c>
+      <c r="DO4" t="s">
         <v>29</v>
       </c>
-      <c r="CY4" t="s">
+      <c r="DP4" t="s">
         <v>25</v>
       </c>
-      <c r="CZ4" t="s">
+      <c r="DQ4" t="s">
         <v>25</v>
       </c>
-      <c r="DA4" t="s">
+      <c r="DR4" t="s">
         <v>30</v>
       </c>
-      <c r="DB4" t="s">
+      <c r="DS4" t="s">
         <v>31</v>
       </c>
-      <c r="DC4" t="s">
+      <c r="DT4" t="s">
         <v>32</v>
       </c>
-      <c r="DD4" t="s">
+      <c r="DU4" t="s">
         <v>33</v>
       </c>
-      <c r="DE4" t="s">
+      <c r="DV4" t="s">
         <v>34</v>
       </c>
-      <c r="DF4" t="s">
+      <c r="DW4" t="s">
         <v>35</v>
       </c>
-      <c r="DG4" t="s">
+      <c r="DX4" t="s">
         <v>36</v>
       </c>
-      <c r="DH4" t="s">
+      <c r="DY4" t="s">
         <v>37</v>
       </c>
-      <c r="DI4" t="s">
+      <c r="DZ4" t="s">
         <v>37</v>
       </c>
-      <c r="DJ4" t="s">
+      <c r="EA4" t="s">
         <v>37</v>
       </c>
-      <c r="DK4" t="s">
+      <c r="EB4" t="s">
         <v>38</v>
       </c>
-      <c r="DL4" t="s">
+      <c r="EC4" t="s">
         <v>39</v>
       </c>
-      <c r="DM4" t="s">
+      <c r="ED4" t="s">
         <v>39</v>
       </c>
-      <c r="DN4" t="s">
+      <c r="EE4" t="s">
         <v>40</v>
       </c>
-      <c r="DO4" t="s">
+      <c r="EF4" t="s">
         <v>40</v>
       </c>
-      <c r="DP4" t="s">
+      <c r="EG4" t="s">
         <v>17</v>
       </c>
-      <c r="DQ4" t="s">
+      <c r="EH4" t="s">
         <v>41</v>
       </c>
-      <c r="DR4" t="s">
+      <c r="EI4" t="s">
         <v>42</v>
       </c>
-      <c r="DS4" t="s">
+      <c r="EJ4" t="s">
         <v>43</v>
       </c>
-      <c r="DT4" t="s">
+      <c r="EK4" t="s">
         <v>44</v>
       </c>
-      <c r="DU4" t="s">
+      <c r="EL4" t="s">
         <v>45</v>
       </c>
-      <c r="DV4" t="s">
+      <c r="EM4" t="s">
         <v>46</v>
       </c>
-      <c r="DW4" t="s">
+      <c r="EN4" t="s">
         <v>47</v>
       </c>
-      <c r="DX4" s="2" t="s">
+      <c r="EO4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="DY4" s="2" t="s">
+      <c r="EP4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="DZ4" s="2" t="s">
+      <c r="EQ4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="EA4" s="2" t="s">
+      <c r="ER4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="EB4" s="2" t="s">
+      <c r="ES4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="EC4" s="2" t="s">
+      <c r="ET4" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="ED4" s="2" t="s">
+      <c r="EU4" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:134" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>55</v>
       </c>
       <c r="B5" s="39"/>
       <c r="C5" s="5">
+        <v>46111</v>
+      </c>
+      <c r="D5" s="5">
+        <v>46108</v>
+      </c>
+      <c r="E5" s="5">
+        <v>46107</v>
+      </c>
+      <c r="F5" s="5">
+        <v>46106</v>
+      </c>
+      <c r="G5" s="5">
+        <v>45818</v>
+      </c>
+      <c r="H5" s="5">
+        <v>45818</v>
+      </c>
+      <c r="I5" s="5">
+        <v>45810</v>
+      </c>
+      <c r="J5" s="5">
+        <v>45793</v>
+      </c>
+      <c r="K5" s="5">
+        <v>45771</v>
+      </c>
+      <c r="L5" s="5">
+        <v>45758</v>
+      </c>
+      <c r="M5" s="5">
+        <v>45751</v>
+      </c>
+      <c r="N5" s="5">
+        <v>45742</v>
+      </c>
+      <c r="O5" s="5">
+        <v>45730</v>
+      </c>
+      <c r="P5" s="5">
+        <v>45726</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>45721</v>
+      </c>
+      <c r="R5" s="5">
+        <v>45688</v>
+      </c>
+      <c r="S5" s="5">
+        <v>45684</v>
+      </c>
+      <c r="T5" s="5">
         <v>45677</v>
       </c>
-      <c r="D5" s="5">
+      <c r="U5" s="5">
         <v>45673</v>
       </c>
-      <c r="E5" s="5">
+      <c r="V5" s="5">
         <v>45672</v>
       </c>
-      <c r="F5" s="5">
+      <c r="W5" s="5">
         <v>45671</v>
       </c>
-      <c r="G5" s="5">
+      <c r="X5" s="5">
         <v>45531</v>
       </c>
-      <c r="H5" s="5">
+      <c r="Y5" s="5">
         <v>45531</v>
       </c>
-      <c r="I5" s="5">
+      <c r="Z5" s="5">
         <v>45531</v>
       </c>
-      <c r="J5" s="5">
+      <c r="AA5" s="5">
         <v>45523</v>
       </c>
-      <c r="K5" s="5">
+      <c r="AB5" s="5">
         <v>45473</v>
       </c>
-      <c r="L5" s="5">
+      <c r="AC5" s="5">
         <v>45378</v>
       </c>
-      <c r="M5" s="5">
+      <c r="AD5" s="5">
         <v>45391</v>
       </c>
-      <c r="N5" s="5">
+      <c r="AE5" s="5">
         <v>45391</v>
       </c>
-      <c r="O5" s="5">
+      <c r="AF5" s="5">
         <v>45385</v>
       </c>
-      <c r="P5" s="5">
+      <c r="AG5" s="5">
         <v>45384</v>
       </c>
-      <c r="Q5" s="5">
+      <c r="AH5" s="5">
         <v>45378</v>
       </c>
-      <c r="R5" s="5">
+      <c r="AI5" s="5">
         <v>45366</v>
       </c>
-      <c r="S5" s="5">
+      <c r="AJ5" s="5">
         <v>45364</v>
       </c>
-      <c r="T5" s="5">
+      <c r="AK5" s="5">
         <v>45351</v>
       </c>
-      <c r="U5" s="5">
+      <c r="AL5" s="5">
         <v>44973</v>
       </c>
-      <c r="V5" s="5">
+      <c r="AM5" s="5">
         <v>45309</v>
       </c>
-      <c r="W5" s="5">
+      <c r="AN5" s="5">
         <v>45307</v>
       </c>
-      <c r="X5" s="5">
+      <c r="AO5" s="5">
         <v>45301</v>
       </c>
-      <c r="Y5" s="5">
+      <c r="AP5" s="5">
         <v>45279</v>
       </c>
-      <c r="Z5" s="5">
+      <c r="AQ5" s="5">
         <v>45268</v>
       </c>
-      <c r="AA5" s="5">
+      <c r="AR5" s="5">
         <v>45268</v>
       </c>
-      <c r="AB5" s="5">
+      <c r="AS5" s="5">
         <v>45267</v>
       </c>
-      <c r="AC5" s="5">
+      <c r="AT5" s="5">
         <v>45267</v>
       </c>
-      <c r="AD5" s="5">
+      <c r="AU5" s="5">
         <v>45254</v>
       </c>
-      <c r="AE5" s="5">
+      <c r="AV5" s="5">
         <v>45252</v>
       </c>
-      <c r="AF5" s="5">
+      <c r="AW5" s="5">
         <v>45247</v>
       </c>
-      <c r="AG5" s="5">
+      <c r="AX5" s="5">
         <v>45246</v>
       </c>
-      <c r="AH5" s="5">
+      <c r="AY5" s="5">
         <v>45237</v>
       </c>
-      <c r="AI5" s="5">
+      <c r="AZ5" s="5">
         <v>45211</v>
       </c>
-      <c r="AJ5" s="5">
+      <c r="BA5" s="5">
         <v>45201</v>
       </c>
-      <c r="AK5" s="5">
+      <c r="BB5" s="5">
         <v>45195</v>
       </c>
-      <c r="AL5" s="5">
+      <c r="BC5" s="5">
         <v>45188</v>
       </c>
-      <c r="AM5" s="5">
+      <c r="BD5" s="5">
         <v>45188</v>
       </c>
-      <c r="AN5" s="5">
+      <c r="BE5" s="5">
         <v>45188</v>
       </c>
-      <c r="AO5" s="5">
+      <c r="BF5" s="5">
         <v>45187</v>
       </c>
-      <c r="AP5" s="5">
+      <c r="BG5" s="5">
         <v>45167</v>
       </c>
-      <c r="AQ5" s="5">
+      <c r="BH5" s="5">
         <v>45154</v>
       </c>
-      <c r="AR5" s="5">
+      <c r="BI5" s="5">
         <v>45154</v>
       </c>
-      <c r="AS5" s="5">
+      <c r="BJ5" s="5">
         <v>45128</v>
       </c>
-      <c r="AT5" s="5">
+      <c r="BK5" s="5">
         <v>45118</v>
       </c>
-      <c r="AU5" s="5">
+      <c r="BL5" s="5">
         <v>45092</v>
       </c>
-      <c r="AV5" s="5">
+      <c r="BM5" s="5">
         <v>45085</v>
       </c>
-      <c r="AW5" s="5">
+      <c r="BN5" s="5">
         <v>45061</v>
       </c>
-      <c r="AX5" s="5">
+      <c r="BO5" s="5">
         <v>45058</v>
       </c>
-      <c r="AY5" s="5">
+      <c r="BP5" s="5">
         <v>45057</v>
       </c>
-      <c r="AZ5" s="5">
+      <c r="BQ5" s="5">
         <v>45056</v>
       </c>
-      <c r="BA5" s="5">
+      <c r="BR5" s="5">
         <v>45051</v>
       </c>
-      <c r="BB5" s="5">
+      <c r="BS5" s="5">
         <v>45050</v>
       </c>
-      <c r="BC5" s="5">
+      <c r="BT5" s="5">
         <v>45041</v>
       </c>
-      <c r="BD5" s="5">
+      <c r="BU5" s="5">
         <v>45035</v>
       </c>
-      <c r="BE5" s="5">
+      <c r="BV5" s="5">
         <v>45030</v>
       </c>
-      <c r="BF5" s="5">
+      <c r="BW5" s="5">
         <v>45030</v>
       </c>
-      <c r="BG5" s="5">
+      <c r="BX5" s="5">
         <v>45029</v>
       </c>
-      <c r="BH5" s="5">
+      <c r="BY5" s="5">
         <v>45027</v>
       </c>
-      <c r="BI5" s="5">
+      <c r="BZ5" s="5">
         <v>45026</v>
       </c>
-      <c r="BJ5" s="5">
+      <c r="CA5" s="5">
         <v>45023</v>
       </c>
-      <c r="BK5" s="5">
+      <c r="CB5" s="5">
         <v>45020</v>
       </c>
-      <c r="BL5" s="5">
+      <c r="CC5" s="5">
         <v>45008</v>
       </c>
-      <c r="BM5" s="5">
+      <c r="CD5" s="5">
         <v>45008</v>
       </c>
-      <c r="BN5" s="5">
+      <c r="CE5" s="5">
         <v>45008</v>
       </c>
-      <c r="BO5" s="5">
+      <c r="CF5" s="5">
         <v>45008</v>
       </c>
-      <c r="BP5" s="5">
+      <c r="CG5" s="5">
         <v>45007</v>
       </c>
-      <c r="BQ5" s="5">
+      <c r="CH5" s="5">
         <v>45006</v>
       </c>
-      <c r="BR5" s="5">
+      <c r="CI5" s="5">
         <v>45002</v>
       </c>
-      <c r="BS5" s="5">
+      <c r="CJ5" s="5">
         <v>45000</v>
       </c>
-      <c r="BT5" s="5">
+      <c r="CK5" s="5">
         <v>44999</v>
       </c>
-      <c r="BU5" s="5">
+      <c r="CL5" s="5">
         <v>44949</v>
       </c>
-      <c r="BV5" s="5">
+      <c r="CM5" s="5">
         <v>44943</v>
       </c>
-      <c r="BW5" s="5">
+      <c r="CN5" s="5">
         <v>44868</v>
       </c>
-      <c r="BZ5" s="5">
+      <c r="CQ5" s="5">
         <v>44903</v>
       </c>
-      <c r="CA5" s="5">
+      <c r="CR5" s="5">
         <v>44889</v>
       </c>
-      <c r="CB5" s="5">
+      <c r="CS5" s="5">
         <v>44879</v>
       </c>
-      <c r="CC5" s="5">
+      <c r="CT5" s="5">
         <v>44868</v>
       </c>
-      <c r="CD5" s="5">
+      <c r="CU5" s="5">
         <v>44632</v>
       </c>
-      <c r="CE5" s="5">
+      <c r="CV5" s="5">
         <v>44620</v>
       </c>
-      <c r="CF5" s="5">
+      <c r="CW5" s="5">
         <v>44608</v>
       </c>
-      <c r="CG5" s="5">
+      <c r="CX5" s="5">
         <v>44592</v>
       </c>
-      <c r="CH5" s="5">
+      <c r="CY5" s="5">
         <v>44575</v>
       </c>
-      <c r="CI5" s="5">
+      <c r="CZ5" s="5">
         <v>44537</v>
       </c>
-      <c r="CJ5" s="5">
+      <c r="DA5" s="5">
         <v>44531</v>
       </c>
-      <c r="CK5" s="5">
+      <c r="DB5" s="5">
         <v>44530</v>
       </c>
-      <c r="CL5" s="5">
+      <c r="DC5" s="5">
         <v>44529</v>
       </c>
-      <c r="CM5" s="5">
+      <c r="DD5" s="5">
         <v>44524</v>
       </c>
-      <c r="CN5" s="5">
+      <c r="DE5" s="5">
         <v>44503</v>
       </c>
-      <c r="CO5" s="5">
+      <c r="DF5" s="5">
         <v>44343</v>
       </c>
-      <c r="CP5" s="5">
+      <c r="DG5" s="5">
         <v>44484</v>
       </c>
-      <c r="CQ5" s="5">
+      <c r="DH5" s="5">
         <v>44484</v>
       </c>
-      <c r="CR5" s="5">
+      <c r="DI5" s="5">
         <v>44473</v>
       </c>
-      <c r="CS5" s="5">
+      <c r="DJ5" s="5">
         <v>44469</v>
       </c>
-      <c r="CT5" s="5">
+      <c r="DK5" s="5">
         <v>44453</v>
       </c>
-      <c r="CU5" s="5">
+      <c r="DL5" s="5">
         <v>44426</v>
       </c>
-      <c r="CV5" s="5">
+      <c r="DM5" s="5">
         <v>44330</v>
       </c>
-      <c r="CW5" s="5">
+      <c r="DN5" s="5">
         <v>44307</v>
       </c>
-      <c r="CX5" s="5">
+      <c r="DO5" s="5">
         <v>44294</v>
       </c>
-      <c r="CY5" s="5">
+      <c r="DP5" s="5">
         <v>44343</v>
       </c>
-      <c r="CZ5" s="5">
+      <c r="DQ5" s="5">
         <v>44292</v>
       </c>
-      <c r="DA5" s="5">
+      <c r="DR5" s="5">
         <v>44291</v>
       </c>
-      <c r="DB5" s="5">
+      <c r="DS5" s="5">
         <v>44286</v>
       </c>
-      <c r="DC5" s="5">
+      <c r="DT5" s="5">
         <v>44260</v>
       </c>
-      <c r="DD5" s="5">
+      <c r="DU5" s="5">
         <v>44244</v>
       </c>
-      <c r="DE5" s="5">
+      <c r="DV5" s="5">
         <v>44245</v>
       </c>
-      <c r="DF5" s="5">
+      <c r="DW5" s="5">
         <v>44223</v>
       </c>
-      <c r="DG5" s="5">
+      <c r="DX5" s="5">
         <v>44209</v>
       </c>
-      <c r="DH5" s="5">
+      <c r="DY5" s="5">
         <v>44253</v>
       </c>
-      <c r="DI5" s="5">
+      <c r="DZ5" s="5">
         <v>44237</v>
       </c>
-      <c r="DL5" s="5">
+      <c r="EC5" s="5">
         <v>44181</v>
       </c>
-      <c r="DX5" s="2"/>
-      <c r="DY5" s="2"/>
-      <c r="DZ5" s="2"/>
-      <c r="EA5" s="2"/>
-      <c r="EB5" s="2"/>
-      <c r="EC5" s="2"/>
-      <c r="ED5" s="2"/>
-    </row>
-    <row r="6" spans="1:134" x14ac:dyDescent="0.25">
+      <c r="EO5" s="2"/>
+      <c r="EP5" s="2"/>
+      <c r="EQ5" s="2"/>
+      <c r="ER5" s="2"/>
+      <c r="ES5" s="2"/>
+      <c r="ET5" s="2"/>
+      <c r="EU5" s="2"/>
+    </row>
+    <row r="6" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>56</v>
       </c>
@@ -5025,10 +5371,10 @@
         <v>747</v>
       </c>
       <c r="H6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="I6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="J6" t="s">
         <v>747</v>
@@ -5037,73 +5383,73 @@
         <v>747</v>
       </c>
       <c r="L6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="M6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="N6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="O6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="P6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="Q6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="R6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="S6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="T6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="U6" t="s">
         <v>747</v>
       </c>
       <c r="V6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="W6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="X6" t="s">
         <v>747</v>
       </c>
       <c r="Y6" t="s">
-        <v>747</v>
+        <v>57</v>
       </c>
       <c r="Z6" t="s">
-        <v>747</v>
+        <v>57</v>
       </c>
       <c r="AA6" t="s">
         <v>747</v>
       </c>
       <c r="AB6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="AC6" t="s">
         <v>57</v>
       </c>
       <c r="AD6" t="s">
-        <v>747</v>
+        <v>57</v>
       </c>
       <c r="AE6" t="s">
-        <v>747</v>
+        <v>57</v>
       </c>
       <c r="AF6" t="s">
-        <v>747</v>
+        <v>57</v>
       </c>
       <c r="AG6" t="s">
-        <v>747</v>
+        <v>57</v>
       </c>
       <c r="AH6" t="s">
-        <v>747</v>
+        <v>57</v>
       </c>
       <c r="AI6" t="s">
         <v>57</v>
@@ -5115,7 +5461,7 @@
         <v>57</v>
       </c>
       <c r="AL6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="AM6" t="s">
         <v>57</v>
@@ -5124,22 +5470,22 @@
         <v>57</v>
       </c>
       <c r="AO6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="AP6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="AQ6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="AR6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="AS6" t="s">
         <v>57</v>
       </c>
       <c r="AT6" t="s">
-        <v>747</v>
+        <v>57</v>
       </c>
       <c r="AU6" t="s">
         <v>747</v>
@@ -5157,37 +5503,37 @@
         <v>747</v>
       </c>
       <c r="AZ6" t="s">
-        <v>747</v>
+        <v>57</v>
       </c>
       <c r="BA6" t="s">
-        <v>747</v>
+        <v>57</v>
       </c>
       <c r="BB6" t="s">
-        <v>747</v>
+        <v>57</v>
       </c>
       <c r="BC6" t="s">
-        <v>747</v>
+        <v>57</v>
       </c>
       <c r="BD6" t="s">
-        <v>747</v>
+        <v>57</v>
       </c>
       <c r="BE6" t="s">
-        <v>747</v>
+        <v>57</v>
       </c>
       <c r="BF6" t="s">
-        <v>747</v>
+        <v>57</v>
       </c>
       <c r="BG6" t="s">
-        <v>747</v>
+        <v>57</v>
       </c>
       <c r="BH6" t="s">
-        <v>747</v>
+        <v>57</v>
       </c>
       <c r="BI6" t="s">
-        <v>747</v>
+        <v>57</v>
       </c>
       <c r="BJ6" t="s">
-        <v>747</v>
+        <v>57</v>
       </c>
       <c r="BK6" t="s">
         <v>747</v>
@@ -5226,88 +5572,88 @@
         <v>747</v>
       </c>
       <c r="BW6" t="s">
+        <v>747</v>
+      </c>
+      <c r="BX6" t="s">
+        <v>747</v>
+      </c>
+      <c r="BY6" t="s">
+        <v>747</v>
+      </c>
+      <c r="BZ6" t="s">
+        <v>747</v>
+      </c>
+      <c r="CA6" t="s">
+        <v>747</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>747</v>
+      </c>
+      <c r="CC6" t="s">
+        <v>747</v>
+      </c>
+      <c r="CD6" t="s">
+        <v>747</v>
+      </c>
+      <c r="CE6" t="s">
+        <v>747</v>
+      </c>
+      <c r="CF6" t="s">
+        <v>747</v>
+      </c>
+      <c r="CG6" t="s">
+        <v>747</v>
+      </c>
+      <c r="CH6" t="s">
+        <v>747</v>
+      </c>
+      <c r="CI6" t="s">
+        <v>747</v>
+      </c>
+      <c r="CJ6" t="s">
+        <v>747</v>
+      </c>
+      <c r="CK6" t="s">
+        <v>747</v>
+      </c>
+      <c r="CL6" t="s">
+        <v>747</v>
+      </c>
+      <c r="CM6" t="s">
+        <v>747</v>
+      </c>
+      <c r="CN6" t="s">
         <v>57</v>
       </c>
-      <c r="BX6" t="s">
+      <c r="CO6" t="s">
         <v>57</v>
       </c>
-      <c r="BY6" t="s">
+      <c r="CP6" t="s">
         <v>57</v>
       </c>
-      <c r="BZ6" t="s">
+      <c r="CQ6" t="s">
         <v>57</v>
       </c>
-      <c r="CA6" t="s">
+      <c r="CR6" t="s">
         <v>57</v>
       </c>
-      <c r="CB6" t="s">
+      <c r="CS6" t="s">
         <v>57</v>
       </c>
-      <c r="CC6" t="s">
+      <c r="CT6" t="s">
         <v>57</v>
       </c>
-      <c r="CD6" t="s">
+      <c r="CU6" t="s">
         <v>58</v>
       </c>
-      <c r="CE6" t="s">
+      <c r="CV6" t="s">
         <v>58</v>
       </c>
-      <c r="CF6" t="s">
+      <c r="CW6" t="s">
         <v>58</v>
       </c>
-      <c r="CG6" t="s">
+      <c r="CX6" t="s">
         <v>58</v>
-      </c>
-      <c r="CH6" t="s">
-        <v>59</v>
-      </c>
-      <c r="CI6" t="s">
-        <v>59</v>
-      </c>
-      <c r="CJ6" t="s">
-        <v>59</v>
-      </c>
-      <c r="CK6" t="s">
-        <v>59</v>
-      </c>
-      <c r="CL6" t="s">
-        <v>59</v>
-      </c>
-      <c r="CM6" t="s">
-        <v>59</v>
-      </c>
-      <c r="CN6" t="s">
-        <v>59</v>
-      </c>
-      <c r="CO6" t="s">
-        <v>60</v>
-      </c>
-      <c r="CP6" t="s">
-        <v>61</v>
-      </c>
-      <c r="CQ6" t="s">
-        <v>61</v>
-      </c>
-      <c r="CR6" t="s">
-        <v>62</v>
-      </c>
-      <c r="CS6" t="s">
-        <v>62</v>
-      </c>
-      <c r="CT6" t="s">
-        <v>59</v>
-      </c>
-      <c r="CU6" t="s">
-        <v>59</v>
-      </c>
-      <c r="CV6" t="s">
-        <v>59</v>
-      </c>
-      <c r="CW6" t="s">
-        <v>63</v>
-      </c>
-      <c r="CX6" t="s">
-        <v>64</v>
       </c>
       <c r="CY6" t="s">
         <v>59</v>
@@ -5319,1262 +5665,1505 @@
         <v>59</v>
       </c>
       <c r="DB6" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="DC6" t="s">
         <v>59</v>
       </c>
       <c r="DD6" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="DE6" t="s">
         <v>59</v>
       </c>
+      <c r="DF6" t="s">
+        <v>60</v>
+      </c>
       <c r="DG6" t="s">
+        <v>61</v>
+      </c>
+      <c r="DH6" t="s">
+        <v>61</v>
+      </c>
+      <c r="DI6" t="s">
+        <v>62</v>
+      </c>
+      <c r="DJ6" t="s">
+        <v>62</v>
+      </c>
+      <c r="DK6" t="s">
         <v>59</v>
       </c>
-      <c r="DH6" t="s">
+      <c r="DL6" t="s">
+        <v>59</v>
+      </c>
+      <c r="DM6" t="s">
+        <v>59</v>
+      </c>
+      <c r="DN6" t="s">
+        <v>63</v>
+      </c>
+      <c r="DO6" t="s">
+        <v>64</v>
+      </c>
+      <c r="DP6" t="s">
+        <v>59</v>
+      </c>
+      <c r="DQ6" t="s">
+        <v>59</v>
+      </c>
+      <c r="DR6" t="s">
+        <v>59</v>
+      </c>
+      <c r="DS6" t="s">
+        <v>65</v>
+      </c>
+      <c r="DT6" t="s">
+        <v>59</v>
+      </c>
+      <c r="DU6" t="s">
+        <v>66</v>
+      </c>
+      <c r="DV6" t="s">
+        <v>59</v>
+      </c>
+      <c r="DX6" t="s">
+        <v>59</v>
+      </c>
+      <c r="DY6" t="s">
         <v>67</v>
       </c>
-      <c r="DI6" t="s">
+      <c r="DZ6" t="s">
         <v>66</v>
       </c>
-      <c r="DL6" t="s">
+      <c r="EC6" t="s">
         <v>68</v>
       </c>
-      <c r="DM6" t="s">
+      <c r="ED6" t="s">
         <v>69</v>
       </c>
-      <c r="DX6" s="2"/>
-      <c r="DY6" s="2"/>
-      <c r="DZ6" s="2"/>
-      <c r="EA6" s="2"/>
-      <c r="EB6" s="2"/>
-      <c r="EC6" s="2"/>
-      <c r="ED6" s="2"/>
-    </row>
-    <row r="7" spans="1:134" x14ac:dyDescent="0.25">
+      <c r="EO6" s="2"/>
+      <c r="EP6" s="2"/>
+      <c r="EQ6" s="2"/>
+      <c r="ER6" s="2"/>
+      <c r="ES6" s="2"/>
+      <c r="ET6" s="2"/>
+      <c r="EU6" s="2"/>
+    </row>
+    <row r="7" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>70</v>
       </c>
       <c r="B7" s="39"/>
       <c r="C7" t="s">
-        <v>1022</v>
+        <v>1083</v>
       </c>
       <c r="D7" t="s">
-        <v>1018</v>
+        <v>1079</v>
       </c>
       <c r="E7" t="s">
-        <v>1013</v>
+        <v>1076</v>
       </c>
       <c r="F7" t="s">
-        <v>1010</v>
+        <v>1073</v>
       </c>
       <c r="G7" t="s">
-        <v>1006</v>
+        <v>1071</v>
       </c>
       <c r="H7" t="s">
-        <v>1004</v>
+        <v>1065</v>
       </c>
       <c r="I7" t="s">
-        <v>999</v>
+        <v>1059</v>
       </c>
       <c r="J7" t="s">
-        <v>996</v>
+        <v>1056</v>
       </c>
       <c r="K7" t="s">
-        <v>994</v>
+        <v>1053</v>
       </c>
       <c r="L7" t="s">
-        <v>991</v>
+        <v>1050</v>
       </c>
       <c r="M7" t="s">
-        <v>986</v>
+        <v>1047</v>
       </c>
       <c r="N7" t="s">
+        <v>1045</v>
+      </c>
+      <c r="O7" t="s">
+        <v>1040</v>
+      </c>
+      <c r="P7" t="s">
+        <v>1036</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>1035</v>
+      </c>
+      <c r="R7" t="s">
+        <v>1029</v>
+      </c>
+      <c r="S7" t="s">
+        <v>1025</v>
+      </c>
+      <c r="T7" t="s">
+        <v>1021</v>
+      </c>
+      <c r="U7" t="s">
+        <v>1017</v>
+      </c>
+      <c r="V7" t="s">
+        <v>1012</v>
+      </c>
+      <c r="W7" t="s">
+        <v>1009</v>
+      </c>
+      <c r="X7" t="s">
+        <v>1005</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>1003</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>998</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>995</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>993</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>990</v>
+      </c>
+      <c r="AD7" t="s">
         <v>985</v>
       </c>
-      <c r="O7" t="s">
-        <v>982</v>
-      </c>
-      <c r="P7" t="s">
-        <v>979</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>973</v>
-      </c>
-      <c r="R7" t="s">
-        <v>970</v>
-      </c>
-      <c r="S7" t="s">
+      <c r="AE7" t="s">
+        <v>984</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>981</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>978</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>972</v>
+      </c>
+      <c r="AI7" t="s">
         <v>969</v>
       </c>
-      <c r="T7" t="s">
-        <v>966</v>
-      </c>
-      <c r="U7" t="s">
-        <v>959</v>
-      </c>
-      <c r="V7" t="s">
+      <c r="AJ7" t="s">
+        <v>968</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>965</v>
+      </c>
+      <c r="AL7" t="s">
         <v>958</v>
       </c>
-      <c r="W7" t="s">
-        <v>954</v>
-      </c>
-      <c r="X7" t="s">
-        <v>951</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>949</v>
-      </c>
-      <c r="Z7" t="s">
+      <c r="AM7" t="s">
+        <v>957</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>953</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>950</v>
+      </c>
+      <c r="AP7" t="s">
         <v>948</v>
       </c>
-      <c r="AA7" t="s">
-        <v>942</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>939</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>935</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>932</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>928</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>924</v>
-      </c>
-      <c r="AG7" t="s">
+      <c r="AQ7" t="s">
+        <v>947</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>941</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>938</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>934</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>931</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>927</v>
+      </c>
+      <c r="AW7" t="s">
         <v>923</v>
       </c>
-      <c r="AH7" t="s">
-        <v>918</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>914</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>911</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>908</v>
-      </c>
-      <c r="AL7" t="s">
-        <v>904</v>
-      </c>
-      <c r="AM7" t="s">
-        <v>901</v>
-      </c>
-      <c r="AN7" t="s">
-        <v>898</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>892</v>
-      </c>
-      <c r="AP7" t="s">
-        <v>880</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>875</v>
-      </c>
-      <c r="AR7" t="s">
-        <v>872</v>
-      </c>
-      <c r="AS7" t="s">
-        <v>852</v>
-      </c>
-      <c r="AT7" t="s">
-        <v>848</v>
-      </c>
-      <c r="AU7" t="s">
-        <v>840</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>837</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>833</v>
-      </c>
       <c r="AX7" t="s">
-        <v>831</v>
+        <v>922</v>
       </c>
       <c r="AY7" t="s">
-        <v>826</v>
+        <v>917</v>
       </c>
       <c r="AZ7" t="s">
-        <v>824</v>
+        <v>913</v>
       </c>
       <c r="BA7" t="s">
-        <v>822</v>
+        <v>910</v>
       </c>
       <c r="BB7" t="s">
-        <v>820</v>
+        <v>907</v>
       </c>
       <c r="BC7" t="s">
-        <v>817</v>
+        <v>903</v>
       </c>
       <c r="BD7" t="s">
-        <v>814</v>
+        <v>900</v>
       </c>
       <c r="BE7" t="s">
-        <v>811</v>
+        <v>897</v>
       </c>
       <c r="BF7" t="s">
-        <v>807</v>
+        <v>891</v>
       </c>
       <c r="BG7" t="s">
+        <v>879</v>
+      </c>
+      <c r="BH7" t="s">
+        <v>874</v>
+      </c>
+      <c r="BI7" t="s">
+        <v>871</v>
+      </c>
+      <c r="BJ7" t="s">
+        <v>851</v>
+      </c>
+      <c r="BK7" t="s">
+        <v>847</v>
+      </c>
+      <c r="BL7" t="s">
+        <v>839</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>836</v>
+      </c>
+      <c r="BN7" t="s">
+        <v>832</v>
+      </c>
+      <c r="BO7" t="s">
+        <v>830</v>
+      </c>
+      <c r="BP7" t="s">
+        <v>825</v>
+      </c>
+      <c r="BQ7" t="s">
+        <v>823</v>
+      </c>
+      <c r="BR7" t="s">
+        <v>821</v>
+      </c>
+      <c r="BS7" t="s">
+        <v>819</v>
+      </c>
+      <c r="BT7" t="s">
+        <v>816</v>
+      </c>
+      <c r="BU7" t="s">
+        <v>813</v>
+      </c>
+      <c r="BV7" t="s">
+        <v>810</v>
+      </c>
+      <c r="BW7" t="s">
         <v>806</v>
       </c>
-      <c r="BH7" t="s">
-        <v>801</v>
-      </c>
-      <c r="BI7" t="s">
-        <v>798</v>
-      </c>
-      <c r="BJ7" t="s">
-        <v>795</v>
-      </c>
-      <c r="BK7" t="s">
-        <v>792</v>
-      </c>
-      <c r="BL7" t="s">
-        <v>788</v>
-      </c>
-      <c r="BM7" t="s">
-        <v>786</v>
-      </c>
-      <c r="BN7" t="s">
-        <v>783</v>
-      </c>
-      <c r="BO7" t="s">
-        <v>779</v>
-      </c>
-      <c r="BP7" t="s">
-        <v>775</v>
-      </c>
-      <c r="BQ7" t="s">
+      <c r="BX7" t="s">
+        <v>805</v>
+      </c>
+      <c r="BY7" t="s">
+        <v>800</v>
+      </c>
+      <c r="BZ7" t="s">
+        <v>797</v>
+      </c>
+      <c r="CA7" t="s">
+        <v>794</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>791</v>
+      </c>
+      <c r="CC7" t="s">
+        <v>787</v>
+      </c>
+      <c r="CD7" t="s">
+        <v>785</v>
+      </c>
+      <c r="CE7" t="s">
+        <v>782</v>
+      </c>
+      <c r="CF7" t="s">
+        <v>778</v>
+      </c>
+      <c r="CG7" t="s">
         <v>774</v>
       </c>
-      <c r="BR7" t="s">
-        <v>769</v>
-      </c>
-      <c r="BS7" t="s">
+      <c r="CH7" t="s">
+        <v>773</v>
+      </c>
+      <c r="CI7" t="s">
         <v>768</v>
       </c>
-      <c r="BT7" t="s">
-        <v>764</v>
-      </c>
-      <c r="BU7" t="s">
+      <c r="CJ7" t="s">
+        <v>767</v>
+      </c>
+      <c r="CK7" t="s">
+        <v>763</v>
+      </c>
+      <c r="CL7" t="s">
         <v>753</v>
       </c>
-      <c r="BV7" t="s">
+      <c r="CM7" t="s">
         <v>748</v>
       </c>
-      <c r="BW7" t="s">
+      <c r="CN7" t="s">
         <v>745</v>
       </c>
-      <c r="BX7" t="s">
+      <c r="CO7" t="s">
         <v>735</v>
       </c>
-      <c r="BY7" t="s">
+      <c r="CP7" t="s">
         <v>732</v>
       </c>
-      <c r="BZ7" t="s">
+      <c r="CQ7" t="s">
         <v>724</v>
       </c>
-      <c r="CA7" t="s">
+      <c r="CR7" t="s">
         <v>656</v>
       </c>
-      <c r="CB7" t="s">
+      <c r="CS7" t="s">
         <v>649</v>
       </c>
-      <c r="CC7" t="s">
+      <c r="CT7" t="s">
         <v>645</v>
       </c>
-      <c r="CD7" t="s">
+      <c r="CU7" t="s">
         <v>651</v>
       </c>
-      <c r="CE7" t="s">
+      <c r="CV7" t="s">
         <v>71</v>
       </c>
-      <c r="CF7" t="s">
+      <c r="CW7" t="s">
         <v>72</v>
       </c>
-      <c r="CG7" t="s">
+      <c r="CX7" t="s">
         <v>73</v>
       </c>
-      <c r="CH7" t="s">
-        <v>760</v>
-      </c>
-      <c r="CI7" t="s">
+      <c r="CY7" t="s">
+        <v>759</v>
+      </c>
+      <c r="CZ7" t="s">
         <v>74</v>
       </c>
-      <c r="CJ7" t="s">
+      <c r="DA7" t="s">
         <v>75</v>
       </c>
-      <c r="CK7" t="s">
+      <c r="DB7" t="s">
         <v>76</v>
       </c>
-      <c r="CL7" t="s">
+      <c r="DC7" t="s">
         <v>77</v>
       </c>
-      <c r="CM7" t="s">
+      <c r="DD7" t="s">
         <v>78</v>
       </c>
-      <c r="CN7" t="s">
+      <c r="DE7" t="s">
         <v>79</v>
       </c>
-      <c r="CO7" t="s">
+      <c r="DF7" t="s">
         <v>80</v>
       </c>
-      <c r="CP7" t="s">
+      <c r="DG7" t="s">
         <v>81</v>
       </c>
-      <c r="CQ7" t="s">
+      <c r="DH7" t="s">
         <v>82</v>
       </c>
-      <c r="CR7" t="s">
+      <c r="DI7" t="s">
         <v>83</v>
       </c>
-      <c r="CS7" t="s">
+      <c r="DJ7" t="s">
         <v>84</v>
       </c>
-      <c r="CT7" t="s">
+      <c r="DK7" t="s">
         <v>85</v>
       </c>
-      <c r="CU7" t="s">
+      <c r="DL7" t="s">
         <v>86</v>
       </c>
-      <c r="CV7" t="s">
+      <c r="DM7" t="s">
         <v>87</v>
       </c>
-      <c r="CW7" t="s">
+      <c r="DN7" t="s">
         <v>88</v>
       </c>
-      <c r="CX7" t="s">
+      <c r="DO7" t="s">
         <v>89</v>
       </c>
-      <c r="CY7" t="s">
+      <c r="DP7" t="s">
         <v>740</v>
       </c>
-      <c r="CZ7" t="s">
+      <c r="DQ7" t="s">
         <v>90</v>
       </c>
-      <c r="DA7" t="s">
+      <c r="DR7" t="s">
         <v>91</v>
       </c>
-      <c r="DB7" t="s">
+      <c r="DS7" t="s">
         <v>92</v>
       </c>
-      <c r="DC7" t="s">
+      <c r="DT7" t="s">
         <v>93</v>
       </c>
-      <c r="DD7" t="s">
+      <c r="DU7" t="s">
         <v>94</v>
       </c>
-      <c r="DE7" t="s">
+      <c r="DV7" t="s">
         <v>95</v>
       </c>
-      <c r="DF7" t="s">
+      <c r="DW7" t="s">
         <v>96</v>
       </c>
-      <c r="DG7" t="s">
+      <c r="DX7" t="s">
         <v>97</v>
       </c>
-      <c r="DH7" t="s">
+      <c r="DY7" t="s">
         <v>98</v>
       </c>
-      <c r="DI7" t="s">
+      <c r="DZ7" t="s">
         <v>99</v>
       </c>
-      <c r="DJ7" t="s">
+      <c r="EA7" t="s">
         <v>100</v>
       </c>
-      <c r="DK7" t="s">
+      <c r="EB7" t="s">
         <v>101</v>
       </c>
-      <c r="DL7" t="s">
+      <c r="EC7" t="s">
         <v>102</v>
       </c>
-      <c r="DM7" t="s">
+      <c r="ED7" t="s">
         <v>103</v>
       </c>
-      <c r="DN7" t="s">
+      <c r="EE7" t="s">
         <v>104</v>
       </c>
-      <c r="DO7" t="s">
+      <c r="EF7" t="s">
         <v>104</v>
       </c>
-      <c r="DP7" t="s">
+      <c r="EG7" t="s">
         <v>105</v>
       </c>
-      <c r="DQ7" t="s">
+      <c r="EH7" t="s">
         <v>106</v>
       </c>
-      <c r="DR7" t="s">
+      <c r="EI7" t="s">
         <v>107</v>
       </c>
-      <c r="DS7" t="s">
+      <c r="EJ7" t="s">
         <v>108</v>
       </c>
-      <c r="DT7" t="s">
+      <c r="EK7" t="s">
         <v>109</v>
       </c>
-      <c r="DU7" t="s">
+      <c r="EL7" t="s">
         <v>110</v>
       </c>
-      <c r="DV7" t="s">
+      <c r="EM7" t="s">
         <v>111</v>
       </c>
-      <c r="DW7" t="s">
+      <c r="EN7" t="s">
         <v>112</v>
       </c>
-      <c r="DX7" t="s">
+      <c r="EO7" t="s">
         <v>113</v>
       </c>
-      <c r="DY7" t="s">
+      <c r="EP7" t="s">
         <v>114</v>
       </c>
-      <c r="DZ7" t="s">
+      <c r="EQ7" t="s">
         <v>115</v>
       </c>
-      <c r="EA7" t="s">
+      <c r="ER7" t="s">
         <v>116</v>
       </c>
-      <c r="EB7" t="s">
+      <c r="ES7" t="s">
         <v>117</v>
       </c>
-      <c r="EC7" t="s">
+      <c r="ET7" t="s">
         <v>118</v>
       </c>
-      <c r="ED7" t="s">
+      <c r="EU7" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="8" spans="1:134" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>120</v>
       </c>
       <c r="B8" s="39"/>
       <c r="C8" t="s">
-        <v>1024</v>
+        <v>1084</v>
       </c>
       <c r="D8" t="s">
-        <v>1020</v>
+        <v>1080</v>
       </c>
       <c r="E8" t="s">
-        <v>1016</v>
+        <v>1077</v>
       </c>
       <c r="F8" t="s">
-        <v>1011</v>
+        <v>1074</v>
       </c>
       <c r="G8" t="s">
-        <v>1007</v>
+        <v>1069</v>
       </c>
       <c r="H8" t="s">
-        <v>1002</v>
+        <v>1066</v>
       </c>
       <c r="I8" t="s">
-        <v>998</v>
+        <v>1061</v>
       </c>
       <c r="J8" t="s">
+        <v>1057</v>
+      </c>
+      <c r="K8" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L8" t="s">
+        <v>1051</v>
+      </c>
+      <c r="M8" t="s">
+        <v>1048</v>
+      </c>
+      <c r="N8" t="s">
+        <v>1044</v>
+      </c>
+      <c r="O8" t="s">
+        <v>1041</v>
+      </c>
+      <c r="P8" t="s">
+        <v>1037</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>1033</v>
+      </c>
+      <c r="R8" t="s">
+        <v>1031</v>
+      </c>
+      <c r="S8" t="s">
+        <v>1026</v>
+      </c>
+      <c r="T8" t="s">
+        <v>1023</v>
+      </c>
+      <c r="U8" t="s">
+        <v>1019</v>
+      </c>
+      <c r="V8" t="s">
+        <v>1015</v>
+      </c>
+      <c r="W8" t="s">
+        <v>1010</v>
+      </c>
+      <c r="X8" t="s">
+        <v>1006</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>1001</v>
+      </c>
+      <c r="Z8" t="s">
         <v>997</v>
       </c>
-      <c r="K8" t="s">
-        <v>992</v>
-      </c>
-      <c r="L8" t="s">
-        <v>989</v>
-      </c>
-      <c r="M8" t="s">
-        <v>987</v>
-      </c>
-      <c r="N8" t="s">
-        <v>983</v>
-      </c>
-      <c r="O8" t="s">
-        <v>981</v>
-      </c>
-      <c r="P8" t="s">
-        <v>978</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>975</v>
-      </c>
-      <c r="R8" t="s">
-        <v>971</v>
-      </c>
-      <c r="S8" t="s">
-        <v>967</v>
-      </c>
-      <c r="T8" t="s">
-        <v>964</v>
-      </c>
-      <c r="U8" t="s">
-        <v>962</v>
-      </c>
-      <c r="V8" t="s">
-        <v>957</v>
-      </c>
-      <c r="W8" t="s">
-        <v>955</v>
-      </c>
-      <c r="X8" t="s">
-        <v>952</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>950</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>947</v>
-      </c>
       <c r="AA8" t="s">
-        <v>943</v>
+        <v>996</v>
       </c>
       <c r="AB8" t="s">
-        <v>941</v>
+        <v>991</v>
       </c>
       <c r="AC8" t="s">
-        <v>936</v>
+        <v>988</v>
       </c>
       <c r="AD8" t="s">
-        <v>933</v>
+        <v>986</v>
       </c>
       <c r="AE8" t="s">
-        <v>931</v>
+        <v>982</v>
       </c>
       <c r="AF8" t="s">
-        <v>926</v>
+        <v>980</v>
       </c>
       <c r="AG8" t="s">
-        <v>922</v>
+        <v>977</v>
       </c>
       <c r="AH8" t="s">
-        <v>920</v>
+        <v>974</v>
       </c>
       <c r="AI8" t="s">
-        <v>915</v>
+        <v>970</v>
       </c>
       <c r="AJ8" t="s">
-        <v>913</v>
+        <v>966</v>
       </c>
       <c r="AK8" t="s">
-        <v>910</v>
+        <v>963</v>
       </c>
       <c r="AL8" t="s">
-        <v>906</v>
+        <v>961</v>
       </c>
       <c r="AM8" t="s">
-        <v>903</v>
+        <v>956</v>
       </c>
       <c r="AN8" t="s">
-        <v>897</v>
+        <v>954</v>
       </c>
       <c r="AO8" t="s">
-        <v>893</v>
+        <v>951</v>
       </c>
       <c r="AP8" t="s">
-        <v>879</v>
+        <v>949</v>
       </c>
       <c r="AQ8" t="s">
-        <v>876</v>
+        <v>946</v>
       </c>
       <c r="AR8" t="s">
-        <v>874</v>
+        <v>942</v>
       </c>
       <c r="AS8" t="s">
-        <v>853</v>
+        <v>940</v>
       </c>
       <c r="AT8" t="s">
-        <v>850</v>
+        <v>935</v>
       </c>
       <c r="AU8" t="s">
-        <v>841</v>
+        <v>932</v>
       </c>
       <c r="AV8" t="s">
-        <v>838</v>
+        <v>930</v>
       </c>
       <c r="AW8" t="s">
-        <v>834</v>
+        <v>925</v>
       </c>
       <c r="AX8" t="s">
-        <v>832</v>
+        <v>921</v>
       </c>
       <c r="AY8" t="s">
-        <v>827</v>
+        <v>919</v>
       </c>
       <c r="AZ8" t="s">
-        <v>825</v>
+        <v>914</v>
       </c>
       <c r="BA8" t="s">
-        <v>823</v>
+        <v>912</v>
       </c>
       <c r="BB8" t="s">
-        <v>821</v>
+        <v>909</v>
       </c>
       <c r="BC8" t="s">
-        <v>816</v>
+        <v>905</v>
       </c>
       <c r="BD8" t="s">
-        <v>813</v>
+        <v>902</v>
       </c>
       <c r="BE8" t="s">
-        <v>810</v>
+        <v>896</v>
       </c>
       <c r="BF8" t="s">
-        <v>808</v>
+        <v>892</v>
       </c>
       <c r="BG8" t="s">
-        <v>805</v>
+        <v>878</v>
       </c>
       <c r="BH8" t="s">
-        <v>802</v>
+        <v>875</v>
       </c>
       <c r="BI8" t="s">
-        <v>797</v>
+        <v>873</v>
       </c>
       <c r="BJ8" t="s">
-        <v>794</v>
+        <v>852</v>
       </c>
       <c r="BK8" t="s">
-        <v>791</v>
+        <v>849</v>
       </c>
       <c r="BL8" t="s">
-        <v>789</v>
+        <v>840</v>
       </c>
       <c r="BM8" t="s">
-        <v>785</v>
+        <v>837</v>
       </c>
       <c r="BN8" t="s">
-        <v>781</v>
+        <v>833</v>
       </c>
       <c r="BO8" t="s">
+        <v>831</v>
+      </c>
+      <c r="BP8" t="s">
+        <v>826</v>
+      </c>
+      <c r="BQ8" t="s">
+        <v>824</v>
+      </c>
+      <c r="BR8" t="s">
+        <v>822</v>
+      </c>
+      <c r="BS8" t="s">
+        <v>820</v>
+      </c>
+      <c r="BT8" t="s">
+        <v>815</v>
+      </c>
+      <c r="BU8" t="s">
+        <v>812</v>
+      </c>
+      <c r="BV8" t="s">
+        <v>809</v>
+      </c>
+      <c r="BW8" t="s">
+        <v>807</v>
+      </c>
+      <c r="BX8" t="s">
+        <v>804</v>
+      </c>
+      <c r="BY8" t="s">
+        <v>801</v>
+      </c>
+      <c r="BZ8" t="s">
+        <v>796</v>
+      </c>
+      <c r="CA8" t="s">
+        <v>793</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>790</v>
+      </c>
+      <c r="CC8" t="s">
+        <v>788</v>
+      </c>
+      <c r="CD8" t="s">
+        <v>784</v>
+      </c>
+      <c r="CE8" t="s">
         <v>780</v>
       </c>
-      <c r="BP8" t="s">
-        <v>777</v>
-      </c>
-      <c r="BQ8" t="s">
-        <v>773</v>
-      </c>
-      <c r="BR8" t="s">
-        <v>771</v>
-      </c>
-      <c r="BS8" t="s">
-        <v>767</v>
-      </c>
-      <c r="BT8" t="s">
-        <v>765</v>
-      </c>
-      <c r="BU8" t="s">
+      <c r="CF8" t="s">
+        <v>779</v>
+      </c>
+      <c r="CG8" t="s">
+        <v>776</v>
+      </c>
+      <c r="CH8" t="s">
+        <v>772</v>
+      </c>
+      <c r="CI8" t="s">
+        <v>770</v>
+      </c>
+      <c r="CJ8" t="s">
+        <v>766</v>
+      </c>
+      <c r="CK8" t="s">
+        <v>764</v>
+      </c>
+      <c r="CL8" t="s">
         <v>754</v>
       </c>
-      <c r="BV8" t="s">
+      <c r="CM8" t="s">
         <v>749</v>
       </c>
-      <c r="BW8" t="s">
+      <c r="CN8" t="s">
         <v>121</v>
       </c>
-      <c r="BX8" t="s">
+      <c r="CO8" t="s">
         <v>734</v>
       </c>
-      <c r="BY8" t="s">
+      <c r="CP8" t="s">
         <v>730</v>
       </c>
-      <c r="BZ8" t="s">
+      <c r="CQ8" t="s">
         <v>725</v>
       </c>
-      <c r="CA8" t="s">
+      <c r="CR8" t="s">
         <v>657</v>
       </c>
-      <c r="CB8" t="s">
+      <c r="CS8" t="s">
         <v>650</v>
       </c>
-      <c r="CC8" t="s">
+      <c r="CT8" t="s">
         <v>121</v>
       </c>
-      <c r="CD8" t="s">
+      <c r="CU8" t="s">
         <v>652</v>
       </c>
-      <c r="CE8" t="s">
+      <c r="CV8" t="s">
         <v>122</v>
       </c>
-      <c r="CF8" t="s">
+      <c r="CW8" t="s">
         <v>123</v>
       </c>
-      <c r="CG8" t="s">
+      <c r="CX8" t="s">
         <v>124</v>
       </c>
-      <c r="CH8" t="s">
-        <v>761</v>
-      </c>
-      <c r="CI8" t="s">
+      <c r="CY8" t="s">
+        <v>760</v>
+      </c>
+      <c r="CZ8" t="s">
         <v>126</v>
       </c>
-      <c r="CJ8" t="s">
+      <c r="DA8" t="s">
         <v>127</v>
       </c>
-      <c r="CK8" t="s">
+      <c r="DB8" t="s">
         <v>128</v>
       </c>
-      <c r="CL8" t="s">
+      <c r="DC8" t="s">
         <v>125</v>
       </c>
-      <c r="CM8" t="s">
+      <c r="DD8" t="s">
         <v>129</v>
       </c>
-      <c r="CN8" t="s">
+      <c r="DE8" t="s">
         <v>130</v>
       </c>
-      <c r="CO8" t="s">
+      <c r="DF8" t="s">
         <v>131</v>
       </c>
-      <c r="CP8" t="s">
+      <c r="DG8" t="s">
         <v>132</v>
       </c>
-      <c r="CQ8" t="s">
+      <c r="DH8" t="s">
         <v>133</v>
       </c>
-      <c r="CR8" t="s">
+      <c r="DI8" t="s">
         <v>134</v>
       </c>
-      <c r="CS8" t="s">
+      <c r="DJ8" t="s">
         <v>135</v>
       </c>
-      <c r="CT8" t="s">
+      <c r="DK8" t="s">
         <v>136</v>
       </c>
-      <c r="CU8" t="s">
+      <c r="DL8" t="s">
         <v>137</v>
       </c>
-      <c r="CV8" t="s">
+      <c r="DM8" t="s">
         <v>138</v>
       </c>
-      <c r="CW8" t="s">
+      <c r="DN8" t="s">
         <v>139</v>
       </c>
-      <c r="CX8" t="s">
+      <c r="DO8" t="s">
         <v>140</v>
       </c>
-      <c r="CY8" t="s">
+      <c r="DP8" t="s">
         <v>739</v>
       </c>
-      <c r="CZ8" t="s">
+      <c r="DQ8" t="s">
         <v>141</v>
       </c>
-      <c r="DA8" t="s">
+      <c r="DR8" t="s">
         <v>142</v>
       </c>
-      <c r="DB8" t="s">
+      <c r="DS8" t="s">
         <v>143</v>
       </c>
-      <c r="DC8" t="s">
+      <c r="DT8" t="s">
         <v>144</v>
       </c>
-      <c r="DD8" t="s">
+      <c r="DU8" t="s">
         <v>145</v>
       </c>
-      <c r="DE8" t="s">
+      <c r="DV8" t="s">
         <v>146</v>
       </c>
-      <c r="DF8" t="s">
+      <c r="DW8" t="s">
         <v>147</v>
       </c>
-      <c r="DG8" t="s">
+      <c r="DX8" t="s">
         <v>148</v>
       </c>
-      <c r="DH8" t="s">
+      <c r="DY8" t="s">
         <v>149</v>
       </c>
-      <c r="DI8" t="s">
+      <c r="DZ8" t="s">
         <v>150</v>
       </c>
-      <c r="DJ8" t="s">
+      <c r="EA8" t="s">
         <v>151</v>
       </c>
-      <c r="DK8" t="s">
+      <c r="EB8" t="s">
         <v>152</v>
       </c>
-      <c r="DL8" t="s">
+      <c r="EC8" t="s">
         <v>153</v>
       </c>
-      <c r="DM8" t="s">
+      <c r="ED8" t="s">
         <v>154</v>
       </c>
-      <c r="DN8" t="s">
+      <c r="EE8" t="s">
         <v>155</v>
       </c>
-      <c r="DO8" t="s">
+      <c r="EF8" t="s">
         <v>156</v>
       </c>
-      <c r="DP8" t="s">
+      <c r="EG8" t="s">
         <v>157</v>
       </c>
-      <c r="DQ8" t="s">
+      <c r="EH8" t="s">
         <v>158</v>
       </c>
-      <c r="DR8" t="s">
+      <c r="EI8" t="s">
         <v>159</v>
       </c>
-      <c r="DS8" t="s">
+      <c r="EJ8" t="s">
         <v>160</v>
       </c>
-      <c r="DT8" t="s">
+      <c r="EK8" t="s">
         <v>161</v>
       </c>
-      <c r="DU8" t="s">
+      <c r="EL8" t="s">
         <v>162</v>
       </c>
-      <c r="DV8" t="s">
+      <c r="EM8" t="s">
         <v>163</v>
       </c>
-      <c r="DW8" t="s">
+      <c r="EN8" t="s">
         <v>164</v>
       </c>
-      <c r="DX8" t="s">
+      <c r="EO8" t="s">
         <v>165</v>
       </c>
-      <c r="DY8" t="s">
+      <c r="EP8" t="s">
         <v>166</v>
       </c>
-      <c r="DZ8" t="s">
+      <c r="EQ8" t="s">
         <v>167</v>
       </c>
-      <c r="EA8" t="s">
+      <c r="ER8" t="s">
         <v>168</v>
       </c>
-      <c r="EB8" t="s">
+      <c r="ES8" t="s">
         <v>169</v>
       </c>
-      <c r="EC8" t="s">
+      <c r="ET8" t="s">
         <v>170</v>
       </c>
-      <c r="ED8" t="s">
+      <c r="EU8" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="9" spans="1:134" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>172</v>
       </c>
       <c r="B9" s="39"/>
-      <c r="AY9" t="s">
-        <v>829</v>
-      </c>
-      <c r="CD9" t="s">
+      <c r="C9"/>
+      <c r="D9"/>
+      <c r="E9"/>
+      <c r="F9"/>
+      <c r="G9" t="s">
+        <v>1070</v>
+      </c>
+      <c r="BP9" t="s">
+        <v>828</v>
+      </c>
+      <c r="CU9" t="s">
         <v>653</v>
       </c>
-      <c r="CE9" t="s">
+      <c r="CV9" t="s">
         <v>173</v>
       </c>
-      <c r="CH9" t="s">
-        <v>762</v>
-      </c>
-      <c r="CI9" t="s">
+      <c r="CY9" t="s">
+        <v>761</v>
+      </c>
+      <c r="CZ9" t="s">
         <v>175</v>
       </c>
-      <c r="CJ9" t="s">
+      <c r="DA9" t="s">
         <v>176</v>
       </c>
-      <c r="CK9" t="s">
+      <c r="DB9" t="s">
         <v>177</v>
       </c>
-      <c r="CL9" t="s">
+      <c r="DC9" t="s">
         <v>174</v>
       </c>
-      <c r="CM9" t="s">
+      <c r="DD9" t="s">
         <v>178</v>
       </c>
-      <c r="CN9" t="s">
+      <c r="DE9" t="s">
         <v>178</v>
       </c>
-      <c r="CP9" t="s">
+      <c r="DG9" t="s">
         <v>179</v>
       </c>
-      <c r="CQ9" t="s">
+      <c r="DH9" t="s">
         <v>180</v>
       </c>
-      <c r="CS9" t="s">
+      <c r="DJ9" t="s">
         <v>181</v>
       </c>
-      <c r="CU9" t="s">
+      <c r="DL9" t="s">
         <v>182</v>
       </c>
-      <c r="CV9" t="s">
+      <c r="DM9" t="s">
         <v>183</v>
       </c>
-      <c r="CY9" t="s">
+      <c r="DP9" t="s">
         <v>741</v>
       </c>
-      <c r="DA9" t="s">
+      <c r="DR9" t="s">
         <v>184</v>
       </c>
-      <c r="DC9" t="s">
+      <c r="DT9" t="s">
         <v>185</v>
       </c>
-      <c r="DG9" t="s">
+      <c r="DX9" t="s">
         <v>186</v>
       </c>
-      <c r="DN9" t="s">
+      <c r="EE9" t="s">
         <v>187</v>
       </c>
-      <c r="DO9" t="s">
+      <c r="EF9" t="s">
         <v>187</v>
       </c>
-      <c r="DQ9" t="s">
+      <c r="EH9" t="s">
         <v>188</v>
       </c>
-      <c r="DT9" t="s">
+      <c r="EK9" t="s">
         <v>189</v>
       </c>
-      <c r="DV9" t="s">
+      <c r="EM9" t="s">
         <v>190</v>
       </c>
-      <c r="DW9" t="s">
+      <c r="EN9" t="s">
         <v>191</v>
       </c>
-      <c r="DZ9" t="s">
+      <c r="EQ9" t="s">
         <v>192</v>
       </c>
-      <c r="EC9" t="s">
+      <c r="ET9" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="10" spans="1:134" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>194</v>
       </c>
       <c r="B10" s="39"/>
-      <c r="CT10" t="s">
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="DK10" t="s">
         <v>195</v>
       </c>
-      <c r="CW10" t="s">
+      <c r="DN10" t="s">
         <v>196</v>
       </c>
-      <c r="DC10" t="s">
+      <c r="DT10" t="s">
         <v>197</v>
       </c>
-      <c r="DN10" t="s">
+      <c r="EE10" t="s">
         <v>198</v>
       </c>
-      <c r="DO10" t="s">
+      <c r="EF10" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="11" spans="1:134" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>199</v>
       </c>
       <c r="B11" s="39"/>
-      <c r="CY11" t="s">
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="DP11" t="s">
         <v>742</v>
       </c>
-      <c r="DA11" t="s">
+      <c r="DR11" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="12" spans="1:134" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B12" s="39"/>
       <c r="C12" t="s">
-        <v>1023</v>
+        <v>1085</v>
       </c>
       <c r="D12" t="s">
-        <v>1019</v>
+        <v>1081</v>
       </c>
       <c r="E12" t="s">
-        <v>1015</v>
+        <v>1078</v>
       </c>
       <c r="F12" t="s">
-        <v>1012</v>
-      </c>
-      <c r="G12" t="s">
-        <v>1008</v>
+        <v>1075</v>
       </c>
       <c r="H12" t="s">
-        <v>1003</v>
+        <v>1067</v>
       </c>
       <c r="I12" t="s">
-        <v>1000</v>
+        <v>1062</v>
       </c>
       <c r="K12" t="s">
-        <v>993</v>
+        <v>1054</v>
       </c>
       <c r="L12" t="s">
-        <v>990</v>
+        <v>1052</v>
       </c>
       <c r="M12" t="s">
-        <v>988</v>
+        <v>1049</v>
       </c>
       <c r="N12" t="s">
-        <v>984</v>
+        <v>1046</v>
+      </c>
+      <c r="O12" t="s">
+        <v>1042</v>
       </c>
       <c r="P12" t="s">
-        <v>977</v>
+        <v>1038</v>
       </c>
       <c r="Q12" t="s">
-        <v>974</v>
+        <v>1034</v>
       </c>
       <c r="R12" t="s">
-        <v>972</v>
+        <v>1030</v>
       </c>
       <c r="S12" t="s">
-        <v>968</v>
+        <v>1027</v>
       </c>
       <c r="T12" t="s">
-        <v>965</v>
+        <v>1022</v>
       </c>
       <c r="U12" t="s">
-        <v>960</v>
+        <v>1018</v>
       </c>
       <c r="V12" t="s">
-        <v>956</v>
+        <v>1014</v>
       </c>
       <c r="W12" t="s">
-        <v>896</v>
+        <v>1011</v>
       </c>
       <c r="X12" t="s">
-        <v>953</v>
+        <v>1007</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>1002</v>
       </c>
       <c r="Z12" t="s">
-        <v>945</v>
-      </c>
-      <c r="AA12" t="s">
+        <v>999</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>992</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>989</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>987</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>983</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>976</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>973</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>971</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>967</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>964</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>959</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>955</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>895</v>
+      </c>
+      <c r="AO12" t="s">
+        <v>952</v>
+      </c>
+      <c r="AQ12" t="s">
         <v>944</v>
       </c>
-      <c r="AB12" t="s">
-        <v>940</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>937</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>934</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>930</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>925</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>919</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>916</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>912</v>
-      </c>
-      <c r="AK12" t="s">
-        <v>909</v>
-      </c>
-      <c r="AL12" t="s">
-        <v>905</v>
-      </c>
-      <c r="AM12" t="s">
-        <v>902</v>
-      </c>
-      <c r="AN12" t="s">
-        <v>896</v>
-      </c>
-      <c r="AO12" t="s">
-        <v>894</v>
-      </c>
-      <c r="AP12" t="s">
-        <v>878</v>
-      </c>
       <c r="AR12" t="s">
-        <v>873</v>
+        <v>943</v>
       </c>
       <c r="AS12" t="s">
-        <v>869</v>
+        <v>939</v>
+      </c>
+      <c r="AT12" t="s">
+        <v>936</v>
+      </c>
+      <c r="AU12" t="s">
+        <v>933</v>
       </c>
       <c r="AV12" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="13" spans="1:134" x14ac:dyDescent="0.25">
+        <v>929</v>
+      </c>
+      <c r="AW12" t="s">
+        <v>924</v>
+      </c>
+      <c r="AY12" t="s">
+        <v>918</v>
+      </c>
+      <c r="AZ12" t="s">
+        <v>915</v>
+      </c>
+      <c r="BA12" t="s">
+        <v>911</v>
+      </c>
+      <c r="BB12" t="s">
+        <v>908</v>
+      </c>
+      <c r="BC12" t="s">
+        <v>904</v>
+      </c>
+      <c r="BD12" t="s">
+        <v>901</v>
+      </c>
+      <c r="BE12" t="s">
+        <v>895</v>
+      </c>
+      <c r="BF12" t="s">
+        <v>893</v>
+      </c>
+      <c r="BG12" t="s">
+        <v>877</v>
+      </c>
+      <c r="BI12" t="s">
+        <v>872</v>
+      </c>
+      <c r="BJ12" t="s">
+        <v>868</v>
+      </c>
+      <c r="BM12" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="13" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>201</v>
       </c>
       <c r="B13" s="39"/>
-      <c r="P13" t="s">
-        <v>976</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>929</v>
-      </c>
-      <c r="AT13" t="s">
-        <v>849</v>
-      </c>
-      <c r="AY13" t="s">
-        <v>828</v>
-      </c>
-      <c r="BC13" t="s">
-        <v>818</v>
-      </c>
-      <c r="BH13" t="s">
-        <v>803</v>
-      </c>
-      <c r="BI13" t="s">
-        <v>799</v>
-      </c>
-      <c r="CP13" t="s">
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="I13" t="s">
+        <v>1063</v>
+      </c>
+      <c r="N13" t="s">
+        <v>1043</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>975</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>928</v>
+      </c>
+      <c r="BK13" t="s">
+        <v>848</v>
+      </c>
+      <c r="BP13" t="s">
+        <v>827</v>
+      </c>
+      <c r="BT13" t="s">
+        <v>817</v>
+      </c>
+      <c r="BY13" t="s">
+        <v>802</v>
+      </c>
+      <c r="BZ13" t="s">
+        <v>798</v>
+      </c>
+      <c r="DG13" t="s">
         <v>202</v>
       </c>
-      <c r="CQ13" t="s">
+      <c r="DH13" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="14" spans="1:134" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>204</v>
       </c>
       <c r="B14" s="39"/>
-    </row>
-    <row r="15" spans="1:134" x14ac:dyDescent="0.25">
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14"/>
+    </row>
+    <row r="15" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>751</v>
       </c>
       <c r="B15" s="39"/>
-    </row>
-    <row r="16" spans="1:134" x14ac:dyDescent="0.25">
+      <c r="C15"/>
+      <c r="D15"/>
+      <c r="E15"/>
+      <c r="F15"/>
+    </row>
+    <row r="16" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>752</v>
       </c>
       <c r="B16" s="39"/>
-    </row>
-    <row r="17" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="C16"/>
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16"/>
+    </row>
+    <row r="17" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>205</v>
       </c>
       <c r="B17" s="39"/>
-    </row>
-    <row r="18" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="C17"/>
+      <c r="D17"/>
+      <c r="E17"/>
+      <c r="F17"/>
+    </row>
+    <row r="18" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>206</v>
       </c>
       <c r="B18" s="39"/>
-    </row>
-    <row r="19" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="C18"/>
+      <c r="D18"/>
+      <c r="E18"/>
+      <c r="F18"/>
+    </row>
+    <row r="19" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>758</v>
       </c>
       <c r="B19" s="39"/>
       <c r="C19" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="D19" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="E19" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="F19" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="G19" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H19" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="I19" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="J19" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="K19" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="L19" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="M19" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="N19" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="O19" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="P19" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="Q19" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="R19" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="S19" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="T19" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="U19" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="V19" t="s">
-        <v>757</v>
+        <v>960</v>
       </c>
       <c r="W19" t="s">
-        <v>757</v>
+        <v>960</v>
       </c>
       <c r="X19" t="s">
-        <v>757</v>
+        <v>960</v>
       </c>
       <c r="Y19" t="s">
-        <v>757</v>
+        <v>960</v>
       </c>
       <c r="Z19" t="s">
-        <v>757</v>
+        <v>960</v>
       </c>
       <c r="AA19" t="s">
-        <v>757</v>
+        <v>960</v>
       </c>
       <c r="AB19" t="s">
-        <v>757</v>
+        <v>960</v>
       </c>
       <c r="AC19" t="s">
-        <v>757</v>
+        <v>960</v>
       </c>
       <c r="AD19" t="s">
-        <v>757</v>
+        <v>960</v>
       </c>
       <c r="AE19" t="s">
-        <v>757</v>
+        <v>960</v>
       </c>
       <c r="AF19" t="s">
-        <v>757</v>
+        <v>960</v>
       </c>
       <c r="AG19" t="s">
-        <v>757</v>
+        <v>960</v>
       </c>
       <c r="AH19" t="s">
-        <v>757</v>
+        <v>960</v>
       </c>
       <c r="AI19" t="s">
-        <v>757</v>
+        <v>960</v>
       </c>
       <c r="AJ19" t="s">
-        <v>757</v>
+        <v>960</v>
       </c>
       <c r="AK19" t="s">
-        <v>757</v>
+        <v>960</v>
       </c>
       <c r="AL19" t="s">
-        <v>757</v>
+        <v>960</v>
       </c>
       <c r="AM19" t="s">
         <v>757</v>
@@ -6595,7 +7184,7 @@
         <v>757</v>
       </c>
       <c r="AS19" t="s">
-        <v>961</v>
+        <v>757</v>
       </c>
       <c r="AT19" t="s">
         <v>757</v>
@@ -6646,11 +7235,20 @@
         <v>757</v>
       </c>
       <c r="BJ19" t="s">
-        <v>757</v>
+        <v>960</v>
       </c>
       <c r="BK19" t="s">
         <v>757</v>
       </c>
+      <c r="BL19" t="s">
+        <v>757</v>
+      </c>
+      <c r="BM19" t="s">
+        <v>757</v>
+      </c>
+      <c r="BN19" t="s">
+        <v>757</v>
+      </c>
       <c r="BO19" t="s">
         <v>757</v>
       </c>
@@ -6670,106 +7268,165 @@
         <v>757</v>
       </c>
       <c r="BU19" t="s">
+        <v>757</v>
+      </c>
+      <c r="BV19" t="s">
+        <v>757</v>
+      </c>
+      <c r="BW19" t="s">
+        <v>757</v>
+      </c>
+      <c r="BX19" t="s">
+        <v>757</v>
+      </c>
+      <c r="BY19" t="s">
+        <v>757</v>
+      </c>
+      <c r="BZ19" t="s">
+        <v>757</v>
+      </c>
+      <c r="CA19" t="s">
+        <v>757</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>757</v>
+      </c>
+      <c r="CF19" t="s">
+        <v>757</v>
+      </c>
+      <c r="CG19" t="s">
+        <v>757</v>
+      </c>
+      <c r="CH19" t="s">
+        <v>757</v>
+      </c>
+      <c r="CI19" t="s">
+        <v>757</v>
+      </c>
+      <c r="CJ19" t="s">
+        <v>757</v>
+      </c>
+      <c r="CK19" t="s">
+        <v>757</v>
+      </c>
+      <c r="CL19" t="s">
         <v>757</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="CC1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
-    <hyperlink ref="CD1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
-    <hyperlink ref="CE1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
-    <hyperlink ref="CF1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
-    <hyperlink ref="CG1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
-    <hyperlink ref="CH1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
-    <hyperlink ref="CI1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
-    <hyperlink ref="CJ1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
-    <hyperlink ref="CK1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
-    <hyperlink ref="CL1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
-    <hyperlink ref="CM1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
-    <hyperlink ref="CN1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
-    <hyperlink ref="CO1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
-    <hyperlink ref="CP1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00000F000000}"/>
-    <hyperlink ref="CQ1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
-    <hyperlink ref="CR1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
-    <hyperlink ref="CS1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000012000000}"/>
-    <hyperlink ref="CT1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
-    <hyperlink ref="CU1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
-    <hyperlink ref="CV1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000015000000}"/>
-    <hyperlink ref="CW1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000016000000}"/>
-    <hyperlink ref="CX1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000017000000}"/>
-    <hyperlink ref="CY1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000018000000}"/>
-    <hyperlink ref="CZ1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000019000000}"/>
-    <hyperlink ref="DA1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00001A000000}"/>
-    <hyperlink ref="DB1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00001B000000}"/>
-    <hyperlink ref="DC1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00001C000000}"/>
-    <hyperlink ref="DD1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00001D000000}"/>
-    <hyperlink ref="DE1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00001E000000}"/>
-    <hyperlink ref="DF1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00001F000000}"/>
-    <hyperlink ref="DG1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000020000000}"/>
-    <hyperlink ref="DH1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000021000000}"/>
-    <hyperlink ref="DI1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000022000000}"/>
-    <hyperlink ref="DJ1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000023000000}"/>
-    <hyperlink ref="DK1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000024000000}"/>
-    <hyperlink ref="DL1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000025000000}"/>
-    <hyperlink ref="DM1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000026000000}"/>
-    <hyperlink ref="DN1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000027000000}"/>
-    <hyperlink ref="DO1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000028000000}"/>
-    <hyperlink ref="DP1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000029000000}"/>
-    <hyperlink ref="DQ1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00002A000000}"/>
-    <hyperlink ref="DR1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00002B000000}"/>
-    <hyperlink ref="DS1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00002C000000}"/>
-    <hyperlink ref="DT1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00002D000000}"/>
-    <hyperlink ref="DU1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00002E000000}"/>
-    <hyperlink ref="DV1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00002F000000}"/>
-    <hyperlink ref="DW1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000030000000}"/>
-    <hyperlink ref="DX1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000031000000}"/>
-    <hyperlink ref="DY1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000032000000}"/>
-    <hyperlink ref="DZ1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000033000000}"/>
-    <hyperlink ref="EA1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000034000000}"/>
-    <hyperlink ref="EB1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000035000000}"/>
-    <hyperlink ref="EC1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000036000000}"/>
-    <hyperlink ref="ED1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000037000000}"/>
-    <hyperlink ref="BW1" location="contents!A1" display="Contents" xr:uid="{9D9CCE4A-5CD2-437E-9617-0F93011D53A3}"/>
-    <hyperlink ref="AS1" location="contents!A1" display="Contents" xr:uid="{3FAD3FE0-AB40-48BA-AEC1-65546650B1CF}"/>
-    <hyperlink ref="AR1" location="contents!A1" display="Contents" xr:uid="{32791349-53A4-427C-89DA-522B44F1739E}"/>
-    <hyperlink ref="AQ1" location="contents!A1" display="Contents" xr:uid="{697DBC3F-41A4-491A-9D08-AC96AB820264}"/>
-    <hyperlink ref="AP1" location="contents!A1" display="Contents" xr:uid="{0C6BB241-3937-42F9-A5BE-E1EACB4925BE}"/>
-    <hyperlink ref="AO1" location="contents!A1" display="Contents" xr:uid="{492D207D-CB9D-414A-8B16-8CA6B3AFB43E}"/>
-    <hyperlink ref="AN1" location="contents!A1" display="Contents" xr:uid="{8E27650F-3982-417B-BDD0-B28B6C362E3E}"/>
-    <hyperlink ref="AM1" location="contents!A1" display="Contents" xr:uid="{D75E7FCB-82AB-484B-97D3-66D5DC991F6C}"/>
-    <hyperlink ref="AL1" location="contents!A1" display="Contents" xr:uid="{BBBF3901-8142-49D3-95EA-19294D1C14EC}"/>
-    <hyperlink ref="AK1" location="contents!A1" display="Contents" xr:uid="{EC5DAE0F-8EBD-4CAA-AD9B-E50DC37655E4}"/>
-    <hyperlink ref="AJ1" location="contents!A1" display="Contents" xr:uid="{38D1CC1C-0B91-4B62-AB18-77F6E128C0BB}"/>
-    <hyperlink ref="AI1" location="contents!A1" display="Contents" xr:uid="{C32720F2-8DA3-4812-A554-165E255F238D}"/>
-    <hyperlink ref="AH1" location="contents!A1" display="Contents" xr:uid="{98E99DE4-5804-46E0-9E8B-774DCAFE93D0}"/>
-    <hyperlink ref="AG1" location="contents!A1" display="Contents" xr:uid="{C236F8FA-A1C3-479D-A295-DACDD3CDEDAD}"/>
-    <hyperlink ref="AF1" location="contents!A1" display="Contents" xr:uid="{D34314D4-D308-4397-91C7-B41BE359A27C}"/>
-    <hyperlink ref="AE1" location="contents!A1" display="Contents" xr:uid="{C93881C9-C93F-4607-A253-B00C084D10C4}"/>
-    <hyperlink ref="AD1" location="contents!A1" display="Contents" xr:uid="{A5F8BA6E-44DA-40C6-8D04-FB61815C4842}"/>
-    <hyperlink ref="AC1" location="contents!A1" display="Contents" xr:uid="{C711AA9A-F171-41FA-9793-81C0EA8638A8}"/>
-    <hyperlink ref="AB1" location="contents!A1" display="Contents" xr:uid="{29E4E036-A3A8-4A16-8E35-DF8155227347}"/>
-    <hyperlink ref="AA1" location="contents!A1" display="Contents" xr:uid="{DA6BFB54-CBD0-4DE0-AF6B-84E4C1B0D4C4}"/>
-    <hyperlink ref="Z1" location="contents!A1" display="Contents" xr:uid="{8551A20B-581D-45C7-AD86-C130DBA4647F}"/>
-    <hyperlink ref="Y1" location="contents!A1" display="Contents" xr:uid="{698696C1-6BB2-41E8-8784-DDF8EEB80E8C}"/>
-    <hyperlink ref="W1" location="contents!A1" display="Contents" xr:uid="{56870F7A-0500-4FAF-8398-B13E7F27905A}"/>
-    <hyperlink ref="V1" location="contents!A1" display="Contents" xr:uid="{BDE7C4E1-7C22-4CFB-96E2-4537880BFC18}"/>
-    <hyperlink ref="T1" location="contents!A1" display="Contents" xr:uid="{31B5305D-A644-46B4-B82A-4DE742C5A6DD}"/>
-    <hyperlink ref="S1" location="contents!A1" display="Contents" xr:uid="{E0129CCB-DDF6-4A3F-A1D2-91374B79CBD3}"/>
-    <hyperlink ref="R1" location="contents!A1" display="Contents" xr:uid="{9EC926A8-52ED-4061-95AE-771DFE06BEB6}"/>
-    <hyperlink ref="Q1" location="contents!A1" display="Contents" xr:uid="{EB3805F5-FA8B-4511-B9C1-3CB5483E72F6}"/>
-    <hyperlink ref="P1" location="contents!A1" display="Contents" xr:uid="{7844FC75-64DB-408A-B395-C73FB0D65864}"/>
-    <hyperlink ref="O1" location="contents!A1" display="Contents" xr:uid="{D1E4A0CD-933A-4AA9-B8C6-A0D8BE111BE3}"/>
-    <hyperlink ref="N1" location="contents!A1" display="Contents" xr:uid="{DDA73B89-9899-4392-982F-032F7CCC149D}"/>
-    <hyperlink ref="M1" location="contents!A1" display="Contents" xr:uid="{A9E6137E-279A-4001-906A-C0AA8E7B33AE}"/>
-    <hyperlink ref="L1" location="contents!A1" display="Contents" xr:uid="{1873EE4F-BE3C-45BA-A7A3-C8F78214A04A}"/>
-    <hyperlink ref="I1" location="contents!A1" display="Contents" xr:uid="{908C3AEE-C418-4D1A-AD93-2FE3201711D9}"/>
-    <hyperlink ref="H1" location="contents!A1" display="Contents" xr:uid="{1F8D91A6-14BA-4F5F-A006-601D90206D75}"/>
-    <hyperlink ref="G1" location="contents!A1" display="Contents" xr:uid="{66A7E497-1597-48BF-9ADE-E9CB32023975}"/>
-    <hyperlink ref="F1" location="contents!A1" display="Contents" xr:uid="{8AA7281B-B47A-41B6-9A4B-545337CDA33F}"/>
-    <hyperlink ref="E1" location="contents!A1" display="Contents" xr:uid="{144FDDA1-8D03-4237-8744-ADEF4FF4B900}"/>
-    <hyperlink ref="D1" location="contents!A1" display="Contents" xr:uid="{8DBEE1F7-DCF6-40EA-BC46-1A2F8C077234}"/>
-    <hyperlink ref="C1" location="contents!A1" display="Contents" xr:uid="{53B126D4-7C43-4EBE-BD0C-294C81D133C0}"/>
+    <hyperlink ref="CT1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="CU1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="CV1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="CW1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="CX1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
+    <hyperlink ref="CY1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
+    <hyperlink ref="CZ1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
+    <hyperlink ref="DA1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
+    <hyperlink ref="DB1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
+    <hyperlink ref="DC1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
+    <hyperlink ref="DD1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
+    <hyperlink ref="DE1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
+    <hyperlink ref="DF1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
+    <hyperlink ref="DG1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00000F000000}"/>
+    <hyperlink ref="DH1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
+    <hyperlink ref="DI1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
+    <hyperlink ref="DJ1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000012000000}"/>
+    <hyperlink ref="DK1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
+    <hyperlink ref="DL1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
+    <hyperlink ref="DM1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000015000000}"/>
+    <hyperlink ref="DN1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000016000000}"/>
+    <hyperlink ref="DO1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000017000000}"/>
+    <hyperlink ref="DP1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000018000000}"/>
+    <hyperlink ref="DQ1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000019000000}"/>
+    <hyperlink ref="DR1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00001A000000}"/>
+    <hyperlink ref="DS1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00001B000000}"/>
+    <hyperlink ref="DT1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00001C000000}"/>
+    <hyperlink ref="DU1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00001D000000}"/>
+    <hyperlink ref="DV1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00001E000000}"/>
+    <hyperlink ref="DW1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00001F000000}"/>
+    <hyperlink ref="DX1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000020000000}"/>
+    <hyperlink ref="DY1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000021000000}"/>
+    <hyperlink ref="DZ1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000022000000}"/>
+    <hyperlink ref="EA1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000023000000}"/>
+    <hyperlink ref="EB1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000024000000}"/>
+    <hyperlink ref="EC1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000025000000}"/>
+    <hyperlink ref="ED1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000026000000}"/>
+    <hyperlink ref="EE1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000027000000}"/>
+    <hyperlink ref="EF1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000028000000}"/>
+    <hyperlink ref="EG1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000029000000}"/>
+    <hyperlink ref="EH1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00002A000000}"/>
+    <hyperlink ref="EI1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00002B000000}"/>
+    <hyperlink ref="EJ1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00002C000000}"/>
+    <hyperlink ref="EK1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00002D000000}"/>
+    <hyperlink ref="EL1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00002E000000}"/>
+    <hyperlink ref="EM1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00002F000000}"/>
+    <hyperlink ref="EN1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000030000000}"/>
+    <hyperlink ref="EO1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000031000000}"/>
+    <hyperlink ref="EP1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000032000000}"/>
+    <hyperlink ref="EQ1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000033000000}"/>
+    <hyperlink ref="ER1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000034000000}"/>
+    <hyperlink ref="ES1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000035000000}"/>
+    <hyperlink ref="ET1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000036000000}"/>
+    <hyperlink ref="EU1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000037000000}"/>
+    <hyperlink ref="CN1" location="contents!A1" display="Contents" xr:uid="{9D9CCE4A-5CD2-437E-9617-0F93011D53A3}"/>
+    <hyperlink ref="BJ1" location="contents!A1" display="Contents" xr:uid="{3FAD3FE0-AB40-48BA-AEC1-65546650B1CF}"/>
+    <hyperlink ref="BI1" location="contents!A1" display="Contents" xr:uid="{32791349-53A4-427C-89DA-522B44F1739E}"/>
+    <hyperlink ref="BH1" location="contents!A1" display="Contents" xr:uid="{697DBC3F-41A4-491A-9D08-AC96AB820264}"/>
+    <hyperlink ref="BG1" location="contents!A1" display="Contents" xr:uid="{0C6BB241-3937-42F9-A5BE-E1EACB4925BE}"/>
+    <hyperlink ref="BF1" location="contents!A1" display="Contents" xr:uid="{492D207D-CB9D-414A-8B16-8CA6B3AFB43E}"/>
+    <hyperlink ref="BE1" location="contents!A1" display="Contents" xr:uid="{8E27650F-3982-417B-BDD0-B28B6C362E3E}"/>
+    <hyperlink ref="BD1" location="contents!A1" display="Contents" xr:uid="{D75E7FCB-82AB-484B-97D3-66D5DC991F6C}"/>
+    <hyperlink ref="BC1" location="contents!A1" display="Contents" xr:uid="{BBBF3901-8142-49D3-95EA-19294D1C14EC}"/>
+    <hyperlink ref="BB1" location="contents!A1" display="Contents" xr:uid="{EC5DAE0F-8EBD-4CAA-AD9B-E50DC37655E4}"/>
+    <hyperlink ref="BA1" location="contents!A1" display="Contents" xr:uid="{38D1CC1C-0B91-4B62-AB18-77F6E128C0BB}"/>
+    <hyperlink ref="AZ1" location="contents!A1" display="Contents" xr:uid="{C32720F2-8DA3-4812-A554-165E255F238D}"/>
+    <hyperlink ref="AY1" location="contents!A1" display="Contents" xr:uid="{98E99DE4-5804-46E0-9E8B-774DCAFE93D0}"/>
+    <hyperlink ref="AX1" location="contents!A1" display="Contents" xr:uid="{C236F8FA-A1C3-479D-A295-DACDD3CDEDAD}"/>
+    <hyperlink ref="AW1" location="contents!A1" display="Contents" xr:uid="{D34314D4-D308-4397-91C7-B41BE359A27C}"/>
+    <hyperlink ref="AV1" location="contents!A1" display="Contents" xr:uid="{C93881C9-C93F-4607-A253-B00C084D10C4}"/>
+    <hyperlink ref="AU1" location="contents!A1" display="Contents" xr:uid="{A5F8BA6E-44DA-40C6-8D04-FB61815C4842}"/>
+    <hyperlink ref="AT1" location="contents!A1" display="Contents" xr:uid="{C711AA9A-F171-41FA-9793-81C0EA8638A8}"/>
+    <hyperlink ref="AS1" location="contents!A1" display="Contents" xr:uid="{29E4E036-A3A8-4A16-8E35-DF8155227347}"/>
+    <hyperlink ref="AR1" location="contents!A1" display="Contents" xr:uid="{DA6BFB54-CBD0-4DE0-AF6B-84E4C1B0D4C4}"/>
+    <hyperlink ref="AQ1" location="contents!A1" display="Contents" xr:uid="{8551A20B-581D-45C7-AD86-C130DBA4647F}"/>
+    <hyperlink ref="AP1" location="contents!A1" display="Contents" xr:uid="{698696C1-6BB2-41E8-8784-DDF8EEB80E8C}"/>
+    <hyperlink ref="AN1" location="contents!A1" display="Contents" xr:uid="{56870F7A-0500-4FAF-8398-B13E7F27905A}"/>
+    <hyperlink ref="AM1" location="contents!A1" display="Contents" xr:uid="{BDE7C4E1-7C22-4CFB-96E2-4537880BFC18}"/>
+    <hyperlink ref="AK1" location="contents!A1" display="Contents" xr:uid="{31B5305D-A644-46B4-B82A-4DE742C5A6DD}"/>
+    <hyperlink ref="AJ1" location="contents!A1" display="Contents" xr:uid="{E0129CCB-DDF6-4A3F-A1D2-91374B79CBD3}"/>
+    <hyperlink ref="AI1" location="contents!A1" display="Contents" xr:uid="{9EC926A8-52ED-4061-95AE-771DFE06BEB6}"/>
+    <hyperlink ref="AH1" location="contents!A1" display="Contents" xr:uid="{EB3805F5-FA8B-4511-B9C1-3CB5483E72F6}"/>
+    <hyperlink ref="AG1" location="contents!A1" display="Contents" xr:uid="{7844FC75-64DB-408A-B395-C73FB0D65864}"/>
+    <hyperlink ref="AF1" location="contents!A1" display="Contents" xr:uid="{D1E4A0CD-933A-4AA9-B8C6-A0D8BE111BE3}"/>
+    <hyperlink ref="AE1" location="contents!A1" display="Contents" xr:uid="{DDA73B89-9899-4392-982F-032F7CCC149D}"/>
+    <hyperlink ref="AD1" location="contents!A1" display="Contents" xr:uid="{A9E6137E-279A-4001-906A-C0AA8E7B33AE}"/>
+    <hyperlink ref="AC1" location="contents!A1" display="Contents" xr:uid="{1873EE4F-BE3C-45BA-A7A3-C8F78214A04A}"/>
+    <hyperlink ref="Z1" location="contents!A1" display="Contents" xr:uid="{908C3AEE-C418-4D1A-AD93-2FE3201711D9}"/>
+    <hyperlink ref="Y1" location="contents!A1" display="Contents" xr:uid="{1F8D91A6-14BA-4F5F-A006-601D90206D75}"/>
+    <hyperlink ref="X1" location="contents!A1" display="Contents" xr:uid="{66A7E497-1597-48BF-9ADE-E9CB32023975}"/>
+    <hyperlink ref="W1" location="contents!A1" display="Contents" xr:uid="{8AA7281B-B47A-41B6-9A4B-545337CDA33F}"/>
+    <hyperlink ref="V1" location="contents!A1" display="Contents" xr:uid="{144FDDA1-8D03-4237-8744-ADEF4FF4B900}"/>
+    <hyperlink ref="U1" location="contents!A1" display="Contents" xr:uid="{8DBEE1F7-DCF6-40EA-BC46-1A2F8C077234}"/>
+    <hyperlink ref="T1" location="contents!A1" display="Contents" xr:uid="{53B126D4-7C43-4EBE-BD0C-294C81D133C0}"/>
+    <hyperlink ref="S1" location="contents!A1" display="Contents" xr:uid="{C8B834F2-F90A-485A-819B-3AEB16B4FF49}"/>
+    <hyperlink ref="R1" location="contents!A1" display="Contents" xr:uid="{49FE4B51-07B5-4C50-A999-EE501393B22D}"/>
+    <hyperlink ref="Q1" location="contents!A1" display="Contents" xr:uid="{8FC8ACD2-5EC5-4C34-9A88-B214B5DFC201}"/>
+    <hyperlink ref="P1" location="contents!A1" display="Contents" xr:uid="{BC06316D-019D-494B-B494-20C1629E5614}"/>
+    <hyperlink ref="O1" location="contents!A1" display="Contents" xr:uid="{DEC54F1B-5A35-4242-AB85-D985BB988F9D}"/>
+    <hyperlink ref="N1" location="contents!A1" display="Contents" xr:uid="{D0D03B8A-CB9D-4898-9139-62041F31D6CA}"/>
+    <hyperlink ref="M1" location="contents!A1" display="Contents" xr:uid="{02AFCB5A-4613-4FD2-953D-792104DE4399}"/>
+    <hyperlink ref="L1" location="contents!A1" display="Contents" xr:uid="{F25254D6-D5AC-4A45-AE45-87AB44B1E07A}"/>
+    <hyperlink ref="K1" location="contents!A1" display="Contents" xr:uid="{CD337BA3-E268-4A23-B64A-07199600E796}"/>
+    <hyperlink ref="J1" location="contents!A1" display="Contents" xr:uid="{1A5108E0-AA64-4EBA-9F0D-301EB4FD4E89}"/>
+    <hyperlink ref="I1" location="contents!A1" display="Contents" xr:uid="{42F20267-FF1D-4B3A-A328-0855E66195DB}"/>
+    <hyperlink ref="H1" location="contents!A1" display="Contents" xr:uid="{12E50AB9-5C28-4140-BF75-D7E1067463CA}"/>
+    <hyperlink ref="G1" location="contents!A1" display="Contents" xr:uid="{A3B6F765-B55A-4498-B5A3-C95085FAB9D6}"/>
+    <hyperlink ref="F1" location="contents!A1" display="Contents" xr:uid="{7278A37B-C720-4573-9694-666084FF9300}"/>
+    <hyperlink ref="E1" location="contents!A1" display="Contents" xr:uid="{56D3D477-F6BC-42BE-A397-860B5B9B140B}"/>
+    <hyperlink ref="D1" location="contents!A1" display="Contents" xr:uid="{7C88203E-D4E7-4A89-B535-55F2A9D9DAE9}"/>
+    <hyperlink ref="C1" location="contents!A1" display="Contents" xr:uid="{F982AE8C-A71C-4A96-862F-E907CE672AB9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -7115,16 +7772,16 @@
         <v>221</v>
       </c>
       <c r="F14" s="12" t="s">
+        <v>888</v>
+      </c>
+      <c r="I14" t="s">
+        <v>222</v>
+      </c>
+      <c r="J14" t="s">
+        <v>222</v>
+      </c>
+      <c r="K14" t="s">
         <v>889</v>
-      </c>
-      <c r="I14" t="s">
-        <v>222</v>
-      </c>
-      <c r="J14" t="s">
-        <v>222</v>
-      </c>
-      <c r="K14" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -8338,25 +8995,25 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B57" s="8" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="D57" s="8" t="s">
         <v>221</v>
       </c>
       <c r="F57" s="37" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="I57" t="s">
+        <v>861</v>
+      </c>
+      <c r="J57" t="s">
+        <v>222</v>
+      </c>
+      <c r="K57" t="s">
         <v>862</v>
-      </c>
-      <c r="J57" t="s">
-        <v>222</v>
-      </c>
-      <c r="K57" t="s">
-        <v>863</v>
       </c>
       <c r="O57" t="s">
         <v>222</v>
@@ -8364,16 +9021,16 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B58" s="8" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>221</v>
       </c>
       <c r="F58" s="37" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="I58" t="s">
         <v>222</v>
@@ -8382,7 +9039,7 @@
         <v>222</v>
       </c>
       <c r="K58" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="O58" t="s">
         <v>222</v>
@@ -8390,16 +9047,16 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B59" s="8" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>221</v>
       </c>
       <c r="F59" s="37" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="I59" t="s">
         <v>222</v>
@@ -8408,7 +9065,7 @@
         <v>222</v>
       </c>
       <c r="K59" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="O59" t="s">
         <v>222</v>
@@ -8416,16 +9073,16 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B60" s="8" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="D60" s="8" t="s">
         <v>221</v>
       </c>
       <c r="F60" s="37" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="I60" t="s">
         <v>222</v>
@@ -8434,7 +9091,7 @@
         <v>222</v>
       </c>
       <c r="K60" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="O60" t="s">
         <v>222</v>
@@ -8442,16 +9099,16 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B61" s="8" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="D61" s="8" t="s">
         <v>221</v>
       </c>
       <c r="F61" s="37" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="I61" t="s">
         <v>222</v>
@@ -8460,7 +9117,7 @@
         <v>222</v>
       </c>
       <c r="K61" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="O61" t="s">
         <v>222</v>
@@ -8468,16 +9125,16 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B62" s="8" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>221</v>
       </c>
       <c r="F62" s="37" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="I62" t="s">
         <v>222</v>
@@ -8486,7 +9143,7 @@
         <v>222</v>
       </c>
       <c r="K62" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="O62" t="s">
         <v>222</v>
@@ -9530,7 +10187,7 @@
         <v>223</v>
       </c>
       <c r="F108" s="12" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="I108" t="s">
         <v>472</v>
@@ -9539,7 +10196,7 @@
         <v>222</v>
       </c>
       <c r="K108" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="O108" t="s">
         <v>472</v>
@@ -9570,7 +10227,7 @@
         <v>224</v>
       </c>
       <c r="F110" s="12" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="I110" t="s">
         <v>222</v>
@@ -9579,7 +10236,7 @@
         <v>222</v>
       </c>
       <c r="K110" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="L110">
         <v>51</v>
@@ -9711,7 +10368,7 @@
         <v>487</v>
       </c>
       <c r="I116" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="J116" t="s">
         <v>222</v>
@@ -9728,7 +10385,7 @@
         <v>223</v>
       </c>
       <c r="F117" s="15" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="I117" t="s">
         <v>222</v>
@@ -9737,7 +10394,7 @@
         <v>222</v>
       </c>
       <c r="K117" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="118" spans="2:15" x14ac:dyDescent="0.25">
@@ -9814,7 +10471,7 @@
         <v>224</v>
       </c>
       <c r="F121" s="15" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="I121" t="s">
         <v>222</v>
@@ -9823,7 +10480,7 @@
         <v>222</v>
       </c>
       <c r="K121" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="L121">
         <v>43</v>
@@ -10044,7 +10701,7 @@
         <v>223</v>
       </c>
       <c r="F131" s="16" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="I131" t="s">
         <v>516</v>
@@ -10064,7 +10721,7 @@
         <v>223</v>
       </c>
       <c r="F132" s="16" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="I132" t="s">
         <v>222</v>
@@ -10084,7 +10741,7 @@
         <v>223</v>
       </c>
       <c r="F133" s="16" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="I133" t="s">
         <v>222</v>
@@ -10107,7 +10764,7 @@
         <v>223</v>
       </c>
       <c r="F134" s="16" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I134" t="s">
         <v>222</v>
@@ -11314,7 +11971,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="24" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B19" s="33" t="str">
         <f>HYPERLINK("[report_info.xlsx]in_out_data_names!Q3","storage_oceanstor_collection")</f>
@@ -12493,7 +13150,7 @@
     <hyperlink ref="A1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -12951,7 +13608,7 @@
         <v>601</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="R3" s="3" t="s">
         <v>602</v>
@@ -13124,7 +13781,7 @@
         <v>362</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="R4" s="7" t="s">
         <v>530</v>
@@ -13181,13 +13838,13 @@
         <v>385</v>
       </c>
       <c r="AJ4" s="7" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="AK4" t="s">
         <v>658</v>
       </c>
       <c r="AL4" s="7" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="AM4" t="s">
         <v>426</v>
@@ -13282,7 +13939,7 @@
         <v>365</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="R5" s="7" t="s">
         <v>534</v>
@@ -13345,7 +14002,7 @@
         <v>264</v>
       </c>
       <c r="AL5" s="7" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="AM5" t="s">
         <v>487</v>
@@ -13354,7 +14011,7 @@
         <v>377</v>
       </c>
       <c r="AP5" s="7" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="AQ5" t="s">
         <v>270</v>
@@ -13419,7 +14076,7 @@
         <v>367</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="R6" s="7" t="s">
         <v>540</v>
@@ -13470,13 +14127,13 @@
         <v>372</v>
       </c>
       <c r="AJ6" s="7" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="AK6" t="s">
         <v>253</v>
       </c>
       <c r="AL6" s="7" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="AM6" t="s">
         <v>270</v>
@@ -13517,7 +14174,7 @@
     </row>
     <row r="7" spans="1:60" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>310</v>
@@ -13532,7 +14189,7 @@
         <v>326</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="R7" s="7" t="s">
         <v>537</v>
@@ -13580,7 +14237,7 @@
         <v>385</v>
       </c>
       <c r="AL7" s="7" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="AM7" t="s">
         <v>273</v>
@@ -13624,7 +14281,7 @@
         <v>328</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="R8" s="7" t="s">
         <v>542</v>
@@ -13690,7 +14347,7 @@
         <v>382</v>
       </c>
       <c r="BA8" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="BB8" t="s">
         <v>666</v>
@@ -13707,7 +14364,7 @@
         <v>330</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="R9" s="7" t="s">
         <v>545</v>
@@ -13758,7 +14415,7 @@
         <v>253</v>
       </c>
       <c r="AP9" s="7" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AQ9" t="s">
         <v>385</v>
@@ -13894,7 +14551,7 @@
         <v>314</v>
       </c>
       <c r="BC11" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="12" spans="1:60" x14ac:dyDescent="0.25">
@@ -14451,10 +15108,10 @@
         <v>755</v>
       </c>
       <c r="B6" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="C6" t="s">
-        <v>759</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -14462,7 +15119,7 @@
         <v>756</v>
       </c>
       <c r="B7" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="C7" t="s">
         <v>719</v>
@@ -14473,7 +15130,7 @@
     <hyperlink ref="A1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/report_info.xlsx
+++ b/report_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\05.PYTHON\Projects\san_report_automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26AB7955-B783-42D4-B36A-3CEBD9EFEB3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D033E582-7265-46F3-858D-126068A025F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7554,9 +7554,6 @@
       <c r="F6" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
       <c r="I6" t="s">
         <v>222</v>
       </c>

--- a/report_info.xlsx
+++ b/report_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\05.PYTHON\Projects\san_report_automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D033E582-7265-46F3-858D-126068A025F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2CBB4A4-BF2D-48D2-AC75-A9E4E2445544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2877" uniqueCount="1086">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2912" uniqueCount="1104">
   <si>
     <t>Contents</t>
   </si>
@@ -3304,6 +3304,60 @@
   </si>
   <si>
     <t>F:\Documents\06.CONFIGS\DataLine\NSK\MAR2026\huawei</t>
+  </si>
+  <si>
+    <t>VC6-VC7</t>
+  </si>
+  <si>
+    <t>F:\Documents\01.CUSTOMERS\DataLine\SAN NORD\VC67\APR2026</t>
+  </si>
+  <si>
+    <t>F:\Documents\06.CONFIGS\DataLine\NORD\VC67\APR2026\huawei</t>
+  </si>
+  <si>
+    <t>F:\Documents\06.CONFIGS\DataLine\NORD\VC67\APR2026\ssave</t>
+  </si>
+  <si>
+    <t>Nord Cloud152</t>
+  </si>
+  <si>
+    <t>F:\Documents\01.CUSTOMERS\DataLine\SAN NORD\Cloud152\APR2026</t>
+  </si>
+  <si>
+    <t>F:\Documents\06.CONFIGS\DataLine\NORD\Cloud152\APR2026\ssave</t>
+  </si>
+  <si>
+    <t>F:\Documents\06.CONFIGS\DataLine\NORD\Cloud152\APR2026\huawei</t>
+  </si>
+  <si>
+    <t>F:\Documents\01.CUSTOMERS\DataLine\SAN NORD\VC02\APR2026</t>
+  </si>
+  <si>
+    <t>F:\Documents\06.CONFIGS\DataLine\NORD\VC02\APR2026\ssave</t>
+  </si>
+  <si>
+    <t>F:\Documents\06.CONFIGS\DataLine\NORD\VC02\APR2026\huawei</t>
+  </si>
+  <si>
+    <t>F:\Documents\06.CONFIGS\DataLine\OST\VC01\APR2026\ssave</t>
+  </si>
+  <si>
+    <t>F:\Documents\06.CONFIGS\DataLine\OST\VC01\APR2026\huawei</t>
+  </si>
+  <si>
+    <t>F:\Documents\01.CUSTOMERS\DataLine\SAN OST\VC01\APR2026</t>
+  </si>
+  <si>
+    <t>OST152</t>
+  </si>
+  <si>
+    <t>F:\Documents\06.CONFIGS\DataLine\OST\Cloud152\MAY2026\ssave</t>
+  </si>
+  <si>
+    <t>F:\Documents\06.CONFIGS\DataLine\OST\Cloud152\MAY2026\huawei</t>
+  </si>
+  <si>
+    <t>F:\Documents\01.CUSTOMERS\DataLine\SAN OST\Cloud152\MAY2026</t>
   </si>
 </sst>
 </file>
@@ -4023,87 +4077,87 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Лист2"/>
-  <dimension ref="A1:EU19"/>
+  <dimension ref="A1:EZ19"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.7109375" customWidth="1"/>
-    <col min="2" max="5" width="66.7109375" style="40" customWidth="1"/>
-    <col min="6" max="6" width="96.85546875" style="40" customWidth="1"/>
-    <col min="7" max="9" width="151" customWidth="1"/>
-    <col min="10" max="26" width="116.28515625" customWidth="1"/>
-    <col min="27" max="28" width="70" customWidth="1"/>
-    <col min="29" max="37" width="116.28515625" customWidth="1"/>
-    <col min="38" max="38" width="90" customWidth="1"/>
-    <col min="39" max="40" width="116.28515625" customWidth="1"/>
-    <col min="41" max="41" width="70" customWidth="1"/>
-    <col min="42" max="42" width="105.28515625" customWidth="1"/>
-    <col min="43" max="44" width="70" customWidth="1"/>
-    <col min="45" max="46" width="116.28515625" customWidth="1"/>
-    <col min="47" max="49" width="70" customWidth="1"/>
-    <col min="50" max="50" width="105.28515625" customWidth="1"/>
-    <col min="51" max="51" width="70" customWidth="1"/>
-    <col min="52" max="62" width="116.28515625" customWidth="1"/>
-    <col min="63" max="65" width="70" customWidth="1"/>
-    <col min="66" max="68" width="96.7109375" customWidth="1"/>
-    <col min="69" max="69" width="70" customWidth="1"/>
-    <col min="70" max="75" width="96.7109375" customWidth="1"/>
-    <col min="76" max="86" width="70" customWidth="1"/>
-    <col min="87" max="87" width="105" customWidth="1"/>
-    <col min="88" max="90" width="96.7109375" customWidth="1"/>
-    <col min="91" max="91" width="70" customWidth="1"/>
-    <col min="92" max="92" width="116.28515625" customWidth="1"/>
-    <col min="93" max="97" width="70" customWidth="1"/>
-    <col min="98" max="100" width="116.28515625" customWidth="1"/>
-    <col min="101" max="101" width="120.85546875" customWidth="1"/>
-    <col min="102" max="102" width="109.42578125" customWidth="1"/>
-    <col min="103" max="103" width="116.7109375" customWidth="1"/>
-    <col min="104" max="104" width="128.5703125" customWidth="1"/>
-    <col min="105" max="105" width="120.28515625" customWidth="1"/>
-    <col min="106" max="106" width="126.5703125" customWidth="1"/>
-    <col min="107" max="107" width="151.28515625" customWidth="1"/>
-    <col min="108" max="108" width="120.42578125" customWidth="1"/>
-    <col min="109" max="109" width="112.42578125" customWidth="1"/>
-    <col min="110" max="110" width="158.5703125" customWidth="1"/>
-    <col min="111" max="111" width="103.7109375" customWidth="1"/>
-    <col min="112" max="112" width="91.85546875" customWidth="1"/>
-    <col min="113" max="113" width="70" customWidth="1"/>
-    <col min="114" max="114" width="124.42578125" customWidth="1"/>
-    <col min="115" max="115" width="139.5703125" customWidth="1"/>
-    <col min="116" max="116" width="48.85546875" customWidth="1"/>
-    <col min="117" max="117" width="76.85546875" customWidth="1"/>
-    <col min="118" max="118" width="80.140625" customWidth="1"/>
-    <col min="119" max="119" width="35.7109375" customWidth="1"/>
-    <col min="120" max="121" width="122.7109375" customWidth="1"/>
-    <col min="122" max="122" width="98" customWidth="1"/>
-    <col min="123" max="123" width="29.7109375" customWidth="1"/>
-    <col min="124" max="124" width="80.140625" customWidth="1"/>
-    <col min="125" max="125" width="68.5703125" customWidth="1"/>
-    <col min="126" max="126" width="109.28515625" customWidth="1"/>
-    <col min="127" max="127" width="62" customWidth="1"/>
-    <col min="128" max="128" width="89.5703125" customWidth="1"/>
-    <col min="129" max="129" width="108.28515625" customWidth="1"/>
-    <col min="130" max="130" width="89.5703125" customWidth="1"/>
-    <col min="131" max="131" width="69.85546875" customWidth="1"/>
-    <col min="132" max="132" width="52.140625" customWidth="1"/>
-    <col min="133" max="133" width="73.140625" customWidth="1"/>
-    <col min="134" max="134" width="29.7109375" customWidth="1"/>
-    <col min="135" max="136" width="76" customWidth="1"/>
-    <col min="137" max="137" width="72.28515625" customWidth="1"/>
-    <col min="138" max="138" width="61.7109375" customWidth="1"/>
-    <col min="139" max="139" width="60" customWidth="1"/>
-    <col min="140" max="140" width="38.140625" customWidth="1"/>
-    <col min="141" max="141" width="69" customWidth="1"/>
-    <col min="142" max="142" width="72.42578125" customWidth="1"/>
-    <col min="143" max="143" width="111.5703125" customWidth="1"/>
-    <col min="144" max="144" width="72.5703125" customWidth="1"/>
-    <col min="145" max="145" width="86.85546875" customWidth="1"/>
-    <col min="146" max="147" width="64.7109375" customWidth="1"/>
-    <col min="148" max="148" width="54.5703125" customWidth="1"/>
-    <col min="149" max="149" width="75.42578125" customWidth="1"/>
-    <col min="150" max="150" width="58.140625" customWidth="1"/>
+    <col min="2" max="10" width="66.7109375" style="40" customWidth="1"/>
+    <col min="11" max="11" width="96.85546875" style="40" customWidth="1"/>
+    <col min="12" max="14" width="151" customWidth="1"/>
+    <col min="15" max="31" width="116.28515625" customWidth="1"/>
+    <col min="32" max="33" width="70" customWidth="1"/>
+    <col min="34" max="42" width="116.28515625" customWidth="1"/>
+    <col min="43" max="43" width="90" customWidth="1"/>
+    <col min="44" max="45" width="116.28515625" customWidth="1"/>
+    <col min="46" max="46" width="70" customWidth="1"/>
+    <col min="47" max="47" width="105.28515625" customWidth="1"/>
+    <col min="48" max="49" width="70" customWidth="1"/>
+    <col min="50" max="51" width="116.28515625" customWidth="1"/>
+    <col min="52" max="54" width="70" customWidth="1"/>
+    <col min="55" max="55" width="105.28515625" customWidth="1"/>
+    <col min="56" max="56" width="70" customWidth="1"/>
+    <col min="57" max="67" width="116.28515625" customWidth="1"/>
+    <col min="68" max="70" width="70" customWidth="1"/>
+    <col min="71" max="73" width="96.7109375" customWidth="1"/>
+    <col min="74" max="74" width="70" customWidth="1"/>
+    <col min="75" max="80" width="96.7109375" customWidth="1"/>
+    <col min="81" max="91" width="70" customWidth="1"/>
+    <col min="92" max="92" width="105" customWidth="1"/>
+    <col min="93" max="95" width="96.7109375" customWidth="1"/>
+    <col min="96" max="96" width="70" customWidth="1"/>
+    <col min="97" max="97" width="116.28515625" customWidth="1"/>
+    <col min="98" max="102" width="70" customWidth="1"/>
+    <col min="103" max="105" width="116.28515625" customWidth="1"/>
+    <col min="106" max="106" width="120.85546875" customWidth="1"/>
+    <col min="107" max="107" width="109.42578125" customWidth="1"/>
+    <col min="108" max="108" width="116.7109375" customWidth="1"/>
+    <col min="109" max="109" width="128.5703125" customWidth="1"/>
+    <col min="110" max="110" width="120.28515625" customWidth="1"/>
+    <col min="111" max="111" width="126.5703125" customWidth="1"/>
+    <col min="112" max="112" width="151.28515625" customWidth="1"/>
+    <col min="113" max="113" width="120.42578125" customWidth="1"/>
+    <col min="114" max="114" width="112.42578125" customWidth="1"/>
+    <col min="115" max="115" width="158.5703125" customWidth="1"/>
+    <col min="116" max="116" width="103.7109375" customWidth="1"/>
+    <col min="117" max="117" width="91.85546875" customWidth="1"/>
+    <col min="118" max="118" width="70" customWidth="1"/>
+    <col min="119" max="119" width="124.42578125" customWidth="1"/>
+    <col min="120" max="120" width="139.5703125" customWidth="1"/>
+    <col min="121" max="121" width="48.85546875" customWidth="1"/>
+    <col min="122" max="122" width="76.85546875" customWidth="1"/>
+    <col min="123" max="123" width="80.140625" customWidth="1"/>
+    <col min="124" max="124" width="35.7109375" customWidth="1"/>
+    <col min="125" max="126" width="122.7109375" customWidth="1"/>
+    <col min="127" max="127" width="98" customWidth="1"/>
+    <col min="128" max="128" width="29.7109375" customWidth="1"/>
+    <col min="129" max="129" width="80.140625" customWidth="1"/>
+    <col min="130" max="130" width="68.5703125" customWidth="1"/>
+    <col min="131" max="131" width="109.28515625" customWidth="1"/>
+    <col min="132" max="132" width="62" customWidth="1"/>
+    <col min="133" max="133" width="89.5703125" customWidth="1"/>
+    <col min="134" max="134" width="108.28515625" customWidth="1"/>
+    <col min="135" max="135" width="89.5703125" customWidth="1"/>
+    <col min="136" max="136" width="69.85546875" customWidth="1"/>
+    <col min="137" max="137" width="52.140625" customWidth="1"/>
+    <col min="138" max="138" width="73.140625" customWidth="1"/>
+    <col min="139" max="139" width="29.7109375" customWidth="1"/>
+    <col min="140" max="141" width="76" customWidth="1"/>
+    <col min="142" max="142" width="72.28515625" customWidth="1"/>
+    <col min="143" max="143" width="61.7109375" customWidth="1"/>
+    <col min="144" max="144" width="60" customWidth="1"/>
+    <col min="145" max="145" width="38.140625" customWidth="1"/>
+    <col min="146" max="146" width="69" customWidth="1"/>
+    <col min="147" max="147" width="72.42578125" customWidth="1"/>
+    <col min="148" max="148" width="111.5703125" customWidth="1"/>
+    <col min="149" max="149" width="72.5703125" customWidth="1"/>
+    <col min="150" max="150" width="86.85546875" customWidth="1"/>
+    <col min="151" max="152" width="64.7109375" customWidth="1"/>
+    <col min="153" max="153" width="54.5703125" customWidth="1"/>
+    <col min="154" max="154" width="75.42578125" customWidth="1"/>
+    <col min="155" max="155" width="58.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:151" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:156" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4180,8 +4234,12 @@
       <c r="Z1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
+      <c r="AA1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="AC1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4191,12 +4249,8 @@
       <c r="AE1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AF1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
       <c r="AH1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4209,29 +4263,29 @@
       <c r="AK1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AL1" s="1"/>
+      <c r="AL1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="AM1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="AN1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AO1" s="1"/>
+      <c r="AO1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="AP1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AQ1" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="AQ1" s="1"/>
       <c r="AR1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="AS1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AT1" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="AT1" s="1"/>
       <c r="AU1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4280,11 +4334,21 @@
       <c r="BJ1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="BK1" s="1"/>
-      <c r="BL1" s="1"/>
-      <c r="BM1" s="1"/>
-      <c r="BN1" s="1"/>
-      <c r="BO1" s="1"/>
+      <c r="BK1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="BP1" s="1"/>
       <c r="BQ1" s="1"/>
       <c r="BR1" s="1"/>
@@ -4309,29 +4373,19 @@
       <c r="CK1" s="1"/>
       <c r="CL1" s="1"/>
       <c r="CM1" s="1"/>
-      <c r="CN1" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="CN1" s="1"/>
       <c r="CO1" s="1"/>
       <c r="CP1" s="1"/>
       <c r="CQ1" s="1"/>
       <c r="CR1" s="1"/>
-      <c r="CS1" s="1"/>
-      <c r="CT1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CU1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CV1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CW1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="CX1" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="CS1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="CT1" s="1"/>
+      <c r="CU1" s="1"/>
+      <c r="CV1" s="1"/>
+      <c r="CW1" s="1"/>
+      <c r="CX1" s="1"/>
       <c r="CY1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4479,8 +4533,23 @@
       <c r="EU1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:151" x14ac:dyDescent="0.25">
+      <c r="EV1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="EW1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="EX1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="EY1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="EZ1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:156" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -4489,8 +4558,13 @@
       <c r="D2"/>
       <c r="E2"/>
       <c r="F2"/>
-    </row>
-    <row r="3" spans="1:151" x14ac:dyDescent="0.25">
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+    </row>
+    <row r="3" spans="1:156" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -4498,859 +4572,889 @@
       <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="AJ3" s="3" t="s">
+      <c r="AO3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="BJ3" s="39"/>
-    </row>
-    <row r="4" spans="1:151" x14ac:dyDescent="0.25">
+      <c r="BO3" s="39"/>
+    </row>
+    <row r="4" spans="1:156" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="39"/>
       <c r="C4" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1090</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="H4" t="s">
         <v>1082</v>
       </c>
-      <c r="D4" t="s">
+      <c r="I4" t="s">
         <v>771</v>
       </c>
-      <c r="E4" t="s">
+      <c r="J4" t="s">
         <v>1024</v>
       </c>
-      <c r="F4" t="s">
+      <c r="K4" t="s">
         <v>1016</v>
       </c>
-      <c r="G4" t="s">
+      <c r="L4" t="s">
         <v>1068</v>
       </c>
-      <c r="H4" t="s">
+      <c r="M4" t="s">
         <v>1064</v>
       </c>
-      <c r="I4" t="s">
+      <c r="N4" t="s">
         <v>1060</v>
       </c>
-      <c r="J4" t="s">
+      <c r="O4" t="s">
         <v>1058</v>
       </c>
-      <c r="K4" t="s">
+      <c r="P4" t="s">
         <v>1020</v>
       </c>
-      <c r="L4" t="s">
+      <c r="Q4" t="s">
         <v>1039</v>
       </c>
-      <c r="M4" t="s">
+      <c r="R4" t="s">
         <v>789</v>
       </c>
-      <c r="N4" t="s">
+      <c r="S4" t="s">
         <v>769</v>
       </c>
-      <c r="O4" t="s">
+      <c r="T4" t="s">
         <v>1039</v>
       </c>
-      <c r="P4" t="s">
+      <c r="U4" t="s">
         <v>994</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="V4" t="s">
         <v>1032</v>
       </c>
-      <c r="R4" t="s">
+      <c r="W4" t="s">
         <v>1028</v>
       </c>
-      <c r="S4" t="s">
+      <c r="X4" t="s">
         <v>1024</v>
       </c>
-      <c r="T4" t="s">
+      <c r="Y4" t="s">
         <v>1020</v>
       </c>
-      <c r="U4" t="s">
+      <c r="Z4" t="s">
         <v>1016</v>
       </c>
-      <c r="V4" t="s">
+      <c r="AA4" t="s">
         <v>1013</v>
       </c>
-      <c r="W4" t="s">
+      <c r="AB4" t="s">
         <v>1008</v>
       </c>
-      <c r="X4" t="s">
+      <c r="AC4" t="s">
         <v>1004</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="AD4" t="s">
         <v>1000</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AE4" t="s">
         <v>850</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AF4" t="s">
         <v>994</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AG4" t="s">
         <v>762</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>850</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>937</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>838</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>979</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>814</v>
       </c>
       <c r="AH4" t="s">
         <v>850</v>
       </c>
       <c r="AI4" t="s">
+        <v>937</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>838</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>979</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>814</v>
+      </c>
+      <c r="AM4" t="s">
         <v>850</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="AN4" t="s">
+        <v>850</v>
+      </c>
+      <c r="AO4" t="s">
         <v>906</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="AP4" t="s">
         <v>850</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AQ4" t="s">
         <v>916</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AR4" t="s">
         <v>838</v>
       </c>
-      <c r="AN4" t="s">
+      <c r="AS4" t="s">
         <v>894</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="AT4" t="s">
         <v>762</v>
       </c>
-      <c r="AP4" t="s">
+      <c r="AU4" t="s">
         <v>920</v>
       </c>
-      <c r="AQ4" t="s">
+      <c r="AV4" t="s">
         <v>945</v>
       </c>
-      <c r="AR4" t="s">
+      <c r="AW4" t="s">
         <v>731</v>
       </c>
-      <c r="AS4" t="s">
+      <c r="AX4" t="s">
         <v>937</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="AY4" t="s">
         <v>838</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AZ4" t="s">
         <v>762</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="BA4" t="s">
         <v>926</v>
       </c>
-      <c r="AW4" t="s">
+      <c r="BB4" t="s">
         <v>916</v>
       </c>
-      <c r="AX4" t="s">
+      <c r="BC4" t="s">
         <v>920</v>
       </c>
-      <c r="AY4" t="s">
+      <c r="BD4" t="s">
         <v>916</v>
       </c>
-      <c r="AZ4" t="s">
+      <c r="BE4" t="s">
         <v>906</v>
       </c>
-      <c r="BA4" t="s">
+      <c r="BF4" t="s">
         <v>771</v>
       </c>
-      <c r="BB4" t="s">
+      <c r="BG4" t="s">
         <v>906</v>
       </c>
-      <c r="BC4" t="s">
+      <c r="BH4" t="s">
         <v>838</v>
       </c>
-      <c r="BD4" t="s">
+      <c r="BI4" t="s">
         <v>899</v>
       </c>
-      <c r="BE4" t="s">
+      <c r="BJ4" t="s">
         <v>894</v>
       </c>
-      <c r="BF4" t="s">
+      <c r="BK4" t="s">
         <v>890</v>
       </c>
-      <c r="BG4" t="s">
+      <c r="BL4" t="s">
         <v>846</v>
       </c>
-      <c r="BH4" t="s">
+      <c r="BM4" t="s">
         <v>876</v>
       </c>
-      <c r="BI4" t="s">
+      <c r="BN4" t="s">
         <v>762</v>
       </c>
-      <c r="BJ4" t="s">
+      <c r="BO4" t="s">
         <v>850</v>
       </c>
-      <c r="BK4" t="s">
+      <c r="BP4" t="s">
         <v>846</v>
       </c>
-      <c r="BL4" t="s">
+      <c r="BQ4" t="s">
         <v>838</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BR4" t="s">
         <v>835</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BS4" t="s">
         <v>834</v>
       </c>
-      <c r="BO4" t="s">
+      <c r="BT4" t="s">
         <v>829</v>
       </c>
-      <c r="BP4" t="s">
+      <c r="BU4" t="s">
         <v>814</v>
       </c>
-      <c r="BQ4" t="s">
+      <c r="BV4" t="s">
         <v>746</v>
       </c>
-      <c r="BR4" t="s">
+      <c r="BW4" t="s">
         <v>818</v>
       </c>
-      <c r="BS4" t="s">
+      <c r="BX4" t="s">
         <v>818</v>
       </c>
-      <c r="BT4" t="s">
+      <c r="BY4" t="s">
         <v>814</v>
       </c>
-      <c r="BU4" t="s">
+      <c r="BZ4" t="s">
         <v>811</v>
       </c>
-      <c r="BV4" t="s">
+      <c r="CA4" t="s">
         <v>808</v>
       </c>
-      <c r="BW4" t="s">
+      <c r="CB4" t="s">
         <v>762</v>
       </c>
-      <c r="BX4" t="s">
+      <c r="CC4" t="s">
         <v>803</v>
       </c>
-      <c r="BY4" t="s">
+      <c r="CD4" t="s">
         <v>799</v>
       </c>
-      <c r="BZ4" t="s">
+      <c r="CE4" t="s">
         <v>795</v>
       </c>
-      <c r="CA4" t="s">
+      <c r="CF4" t="s">
         <v>792</v>
       </c>
-      <c r="CB4" t="s">
+      <c r="CG4" t="s">
         <v>789</v>
       </c>
-      <c r="CC4" t="s">
+      <c r="CH4" t="s">
         <v>786</v>
       </c>
-      <c r="CD4" t="s">
+      <c r="CI4" t="s">
         <v>783</v>
       </c>
-      <c r="CE4" t="s">
+      <c r="CJ4" t="s">
         <v>781</v>
       </c>
-      <c r="CF4" t="s">
+      <c r="CK4" t="s">
         <v>777</v>
       </c>
-      <c r="CG4" t="s">
+      <c r="CL4" t="s">
         <v>775</v>
       </c>
-      <c r="CH4" t="s">
+      <c r="CM4" t="s">
         <v>771</v>
       </c>
-      <c r="CI4" t="s">
+      <c r="CN4" t="s">
         <v>769</v>
       </c>
-      <c r="CJ4" t="s">
+      <c r="CO4" t="s">
         <v>765</v>
       </c>
-      <c r="CK4" t="s">
+      <c r="CP4" t="s">
         <v>762</v>
       </c>
-      <c r="CL4" t="s">
+      <c r="CQ4" t="s">
         <v>654</v>
       </c>
-      <c r="CM4" t="s">
+      <c r="CR4" t="s">
         <v>746</v>
       </c>
-      <c r="CN4" t="s">
+      <c r="CS4" t="s">
         <v>15</v>
       </c>
-      <c r="CO4" t="s">
+      <c r="CT4" t="s">
         <v>733</v>
       </c>
-      <c r="CP4" t="s">
+      <c r="CU4" t="s">
         <v>731</v>
       </c>
-      <c r="CQ4" t="s">
+      <c r="CV4" t="s">
         <v>723</v>
       </c>
-      <c r="CR4" t="s">
+      <c r="CW4" t="s">
         <v>655</v>
       </c>
-      <c r="CS4" t="s">
+      <c r="CX4" t="s">
         <v>654</v>
       </c>
-      <c r="CT4" t="s">
+      <c r="CY4" t="s">
         <v>15</v>
       </c>
-      <c r="CU4" t="s">
+      <c r="CZ4" t="s">
         <v>16</v>
       </c>
-      <c r="CV4" t="s">
+      <c r="DA4" t="s">
         <v>16</v>
       </c>
-      <c r="CW4" t="s">
+      <c r="DB4" t="s">
         <v>17</v>
       </c>
-      <c r="CX4" t="s">
+      <c r="DC4" t="s">
         <v>18</v>
       </c>
-      <c r="CY4" t="s">
+      <c r="DD4" t="s">
         <v>19</v>
       </c>
-      <c r="CZ4" t="s">
+      <c r="DE4" t="s">
         <v>20</v>
       </c>
-      <c r="DA4" t="s">
+      <c r="DF4" t="s">
         <v>21</v>
       </c>
-      <c r="DB4" t="s">
+      <c r="DG4" t="s">
         <v>22</v>
       </c>
-      <c r="DC4" t="s">
+      <c r="DH4" t="s">
         <v>19</v>
       </c>
-      <c r="DD4" t="s">
+      <c r="DI4" t="s">
         <v>23</v>
       </c>
-      <c r="DE4" t="s">
+      <c r="DJ4" t="s">
         <v>24</v>
       </c>
-      <c r="DF4" t="s">
+      <c r="DK4" t="s">
         <v>25</v>
       </c>
-      <c r="DG4" t="s">
+      <c r="DL4" t="s">
         <v>26</v>
       </c>
-      <c r="DH4" t="s">
+      <c r="DM4" t="s">
         <v>26</v>
       </c>
-      <c r="DI4" t="s">
+      <c r="DN4" t="s">
         <v>27</v>
       </c>
-      <c r="DJ4" t="s">
+      <c r="DO4" t="s">
         <v>27</v>
       </c>
-      <c r="DK4" t="s">
+      <c r="DP4" t="s">
         <v>16</v>
       </c>
-      <c r="DL4" t="s">
+      <c r="DQ4" t="s">
         <v>28</v>
       </c>
-      <c r="DM4" t="s">
+      <c r="DR4" t="s">
         <v>27</v>
       </c>
-      <c r="DN4" t="s">
+      <c r="DS4" t="s">
         <v>17</v>
       </c>
-      <c r="DO4" t="s">
+      <c r="DT4" t="s">
         <v>29</v>
       </c>
-      <c r="DP4" t="s">
+      <c r="DU4" t="s">
         <v>25</v>
       </c>
-      <c r="DQ4" t="s">
+      <c r="DV4" t="s">
         <v>25</v>
       </c>
-      <c r="DR4" t="s">
+      <c r="DW4" t="s">
         <v>30</v>
       </c>
-      <c r="DS4" t="s">
+      <c r="DX4" t="s">
         <v>31</v>
       </c>
-      <c r="DT4" t="s">
+      <c r="DY4" t="s">
         <v>32</v>
       </c>
-      <c r="DU4" t="s">
+      <c r="DZ4" t="s">
         <v>33</v>
       </c>
-      <c r="DV4" t="s">
+      <c r="EA4" t="s">
         <v>34</v>
       </c>
-      <c r="DW4" t="s">
+      <c r="EB4" t="s">
         <v>35</v>
       </c>
-      <c r="DX4" t="s">
+      <c r="EC4" t="s">
         <v>36</v>
       </c>
-      <c r="DY4" t="s">
+      <c r="ED4" t="s">
         <v>37</v>
       </c>
-      <c r="DZ4" t="s">
+      <c r="EE4" t="s">
         <v>37</v>
       </c>
-      <c r="EA4" t="s">
+      <c r="EF4" t="s">
         <v>37</v>
       </c>
-      <c r="EB4" t="s">
+      <c r="EG4" t="s">
         <v>38</v>
       </c>
-      <c r="EC4" t="s">
+      <c r="EH4" t="s">
         <v>39</v>
       </c>
-      <c r="ED4" t="s">
+      <c r="EI4" t="s">
         <v>39</v>
       </c>
-      <c r="EE4" t="s">
+      <c r="EJ4" t="s">
         <v>40</v>
       </c>
-      <c r="EF4" t="s">
+      <c r="EK4" t="s">
         <v>40</v>
       </c>
-      <c r="EG4" t="s">
+      <c r="EL4" t="s">
         <v>17</v>
       </c>
-      <c r="EH4" t="s">
+      <c r="EM4" t="s">
         <v>41</v>
       </c>
-      <c r="EI4" t="s">
+      <c r="EN4" t="s">
         <v>42</v>
       </c>
-      <c r="EJ4" t="s">
+      <c r="EO4" t="s">
         <v>43</v>
       </c>
-      <c r="EK4" t="s">
+      <c r="EP4" t="s">
         <v>44</v>
       </c>
-      <c r="EL4" t="s">
+      <c r="EQ4" t="s">
         <v>45</v>
       </c>
-      <c r="EM4" t="s">
+      <c r="ER4" t="s">
         <v>46</v>
       </c>
-      <c r="EN4" t="s">
+      <c r="ES4" t="s">
         <v>47</v>
       </c>
-      <c r="EO4" s="2" t="s">
+      <c r="ET4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="EP4" s="2" t="s">
+      <c r="EU4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="EQ4" s="2" t="s">
+      <c r="EV4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="ER4" s="2" t="s">
+      <c r="EW4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="ES4" s="2" t="s">
+      <c r="EX4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="ET4" s="2" t="s">
+      <c r="EY4" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="EU4" s="2" t="s">
+      <c r="EZ4" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:151" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:156" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>55</v>
       </c>
       <c r="B5" s="39"/>
       <c r="C5" s="5">
+        <v>46147</v>
+      </c>
+      <c r="D5" s="5">
+        <v>46142</v>
+      </c>
+      <c r="E5" s="5">
+        <v>46133</v>
+      </c>
+      <c r="F5" s="5">
+        <v>46128</v>
+      </c>
+      <c r="G5" s="5">
+        <v>46118</v>
+      </c>
+      <c r="H5" s="5">
         <v>46111</v>
       </c>
-      <c r="D5" s="5">
+      <c r="I5" s="5">
         <v>46108</v>
       </c>
-      <c r="E5" s="5">
+      <c r="J5" s="5">
         <v>46107</v>
       </c>
-      <c r="F5" s="5">
+      <c r="K5" s="5">
         <v>46106</v>
       </c>
-      <c r="G5" s="5">
+      <c r="L5" s="5">
         <v>45818</v>
       </c>
-      <c r="H5" s="5">
+      <c r="M5" s="5">
         <v>45818</v>
       </c>
-      <c r="I5" s="5">
+      <c r="N5" s="5">
         <v>45810</v>
       </c>
-      <c r="J5" s="5">
+      <c r="O5" s="5">
         <v>45793</v>
       </c>
-      <c r="K5" s="5">
+      <c r="P5" s="5">
         <v>45771</v>
       </c>
-      <c r="L5" s="5">
+      <c r="Q5" s="5">
         <v>45758</v>
       </c>
-      <c r="M5" s="5">
+      <c r="R5" s="5">
         <v>45751</v>
       </c>
-      <c r="N5" s="5">
+      <c r="S5" s="5">
         <v>45742</v>
       </c>
-      <c r="O5" s="5">
+      <c r="T5" s="5">
         <v>45730</v>
       </c>
-      <c r="P5" s="5">
+      <c r="U5" s="5">
         <v>45726</v>
       </c>
-      <c r="Q5" s="5">
+      <c r="V5" s="5">
         <v>45721</v>
       </c>
-      <c r="R5" s="5">
+      <c r="W5" s="5">
         <v>45688</v>
       </c>
-      <c r="S5" s="5">
+      <c r="X5" s="5">
         <v>45684</v>
       </c>
-      <c r="T5" s="5">
+      <c r="Y5" s="5">
         <v>45677</v>
       </c>
-      <c r="U5" s="5">
+      <c r="Z5" s="5">
         <v>45673</v>
       </c>
-      <c r="V5" s="5">
+      <c r="AA5" s="5">
         <v>45672</v>
       </c>
-      <c r="W5" s="5">
+      <c r="AB5" s="5">
         <v>45671</v>
       </c>
-      <c r="X5" s="5">
+      <c r="AC5" s="5">
         <v>45531</v>
       </c>
-      <c r="Y5" s="5">
+      <c r="AD5" s="5">
         <v>45531</v>
       </c>
-      <c r="Z5" s="5">
+      <c r="AE5" s="5">
         <v>45531</v>
       </c>
-      <c r="AA5" s="5">
+      <c r="AF5" s="5">
         <v>45523</v>
       </c>
-      <c r="AB5" s="5">
+      <c r="AG5" s="5">
         <v>45473</v>
-      </c>
-      <c r="AC5" s="5">
-        <v>45378</v>
-      </c>
-      <c r="AD5" s="5">
-        <v>45391</v>
-      </c>
-      <c r="AE5" s="5">
-        <v>45391</v>
-      </c>
-      <c r="AF5" s="5">
-        <v>45385</v>
-      </c>
-      <c r="AG5" s="5">
-        <v>45384</v>
       </c>
       <c r="AH5" s="5">
         <v>45378</v>
       </c>
       <c r="AI5" s="5">
+        <v>45391</v>
+      </c>
+      <c r="AJ5" s="5">
+        <v>45391</v>
+      </c>
+      <c r="AK5" s="5">
+        <v>45385</v>
+      </c>
+      <c r="AL5" s="5">
+        <v>45384</v>
+      </c>
+      <c r="AM5" s="5">
+        <v>45378</v>
+      </c>
+      <c r="AN5" s="5">
         <v>45366</v>
       </c>
-      <c r="AJ5" s="5">
+      <c r="AO5" s="5">
         <v>45364</v>
       </c>
-      <c r="AK5" s="5">
+      <c r="AP5" s="5">
         <v>45351</v>
       </c>
-      <c r="AL5" s="5">
+      <c r="AQ5" s="5">
         <v>44973</v>
       </c>
-      <c r="AM5" s="5">
+      <c r="AR5" s="5">
         <v>45309</v>
       </c>
-      <c r="AN5" s="5">
+      <c r="AS5" s="5">
         <v>45307</v>
       </c>
-      <c r="AO5" s="5">
+      <c r="AT5" s="5">
         <v>45301</v>
       </c>
-      <c r="AP5" s="5">
+      <c r="AU5" s="5">
         <v>45279</v>
       </c>
-      <c r="AQ5" s="5">
+      <c r="AV5" s="5">
         <v>45268</v>
       </c>
-      <c r="AR5" s="5">
+      <c r="AW5" s="5">
         <v>45268</v>
       </c>
-      <c r="AS5" s="5">
+      <c r="AX5" s="5">
         <v>45267</v>
       </c>
-      <c r="AT5" s="5">
+      <c r="AY5" s="5">
         <v>45267</v>
       </c>
-      <c r="AU5" s="5">
+      <c r="AZ5" s="5">
         <v>45254</v>
       </c>
-      <c r="AV5" s="5">
+      <c r="BA5" s="5">
         <v>45252</v>
       </c>
-      <c r="AW5" s="5">
+      <c r="BB5" s="5">
         <v>45247</v>
       </c>
-      <c r="AX5" s="5">
+      <c r="BC5" s="5">
         <v>45246</v>
       </c>
-      <c r="AY5" s="5">
+      <c r="BD5" s="5">
         <v>45237</v>
       </c>
-      <c r="AZ5" s="5">
+      <c r="BE5" s="5">
         <v>45211</v>
       </c>
-      <c r="BA5" s="5">
+      <c r="BF5" s="5">
         <v>45201</v>
       </c>
-      <c r="BB5" s="5">
+      <c r="BG5" s="5">
         <v>45195</v>
       </c>
-      <c r="BC5" s="5">
+      <c r="BH5" s="5">
         <v>45188</v>
       </c>
-      <c r="BD5" s="5">
+      <c r="BI5" s="5">
         <v>45188</v>
       </c>
-      <c r="BE5" s="5">
+      <c r="BJ5" s="5">
         <v>45188</v>
       </c>
-      <c r="BF5" s="5">
+      <c r="BK5" s="5">
         <v>45187</v>
       </c>
-      <c r="BG5" s="5">
+      <c r="BL5" s="5">
         <v>45167</v>
       </c>
-      <c r="BH5" s="5">
+      <c r="BM5" s="5">
         <v>45154</v>
       </c>
-      <c r="BI5" s="5">
+      <c r="BN5" s="5">
         <v>45154</v>
       </c>
-      <c r="BJ5" s="5">
+      <c r="BO5" s="5">
         <v>45128</v>
       </c>
-      <c r="BK5" s="5">
+      <c r="BP5" s="5">
         <v>45118</v>
       </c>
-      <c r="BL5" s="5">
+      <c r="BQ5" s="5">
         <v>45092</v>
       </c>
-      <c r="BM5" s="5">
+      <c r="BR5" s="5">
         <v>45085</v>
       </c>
-      <c r="BN5" s="5">
+      <c r="BS5" s="5">
         <v>45061</v>
       </c>
-      <c r="BO5" s="5">
+      <c r="BT5" s="5">
         <v>45058</v>
       </c>
-      <c r="BP5" s="5">
+      <c r="BU5" s="5">
         <v>45057</v>
       </c>
-      <c r="BQ5" s="5">
+      <c r="BV5" s="5">
         <v>45056</v>
       </c>
-      <c r="BR5" s="5">
+      <c r="BW5" s="5">
         <v>45051</v>
       </c>
-      <c r="BS5" s="5">
+      <c r="BX5" s="5">
         <v>45050</v>
       </c>
-      <c r="BT5" s="5">
+      <c r="BY5" s="5">
         <v>45041</v>
       </c>
-      <c r="BU5" s="5">
+      <c r="BZ5" s="5">
         <v>45035</v>
       </c>
-      <c r="BV5" s="5">
+      <c r="CA5" s="5">
         <v>45030</v>
       </c>
-      <c r="BW5" s="5">
+      <c r="CB5" s="5">
         <v>45030</v>
       </c>
-      <c r="BX5" s="5">
+      <c r="CC5" s="5">
         <v>45029</v>
       </c>
-      <c r="BY5" s="5">
+      <c r="CD5" s="5">
         <v>45027</v>
       </c>
-      <c r="BZ5" s="5">
+      <c r="CE5" s="5">
         <v>45026</v>
       </c>
-      <c r="CA5" s="5">
+      <c r="CF5" s="5">
         <v>45023</v>
       </c>
-      <c r="CB5" s="5">
+      <c r="CG5" s="5">
         <v>45020</v>
       </c>
-      <c r="CC5" s="5">
+      <c r="CH5" s="5">
         <v>45008</v>
       </c>
-      <c r="CD5" s="5">
+      <c r="CI5" s="5">
         <v>45008</v>
       </c>
-      <c r="CE5" s="5">
+      <c r="CJ5" s="5">
         <v>45008</v>
       </c>
-      <c r="CF5" s="5">
+      <c r="CK5" s="5">
         <v>45008</v>
       </c>
-      <c r="CG5" s="5">
+      <c r="CL5" s="5">
         <v>45007</v>
       </c>
-      <c r="CH5" s="5">
+      <c r="CM5" s="5">
         <v>45006</v>
       </c>
-      <c r="CI5" s="5">
+      <c r="CN5" s="5">
         <v>45002</v>
       </c>
-      <c r="CJ5" s="5">
+      <c r="CO5" s="5">
         <v>45000</v>
       </c>
-      <c r="CK5" s="5">
+      <c r="CP5" s="5">
         <v>44999</v>
       </c>
-      <c r="CL5" s="5">
+      <c r="CQ5" s="5">
         <v>44949</v>
       </c>
-      <c r="CM5" s="5">
+      <c r="CR5" s="5">
         <v>44943</v>
       </c>
-      <c r="CN5" s="5">
+      <c r="CS5" s="5">
         <v>44868</v>
       </c>
-      <c r="CQ5" s="5">
+      <c r="CV5" s="5">
         <v>44903</v>
       </c>
-      <c r="CR5" s="5">
+      <c r="CW5" s="5">
         <v>44889</v>
       </c>
-      <c r="CS5" s="5">
+      <c r="CX5" s="5">
         <v>44879</v>
       </c>
-      <c r="CT5" s="5">
+      <c r="CY5" s="5">
         <v>44868</v>
       </c>
-      <c r="CU5" s="5">
+      <c r="CZ5" s="5">
         <v>44632</v>
       </c>
-      <c r="CV5" s="5">
+      <c r="DA5" s="5">
         <v>44620</v>
       </c>
-      <c r="CW5" s="5">
+      <c r="DB5" s="5">
         <v>44608</v>
       </c>
-      <c r="CX5" s="5">
+      <c r="DC5" s="5">
         <v>44592</v>
       </c>
-      <c r="CY5" s="5">
+      <c r="DD5" s="5">
         <v>44575</v>
       </c>
-      <c r="CZ5" s="5">
+      <c r="DE5" s="5">
         <v>44537</v>
       </c>
-      <c r="DA5" s="5">
+      <c r="DF5" s="5">
         <v>44531</v>
       </c>
-      <c r="DB5" s="5">
+      <c r="DG5" s="5">
         <v>44530</v>
       </c>
-      <c r="DC5" s="5">
+      <c r="DH5" s="5">
         <v>44529</v>
       </c>
-      <c r="DD5" s="5">
+      <c r="DI5" s="5">
         <v>44524</v>
       </c>
-      <c r="DE5" s="5">
+      <c r="DJ5" s="5">
         <v>44503</v>
       </c>
-      <c r="DF5" s="5">
+      <c r="DK5" s="5">
         <v>44343</v>
       </c>
-      <c r="DG5" s="5">
+      <c r="DL5" s="5">
         <v>44484</v>
       </c>
-      <c r="DH5" s="5">
+      <c r="DM5" s="5">
         <v>44484</v>
       </c>
-      <c r="DI5" s="5">
+      <c r="DN5" s="5">
         <v>44473</v>
       </c>
-      <c r="DJ5" s="5">
+      <c r="DO5" s="5">
         <v>44469</v>
       </c>
-      <c r="DK5" s="5">
+      <c r="DP5" s="5">
         <v>44453</v>
       </c>
-      <c r="DL5" s="5">
+      <c r="DQ5" s="5">
         <v>44426</v>
       </c>
-      <c r="DM5" s="5">
+      <c r="DR5" s="5">
         <v>44330</v>
       </c>
-      <c r="DN5" s="5">
+      <c r="DS5" s="5">
         <v>44307</v>
       </c>
-      <c r="DO5" s="5">
+      <c r="DT5" s="5">
         <v>44294</v>
       </c>
-      <c r="DP5" s="5">
+      <c r="DU5" s="5">
         <v>44343</v>
       </c>
-      <c r="DQ5" s="5">
+      <c r="DV5" s="5">
         <v>44292</v>
       </c>
-      <c r="DR5" s="5">
+      <c r="DW5" s="5">
         <v>44291</v>
       </c>
-      <c r="DS5" s="5">
+      <c r="DX5" s="5">
         <v>44286</v>
       </c>
-      <c r="DT5" s="5">
+      <c r="DY5" s="5">
         <v>44260</v>
       </c>
-      <c r="DU5" s="5">
+      <c r="DZ5" s="5">
         <v>44244</v>
       </c>
-      <c r="DV5" s="5">
+      <c r="EA5" s="5">
         <v>44245</v>
       </c>
-      <c r="DW5" s="5">
+      <c r="EB5" s="5">
         <v>44223</v>
       </c>
-      <c r="DX5" s="5">
+      <c r="EC5" s="5">
         <v>44209</v>
       </c>
-      <c r="DY5" s="5">
+      <c r="ED5" s="5">
         <v>44253</v>
       </c>
-      <c r="DZ5" s="5">
+      <c r="EE5" s="5">
         <v>44237</v>
       </c>
-      <c r="EC5" s="5">
+      <c r="EH5" s="5">
         <v>44181</v>
       </c>
-      <c r="EO5" s="2"/>
-      <c r="EP5" s="2"/>
-      <c r="EQ5" s="2"/>
-      <c r="ER5" s="2"/>
-      <c r="ES5" s="2"/>
       <c r="ET5" s="2"/>
       <c r="EU5" s="2"/>
-    </row>
-    <row r="6" spans="1:151" x14ac:dyDescent="0.25">
+      <c r="EV5" s="2"/>
+      <c r="EW5" s="2"/>
+      <c r="EX5" s="2"/>
+      <c r="EY5" s="2"/>
+      <c r="EZ5" s="2"/>
+    </row>
+    <row r="6" spans="1:156" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>56</v>
       </c>
@@ -5422,10 +5526,10 @@
         <v>747</v>
       </c>
       <c r="Y6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="Z6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="AA6" t="s">
         <v>747</v>
@@ -5434,7 +5538,7 @@
         <v>747</v>
       </c>
       <c r="AC6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="AD6" t="s">
         <v>57</v>
@@ -5443,10 +5547,10 @@
         <v>57</v>
       </c>
       <c r="AF6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="AG6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="AH6" t="s">
         <v>57</v>
@@ -5461,7 +5565,7 @@
         <v>57</v>
       </c>
       <c r="AL6" t="s">
-        <v>747</v>
+        <v>57</v>
       </c>
       <c r="AM6" t="s">
         <v>57</v>
@@ -5470,22 +5574,22 @@
         <v>57</v>
       </c>
       <c r="AO6" t="s">
-        <v>747</v>
+        <v>57</v>
       </c>
       <c r="AP6" t="s">
-        <v>747</v>
+        <v>57</v>
       </c>
       <c r="AQ6" t="s">
         <v>747</v>
       </c>
       <c r="AR6" t="s">
-        <v>747</v>
+        <v>57</v>
       </c>
       <c r="AS6" t="s">
         <v>57</v>
       </c>
       <c r="AT6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="AU6" t="s">
         <v>747</v>
@@ -5497,25 +5601,25 @@
         <v>747</v>
       </c>
       <c r="AX6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AZ6" t="s">
         <v>747</v>
       </c>
-      <c r="AY6" t="s">
+      <c r="BA6" t="s">
         <v>747</v>
       </c>
-      <c r="AZ6" t="s">
-        <v>57</v>
-      </c>
-      <c r="BA6" t="s">
-        <v>57</v>
-      </c>
       <c r="BB6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="BC6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="BD6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="BE6" t="s">
         <v>57</v>
@@ -5536,19 +5640,19 @@
         <v>57</v>
       </c>
       <c r="BK6" t="s">
-        <v>747</v>
+        <v>57</v>
       </c>
       <c r="BL6" t="s">
-        <v>747</v>
+        <v>57</v>
       </c>
       <c r="BM6" t="s">
-        <v>747</v>
+        <v>57</v>
       </c>
       <c r="BN6" t="s">
-        <v>747</v>
+        <v>57</v>
       </c>
       <c r="BO6" t="s">
-        <v>747</v>
+        <v>57</v>
       </c>
       <c r="BP6" t="s">
         <v>747</v>
@@ -5623,19 +5727,19 @@
         <v>747</v>
       </c>
       <c r="CN6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="CO6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="CP6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="CQ6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="CR6" t="s">
-        <v>57</v>
+        <v>747</v>
       </c>
       <c r="CS6" t="s">
         <v>57</v>
@@ -5644,31 +5748,31 @@
         <v>57</v>
       </c>
       <c r="CU6" t="s">
+        <v>57</v>
+      </c>
+      <c r="CV6" t="s">
+        <v>57</v>
+      </c>
+      <c r="CW6" t="s">
+        <v>57</v>
+      </c>
+      <c r="CX6" t="s">
+        <v>57</v>
+      </c>
+      <c r="CY6" t="s">
+        <v>57</v>
+      </c>
+      <c r="CZ6" t="s">
         <v>58</v>
       </c>
-      <c r="CV6" t="s">
+      <c r="DA6" t="s">
         <v>58</v>
       </c>
-      <c r="CW6" t="s">
+      <c r="DB6" t="s">
         <v>58</v>
       </c>
-      <c r="CX6" t="s">
+      <c r="DC6" t="s">
         <v>58</v>
-      </c>
-      <c r="CY6" t="s">
-        <v>59</v>
-      </c>
-      <c r="CZ6" t="s">
-        <v>59</v>
-      </c>
-      <c r="DA6" t="s">
-        <v>59</v>
-      </c>
-      <c r="DB6" t="s">
-        <v>59</v>
-      </c>
-      <c r="DC6" t="s">
-        <v>59</v>
       </c>
       <c r="DD6" t="s">
         <v>59</v>
@@ -5677,34 +5781,34 @@
         <v>59</v>
       </c>
       <c r="DF6" t="s">
+        <v>59</v>
+      </c>
+      <c r="DG6" t="s">
+        <v>59</v>
+      </c>
+      <c r="DH6" t="s">
+        <v>59</v>
+      </c>
+      <c r="DI6" t="s">
+        <v>59</v>
+      </c>
+      <c r="DJ6" t="s">
+        <v>59</v>
+      </c>
+      <c r="DK6" t="s">
         <v>60</v>
       </c>
-      <c r="DG6" t="s">
+      <c r="DL6" t="s">
         <v>61</v>
       </c>
-      <c r="DH6" t="s">
+      <c r="DM6" t="s">
         <v>61</v>
       </c>
-      <c r="DI6" t="s">
+      <c r="DN6" t="s">
         <v>62</v>
       </c>
-      <c r="DJ6" t="s">
+      <c r="DO6" t="s">
         <v>62</v>
-      </c>
-      <c r="DK6" t="s">
-        <v>59</v>
-      </c>
-      <c r="DL6" t="s">
-        <v>59</v>
-      </c>
-      <c r="DM6" t="s">
-        <v>59</v>
-      </c>
-      <c r="DN6" t="s">
-        <v>63</v>
-      </c>
-      <c r="DO6" t="s">
-        <v>64</v>
       </c>
       <c r="DP6" t="s">
         <v>59</v>
@@ -5716,947 +5820,992 @@
         <v>59</v>
       </c>
       <c r="DS6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="DT6" t="s">
+        <v>64</v>
+      </c>
+      <c r="DU6" t="s">
         <v>59</v>
-      </c>
-      <c r="DU6" t="s">
-        <v>66</v>
       </c>
       <c r="DV6" t="s">
         <v>59</v>
       </c>
+      <c r="DW6" t="s">
+        <v>59</v>
+      </c>
       <c r="DX6" t="s">
+        <v>65</v>
+      </c>
+      <c r="DY6" t="s">
         <v>59</v>
-      </c>
-      <c r="DY6" t="s">
-        <v>67</v>
       </c>
       <c r="DZ6" t="s">
         <v>66</v>
       </c>
+      <c r="EA6" t="s">
+        <v>59</v>
+      </c>
       <c r="EC6" t="s">
+        <v>59</v>
+      </c>
+      <c r="ED6" t="s">
+        <v>67</v>
+      </c>
+      <c r="EE6" t="s">
+        <v>66</v>
+      </c>
+      <c r="EH6" t="s">
         <v>68</v>
       </c>
-      <c r="ED6" t="s">
+      <c r="EI6" t="s">
         <v>69</v>
       </c>
-      <c r="EO6" s="2"/>
-      <c r="EP6" s="2"/>
-      <c r="EQ6" s="2"/>
-      <c r="ER6" s="2"/>
-      <c r="ES6" s="2"/>
       <c r="ET6" s="2"/>
       <c r="EU6" s="2"/>
-    </row>
-    <row r="7" spans="1:151" x14ac:dyDescent="0.25">
+      <c r="EV6" s="2"/>
+      <c r="EW6" s="2"/>
+      <c r="EX6" s="2"/>
+      <c r="EY6" s="2"/>
+      <c r="EZ6" s="2"/>
+    </row>
+    <row r="7" spans="1:156" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>70</v>
       </c>
       <c r="B7" s="39"/>
       <c r="C7" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1091</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1087</v>
+      </c>
+      <c r="H7" t="s">
         <v>1083</v>
       </c>
-      <c r="D7" t="s">
+      <c r="I7" t="s">
         <v>1079</v>
       </c>
-      <c r="E7" t="s">
+      <c r="J7" t="s">
         <v>1076</v>
       </c>
-      <c r="F7" t="s">
+      <c r="K7" t="s">
         <v>1073</v>
       </c>
-      <c r="G7" t="s">
+      <c r="L7" t="s">
         <v>1071</v>
       </c>
-      <c r="H7" t="s">
+      <c r="M7" t="s">
         <v>1065</v>
       </c>
-      <c r="I7" t="s">
+      <c r="N7" t="s">
         <v>1059</v>
       </c>
-      <c r="J7" t="s">
+      <c r="O7" t="s">
         <v>1056</v>
       </c>
-      <c r="K7" t="s">
+      <c r="P7" t="s">
         <v>1053</v>
       </c>
-      <c r="L7" t="s">
+      <c r="Q7" t="s">
         <v>1050</v>
       </c>
-      <c r="M7" t="s">
+      <c r="R7" t="s">
         <v>1047</v>
       </c>
-      <c r="N7" t="s">
+      <c r="S7" t="s">
         <v>1045</v>
       </c>
-      <c r="O7" t="s">
+      <c r="T7" t="s">
         <v>1040</v>
       </c>
-      <c r="P7" t="s">
+      <c r="U7" t="s">
         <v>1036</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="V7" t="s">
         <v>1035</v>
       </c>
-      <c r="R7" t="s">
+      <c r="W7" t="s">
         <v>1029</v>
       </c>
-      <c r="S7" t="s">
+      <c r="X7" t="s">
         <v>1025</v>
       </c>
-      <c r="T7" t="s">
+      <c r="Y7" t="s">
         <v>1021</v>
       </c>
-      <c r="U7" t="s">
+      <c r="Z7" t="s">
         <v>1017</v>
       </c>
-      <c r="V7" t="s">
+      <c r="AA7" t="s">
         <v>1012</v>
       </c>
-      <c r="W7" t="s">
+      <c r="AB7" t="s">
         <v>1009</v>
       </c>
-      <c r="X7" t="s">
+      <c r="AC7" t="s">
         <v>1005</v>
       </c>
-      <c r="Y7" t="s">
+      <c r="AD7" t="s">
         <v>1003</v>
       </c>
-      <c r="Z7" t="s">
+      <c r="AE7" t="s">
         <v>998</v>
       </c>
-      <c r="AA7" t="s">
+      <c r="AF7" t="s">
         <v>995</v>
       </c>
-      <c r="AB7" t="s">
+      <c r="AG7" t="s">
         <v>993</v>
       </c>
-      <c r="AC7" t="s">
+      <c r="AH7" t="s">
         <v>990</v>
       </c>
-      <c r="AD7" t="s">
+      <c r="AI7" t="s">
         <v>985</v>
       </c>
-      <c r="AE7" t="s">
+      <c r="AJ7" t="s">
         <v>984</v>
       </c>
-      <c r="AF7" t="s">
+      <c r="AK7" t="s">
         <v>981</v>
       </c>
-      <c r="AG7" t="s">
+      <c r="AL7" t="s">
         <v>978</v>
       </c>
-      <c r="AH7" t="s">
+      <c r="AM7" t="s">
         <v>972</v>
       </c>
-      <c r="AI7" t="s">
+      <c r="AN7" t="s">
         <v>969</v>
       </c>
-      <c r="AJ7" t="s">
+      <c r="AO7" t="s">
         <v>968</v>
       </c>
-      <c r="AK7" t="s">
+      <c r="AP7" t="s">
         <v>965</v>
       </c>
-      <c r="AL7" t="s">
+      <c r="AQ7" t="s">
         <v>958</v>
       </c>
-      <c r="AM7" t="s">
+      <c r="AR7" t="s">
         <v>957</v>
       </c>
-      <c r="AN7" t="s">
+      <c r="AS7" t="s">
         <v>953</v>
       </c>
-      <c r="AO7" t="s">
+      <c r="AT7" t="s">
         <v>950</v>
       </c>
-      <c r="AP7" t="s">
+      <c r="AU7" t="s">
         <v>948</v>
       </c>
-      <c r="AQ7" t="s">
+      <c r="AV7" t="s">
         <v>947</v>
       </c>
-      <c r="AR7" t="s">
+      <c r="AW7" t="s">
         <v>941</v>
       </c>
-      <c r="AS7" t="s">
+      <c r="AX7" t="s">
         <v>938</v>
       </c>
-      <c r="AT7" t="s">
+      <c r="AY7" t="s">
         <v>934</v>
       </c>
-      <c r="AU7" t="s">
+      <c r="AZ7" t="s">
         <v>931</v>
       </c>
-      <c r="AV7" t="s">
+      <c r="BA7" t="s">
         <v>927</v>
       </c>
-      <c r="AW7" t="s">
+      <c r="BB7" t="s">
         <v>923</v>
       </c>
-      <c r="AX7" t="s">
+      <c r="BC7" t="s">
         <v>922</v>
       </c>
-      <c r="AY7" t="s">
+      <c r="BD7" t="s">
         <v>917</v>
       </c>
-      <c r="AZ7" t="s">
+      <c r="BE7" t="s">
         <v>913</v>
       </c>
-      <c r="BA7" t="s">
+      <c r="BF7" t="s">
         <v>910</v>
       </c>
-      <c r="BB7" t="s">
+      <c r="BG7" t="s">
         <v>907</v>
       </c>
-      <c r="BC7" t="s">
+      <c r="BH7" t="s">
         <v>903</v>
       </c>
-      <c r="BD7" t="s">
+      <c r="BI7" t="s">
         <v>900</v>
       </c>
-      <c r="BE7" t="s">
+      <c r="BJ7" t="s">
         <v>897</v>
       </c>
-      <c r="BF7" t="s">
+      <c r="BK7" t="s">
         <v>891</v>
       </c>
-      <c r="BG7" t="s">
+      <c r="BL7" t="s">
         <v>879</v>
       </c>
-      <c r="BH7" t="s">
+      <c r="BM7" t="s">
         <v>874</v>
       </c>
-      <c r="BI7" t="s">
+      <c r="BN7" t="s">
         <v>871</v>
       </c>
-      <c r="BJ7" t="s">
+      <c r="BO7" t="s">
         <v>851</v>
       </c>
-      <c r="BK7" t="s">
+      <c r="BP7" t="s">
         <v>847</v>
       </c>
-      <c r="BL7" t="s">
+      <c r="BQ7" t="s">
         <v>839</v>
       </c>
-      <c r="BM7" t="s">
+      <c r="BR7" t="s">
         <v>836</v>
       </c>
-      <c r="BN7" t="s">
+      <c r="BS7" t="s">
         <v>832</v>
       </c>
-      <c r="BO7" t="s">
+      <c r="BT7" t="s">
         <v>830</v>
       </c>
-      <c r="BP7" t="s">
+      <c r="BU7" t="s">
         <v>825</v>
       </c>
-      <c r="BQ7" t="s">
+      <c r="BV7" t="s">
         <v>823</v>
       </c>
-      <c r="BR7" t="s">
+      <c r="BW7" t="s">
         <v>821</v>
       </c>
-      <c r="BS7" t="s">
+      <c r="BX7" t="s">
         <v>819</v>
       </c>
-      <c r="BT7" t="s">
+      <c r="BY7" t="s">
         <v>816</v>
       </c>
-      <c r="BU7" t="s">
+      <c r="BZ7" t="s">
         <v>813</v>
       </c>
-      <c r="BV7" t="s">
+      <c r="CA7" t="s">
         <v>810</v>
       </c>
-      <c r="BW7" t="s">
+      <c r="CB7" t="s">
         <v>806</v>
       </c>
-      <c r="BX7" t="s">
+      <c r="CC7" t="s">
         <v>805</v>
       </c>
-      <c r="BY7" t="s">
+      <c r="CD7" t="s">
         <v>800</v>
       </c>
-      <c r="BZ7" t="s">
+      <c r="CE7" t="s">
         <v>797</v>
       </c>
-      <c r="CA7" t="s">
+      <c r="CF7" t="s">
         <v>794</v>
       </c>
-      <c r="CB7" t="s">
+      <c r="CG7" t="s">
         <v>791</v>
       </c>
-      <c r="CC7" t="s">
+      <c r="CH7" t="s">
         <v>787</v>
       </c>
-      <c r="CD7" t="s">
+      <c r="CI7" t="s">
         <v>785</v>
       </c>
-      <c r="CE7" t="s">
+      <c r="CJ7" t="s">
         <v>782</v>
       </c>
-      <c r="CF7" t="s">
+      <c r="CK7" t="s">
         <v>778</v>
       </c>
-      <c r="CG7" t="s">
+      <c r="CL7" t="s">
         <v>774</v>
       </c>
-      <c r="CH7" t="s">
+      <c r="CM7" t="s">
         <v>773</v>
       </c>
-      <c r="CI7" t="s">
+      <c r="CN7" t="s">
         <v>768</v>
       </c>
-      <c r="CJ7" t="s">
+      <c r="CO7" t="s">
         <v>767</v>
       </c>
-      <c r="CK7" t="s">
+      <c r="CP7" t="s">
         <v>763</v>
       </c>
-      <c r="CL7" t="s">
+      <c r="CQ7" t="s">
         <v>753</v>
       </c>
-      <c r="CM7" t="s">
+      <c r="CR7" t="s">
         <v>748</v>
       </c>
-      <c r="CN7" t="s">
+      <c r="CS7" t="s">
         <v>745</v>
       </c>
-      <c r="CO7" t="s">
+      <c r="CT7" t="s">
         <v>735</v>
       </c>
-      <c r="CP7" t="s">
+      <c r="CU7" t="s">
         <v>732</v>
       </c>
-      <c r="CQ7" t="s">
+      <c r="CV7" t="s">
         <v>724</v>
       </c>
-      <c r="CR7" t="s">
+      <c r="CW7" t="s">
         <v>656</v>
       </c>
-      <c r="CS7" t="s">
+      <c r="CX7" t="s">
         <v>649</v>
       </c>
-      <c r="CT7" t="s">
+      <c r="CY7" t="s">
         <v>645</v>
       </c>
-      <c r="CU7" t="s">
+      <c r="CZ7" t="s">
         <v>651</v>
       </c>
-      <c r="CV7" t="s">
+      <c r="DA7" t="s">
         <v>71</v>
       </c>
-      <c r="CW7" t="s">
+      <c r="DB7" t="s">
         <v>72</v>
       </c>
-      <c r="CX7" t="s">
+      <c r="DC7" t="s">
         <v>73</v>
       </c>
-      <c r="CY7" t="s">
+      <c r="DD7" t="s">
         <v>759</v>
       </c>
-      <c r="CZ7" t="s">
+      <c r="DE7" t="s">
         <v>74</v>
       </c>
-      <c r="DA7" t="s">
+      <c r="DF7" t="s">
         <v>75</v>
       </c>
-      <c r="DB7" t="s">
+      <c r="DG7" t="s">
         <v>76</v>
       </c>
-      <c r="DC7" t="s">
+      <c r="DH7" t="s">
         <v>77</v>
       </c>
-      <c r="DD7" t="s">
+      <c r="DI7" t="s">
         <v>78</v>
       </c>
-      <c r="DE7" t="s">
+      <c r="DJ7" t="s">
         <v>79</v>
       </c>
-      <c r="DF7" t="s">
+      <c r="DK7" t="s">
         <v>80</v>
       </c>
-      <c r="DG7" t="s">
+      <c r="DL7" t="s">
         <v>81</v>
       </c>
-      <c r="DH7" t="s">
+      <c r="DM7" t="s">
         <v>82</v>
       </c>
-      <c r="DI7" t="s">
+      <c r="DN7" t="s">
         <v>83</v>
       </c>
-      <c r="DJ7" t="s">
+      <c r="DO7" t="s">
         <v>84</v>
       </c>
-      <c r="DK7" t="s">
+      <c r="DP7" t="s">
         <v>85</v>
       </c>
-      <c r="DL7" t="s">
+      <c r="DQ7" t="s">
         <v>86</v>
       </c>
-      <c r="DM7" t="s">
+      <c r="DR7" t="s">
         <v>87</v>
       </c>
-      <c r="DN7" t="s">
+      <c r="DS7" t="s">
         <v>88</v>
       </c>
-      <c r="DO7" t="s">
+      <c r="DT7" t="s">
         <v>89</v>
       </c>
-      <c r="DP7" t="s">
+      <c r="DU7" t="s">
         <v>740</v>
       </c>
-      <c r="DQ7" t="s">
+      <c r="DV7" t="s">
         <v>90</v>
       </c>
-      <c r="DR7" t="s">
+      <c r="DW7" t="s">
         <v>91</v>
       </c>
-      <c r="DS7" t="s">
+      <c r="DX7" t="s">
         <v>92</v>
       </c>
-      <c r="DT7" t="s">
+      <c r="DY7" t="s">
         <v>93</v>
       </c>
-      <c r="DU7" t="s">
+      <c r="DZ7" t="s">
         <v>94</v>
       </c>
-      <c r="DV7" t="s">
+      <c r="EA7" t="s">
         <v>95</v>
       </c>
-      <c r="DW7" t="s">
+      <c r="EB7" t="s">
         <v>96</v>
       </c>
-      <c r="DX7" t="s">
+      <c r="EC7" t="s">
         <v>97</v>
       </c>
-      <c r="DY7" t="s">
+      <c r="ED7" t="s">
         <v>98</v>
       </c>
-      <c r="DZ7" t="s">
+      <c r="EE7" t="s">
         <v>99</v>
       </c>
-      <c r="EA7" t="s">
+      <c r="EF7" t="s">
         <v>100</v>
       </c>
-      <c r="EB7" t="s">
+      <c r="EG7" t="s">
         <v>101</v>
       </c>
-      <c r="EC7" t="s">
+      <c r="EH7" t="s">
         <v>102</v>
       </c>
-      <c r="ED7" t="s">
+      <c r="EI7" t="s">
         <v>103</v>
       </c>
-      <c r="EE7" t="s">
+      <c r="EJ7" t="s">
         <v>104</v>
       </c>
-      <c r="EF7" t="s">
+      <c r="EK7" t="s">
         <v>104</v>
       </c>
-      <c r="EG7" t="s">
+      <c r="EL7" t="s">
         <v>105</v>
       </c>
-      <c r="EH7" t="s">
+      <c r="EM7" t="s">
         <v>106</v>
       </c>
-      <c r="EI7" t="s">
+      <c r="EN7" t="s">
         <v>107</v>
       </c>
-      <c r="EJ7" t="s">
+      <c r="EO7" t="s">
         <v>108</v>
       </c>
-      <c r="EK7" t="s">
+      <c r="EP7" t="s">
         <v>109</v>
       </c>
-      <c r="EL7" t="s">
+      <c r="EQ7" t="s">
         <v>110</v>
       </c>
-      <c r="EM7" t="s">
+      <c r="ER7" t="s">
         <v>111</v>
       </c>
-      <c r="EN7" t="s">
+      <c r="ES7" t="s">
         <v>112</v>
       </c>
-      <c r="EO7" t="s">
+      <c r="ET7" t="s">
         <v>113</v>
       </c>
-      <c r="EP7" t="s">
+      <c r="EU7" t="s">
         <v>114</v>
       </c>
-      <c r="EQ7" t="s">
+      <c r="EV7" t="s">
         <v>115</v>
       </c>
-      <c r="ER7" t="s">
+      <c r="EW7" t="s">
         <v>116</v>
       </c>
-      <c r="ES7" t="s">
+      <c r="EX7" t="s">
         <v>117</v>
       </c>
-      <c r="ET7" t="s">
+      <c r="EY7" t="s">
         <v>118</v>
       </c>
-      <c r="EU7" t="s">
+      <c r="EZ7" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="8" spans="1:151" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:156" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>120</v>
       </c>
       <c r="B8" s="39"/>
       <c r="C8" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1095</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1092</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1089</v>
+      </c>
+      <c r="H8" t="s">
         <v>1084</v>
       </c>
-      <c r="D8" t="s">
+      <c r="I8" t="s">
         <v>1080</v>
       </c>
-      <c r="E8" t="s">
+      <c r="J8" t="s">
         <v>1077</v>
       </c>
-      <c r="F8" t="s">
+      <c r="K8" t="s">
         <v>1074</v>
       </c>
-      <c r="G8" t="s">
+      <c r="L8" t="s">
         <v>1069</v>
       </c>
-      <c r="H8" t="s">
+      <c r="M8" t="s">
         <v>1066</v>
       </c>
-      <c r="I8" t="s">
+      <c r="N8" t="s">
         <v>1061</v>
       </c>
-      <c r="J8" t="s">
+      <c r="O8" t="s">
         <v>1057</v>
       </c>
-      <c r="K8" t="s">
+      <c r="P8" t="s">
         <v>1055</v>
       </c>
-      <c r="L8" t="s">
+      <c r="Q8" t="s">
         <v>1051</v>
       </c>
-      <c r="M8" t="s">
+      <c r="R8" t="s">
         <v>1048</v>
       </c>
-      <c r="N8" t="s">
+      <c r="S8" t="s">
         <v>1044</v>
       </c>
-      <c r="O8" t="s">
+      <c r="T8" t="s">
         <v>1041</v>
       </c>
-      <c r="P8" t="s">
+      <c r="U8" t="s">
         <v>1037</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="V8" t="s">
         <v>1033</v>
       </c>
-      <c r="R8" t="s">
+      <c r="W8" t="s">
         <v>1031</v>
       </c>
-      <c r="S8" t="s">
+      <c r="X8" t="s">
         <v>1026</v>
       </c>
-      <c r="T8" t="s">
+      <c r="Y8" t="s">
         <v>1023</v>
       </c>
-      <c r="U8" t="s">
+      <c r="Z8" t="s">
         <v>1019</v>
       </c>
-      <c r="V8" t="s">
+      <c r="AA8" t="s">
         <v>1015</v>
       </c>
-      <c r="W8" t="s">
+      <c r="AB8" t="s">
         <v>1010</v>
       </c>
-      <c r="X8" t="s">
+      <c r="AC8" t="s">
         <v>1006</v>
       </c>
-      <c r="Y8" t="s">
+      <c r="AD8" t="s">
         <v>1001</v>
       </c>
-      <c r="Z8" t="s">
+      <c r="AE8" t="s">
         <v>997</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="AF8" t="s">
         <v>996</v>
       </c>
-      <c r="AB8" t="s">
+      <c r="AG8" t="s">
         <v>991</v>
       </c>
-      <c r="AC8" t="s">
+      <c r="AH8" t="s">
         <v>988</v>
       </c>
-      <c r="AD8" t="s">
+      <c r="AI8" t="s">
         <v>986</v>
       </c>
-      <c r="AE8" t="s">
+      <c r="AJ8" t="s">
         <v>982</v>
       </c>
-      <c r="AF8" t="s">
+      <c r="AK8" t="s">
         <v>980</v>
       </c>
-      <c r="AG8" t="s">
+      <c r="AL8" t="s">
         <v>977</v>
       </c>
-      <c r="AH8" t="s">
+      <c r="AM8" t="s">
         <v>974</v>
       </c>
-      <c r="AI8" t="s">
+      <c r="AN8" t="s">
         <v>970</v>
       </c>
-      <c r="AJ8" t="s">
+      <c r="AO8" t="s">
         <v>966</v>
       </c>
-      <c r="AK8" t="s">
+      <c r="AP8" t="s">
         <v>963</v>
       </c>
-      <c r="AL8" t="s">
+      <c r="AQ8" t="s">
         <v>961</v>
       </c>
-      <c r="AM8" t="s">
+      <c r="AR8" t="s">
         <v>956</v>
       </c>
-      <c r="AN8" t="s">
+      <c r="AS8" t="s">
         <v>954</v>
       </c>
-      <c r="AO8" t="s">
+      <c r="AT8" t="s">
         <v>951</v>
       </c>
-      <c r="AP8" t="s">
+      <c r="AU8" t="s">
         <v>949</v>
       </c>
-      <c r="AQ8" t="s">
+      <c r="AV8" t="s">
         <v>946</v>
       </c>
-      <c r="AR8" t="s">
+      <c r="AW8" t="s">
         <v>942</v>
       </c>
-      <c r="AS8" t="s">
+      <c r="AX8" t="s">
         <v>940</v>
       </c>
-      <c r="AT8" t="s">
+      <c r="AY8" t="s">
         <v>935</v>
       </c>
-      <c r="AU8" t="s">
+      <c r="AZ8" t="s">
         <v>932</v>
       </c>
-      <c r="AV8" t="s">
+      <c r="BA8" t="s">
         <v>930</v>
       </c>
-      <c r="AW8" t="s">
+      <c r="BB8" t="s">
         <v>925</v>
       </c>
-      <c r="AX8" t="s">
+      <c r="BC8" t="s">
         <v>921</v>
       </c>
-      <c r="AY8" t="s">
+      <c r="BD8" t="s">
         <v>919</v>
       </c>
-      <c r="AZ8" t="s">
+      <c r="BE8" t="s">
         <v>914</v>
       </c>
-      <c r="BA8" t="s">
+      <c r="BF8" t="s">
         <v>912</v>
       </c>
-      <c r="BB8" t="s">
+      <c r="BG8" t="s">
         <v>909</v>
       </c>
-      <c r="BC8" t="s">
+      <c r="BH8" t="s">
         <v>905</v>
       </c>
-      <c r="BD8" t="s">
+      <c r="BI8" t="s">
         <v>902</v>
       </c>
-      <c r="BE8" t="s">
+      <c r="BJ8" t="s">
         <v>896</v>
       </c>
-      <c r="BF8" t="s">
+      <c r="BK8" t="s">
         <v>892</v>
       </c>
-      <c r="BG8" t="s">
+      <c r="BL8" t="s">
         <v>878</v>
       </c>
-      <c r="BH8" t="s">
+      <c r="BM8" t="s">
         <v>875</v>
       </c>
-      <c r="BI8" t="s">
+      <c r="BN8" t="s">
         <v>873</v>
       </c>
-      <c r="BJ8" t="s">
+      <c r="BO8" t="s">
         <v>852</v>
       </c>
-      <c r="BK8" t="s">
+      <c r="BP8" t="s">
         <v>849</v>
       </c>
-      <c r="BL8" t="s">
+      <c r="BQ8" t="s">
         <v>840</v>
       </c>
-      <c r="BM8" t="s">
+      <c r="BR8" t="s">
         <v>837</v>
       </c>
-      <c r="BN8" t="s">
+      <c r="BS8" t="s">
         <v>833</v>
       </c>
-      <c r="BO8" t="s">
+      <c r="BT8" t="s">
         <v>831</v>
       </c>
-      <c r="BP8" t="s">
+      <c r="BU8" t="s">
         <v>826</v>
       </c>
-      <c r="BQ8" t="s">
+      <c r="BV8" t="s">
         <v>824</v>
       </c>
-      <c r="BR8" t="s">
+      <c r="BW8" t="s">
         <v>822</v>
       </c>
-      <c r="BS8" t="s">
+      <c r="BX8" t="s">
         <v>820</v>
       </c>
-      <c r="BT8" t="s">
+      <c r="BY8" t="s">
         <v>815</v>
       </c>
-      <c r="BU8" t="s">
+      <c r="BZ8" t="s">
         <v>812</v>
       </c>
-      <c r="BV8" t="s">
+      <c r="CA8" t="s">
         <v>809</v>
       </c>
-      <c r="BW8" t="s">
+      <c r="CB8" t="s">
         <v>807</v>
       </c>
-      <c r="BX8" t="s">
+      <c r="CC8" t="s">
         <v>804</v>
       </c>
-      <c r="BY8" t="s">
+      <c r="CD8" t="s">
         <v>801</v>
       </c>
-      <c r="BZ8" t="s">
+      <c r="CE8" t="s">
         <v>796</v>
       </c>
-      <c r="CA8" t="s">
+      <c r="CF8" t="s">
         <v>793</v>
       </c>
-      <c r="CB8" t="s">
+      <c r="CG8" t="s">
         <v>790</v>
       </c>
-      <c r="CC8" t="s">
+      <c r="CH8" t="s">
         <v>788</v>
       </c>
-      <c r="CD8" t="s">
+      <c r="CI8" t="s">
         <v>784</v>
       </c>
-      <c r="CE8" t="s">
+      <c r="CJ8" t="s">
         <v>780</v>
       </c>
-      <c r="CF8" t="s">
+      <c r="CK8" t="s">
         <v>779</v>
       </c>
-      <c r="CG8" t="s">
+      <c r="CL8" t="s">
         <v>776</v>
       </c>
-      <c r="CH8" t="s">
+      <c r="CM8" t="s">
         <v>772</v>
       </c>
-      <c r="CI8" t="s">
+      <c r="CN8" t="s">
         <v>770</v>
       </c>
-      <c r="CJ8" t="s">
+      <c r="CO8" t="s">
         <v>766</v>
       </c>
-      <c r="CK8" t="s">
+      <c r="CP8" t="s">
         <v>764</v>
       </c>
-      <c r="CL8" t="s">
+      <c r="CQ8" t="s">
         <v>754</v>
       </c>
-      <c r="CM8" t="s">
+      <c r="CR8" t="s">
         <v>749</v>
       </c>
-      <c r="CN8" t="s">
+      <c r="CS8" t="s">
         <v>121</v>
       </c>
-      <c r="CO8" t="s">
+      <c r="CT8" t="s">
         <v>734</v>
       </c>
-      <c r="CP8" t="s">
+      <c r="CU8" t="s">
         <v>730</v>
       </c>
-      <c r="CQ8" t="s">
+      <c r="CV8" t="s">
         <v>725</v>
       </c>
-      <c r="CR8" t="s">
+      <c r="CW8" t="s">
         <v>657</v>
       </c>
-      <c r="CS8" t="s">
+      <c r="CX8" t="s">
         <v>650</v>
       </c>
-      <c r="CT8" t="s">
+      <c r="CY8" t="s">
         <v>121</v>
       </c>
-      <c r="CU8" t="s">
+      <c r="CZ8" t="s">
         <v>652</v>
       </c>
-      <c r="CV8" t="s">
+      <c r="DA8" t="s">
         <v>122</v>
       </c>
-      <c r="CW8" t="s">
+      <c r="DB8" t="s">
         <v>123</v>
       </c>
-      <c r="CX8" t="s">
+      <c r="DC8" t="s">
         <v>124</v>
       </c>
-      <c r="CY8" t="s">
+      <c r="DD8" t="s">
         <v>760</v>
       </c>
-      <c r="CZ8" t="s">
+      <c r="DE8" t="s">
         <v>126</v>
       </c>
-      <c r="DA8" t="s">
+      <c r="DF8" t="s">
         <v>127</v>
       </c>
-      <c r="DB8" t="s">
+      <c r="DG8" t="s">
         <v>128</v>
       </c>
-      <c r="DC8" t="s">
+      <c r="DH8" t="s">
         <v>125</v>
       </c>
-      <c r="DD8" t="s">
+      <c r="DI8" t="s">
         <v>129</v>
       </c>
-      <c r="DE8" t="s">
+      <c r="DJ8" t="s">
         <v>130</v>
       </c>
-      <c r="DF8" t="s">
+      <c r="DK8" t="s">
         <v>131</v>
       </c>
-      <c r="DG8" t="s">
+      <c r="DL8" t="s">
         <v>132</v>
       </c>
-      <c r="DH8" t="s">
+      <c r="DM8" t="s">
         <v>133</v>
       </c>
-      <c r="DI8" t="s">
+      <c r="DN8" t="s">
         <v>134</v>
       </c>
-      <c r="DJ8" t="s">
+      <c r="DO8" t="s">
         <v>135</v>
       </c>
-      <c r="DK8" t="s">
+      <c r="DP8" t="s">
         <v>136</v>
       </c>
-      <c r="DL8" t="s">
+      <c r="DQ8" t="s">
         <v>137</v>
       </c>
-      <c r="DM8" t="s">
+      <c r="DR8" t="s">
         <v>138</v>
       </c>
-      <c r="DN8" t="s">
+      <c r="DS8" t="s">
         <v>139</v>
       </c>
-      <c r="DO8" t="s">
+      <c r="DT8" t="s">
         <v>140</v>
       </c>
-      <c r="DP8" t="s">
+      <c r="DU8" t="s">
         <v>739</v>
       </c>
-      <c r="DQ8" t="s">
+      <c r="DV8" t="s">
         <v>141</v>
       </c>
-      <c r="DR8" t="s">
+      <c r="DW8" t="s">
         <v>142</v>
       </c>
-      <c r="DS8" t="s">
+      <c r="DX8" t="s">
         <v>143</v>
       </c>
-      <c r="DT8" t="s">
+      <c r="DY8" t="s">
         <v>144</v>
       </c>
-      <c r="DU8" t="s">
+      <c r="DZ8" t="s">
         <v>145</v>
       </c>
-      <c r="DV8" t="s">
+      <c r="EA8" t="s">
         <v>146</v>
       </c>
-      <c r="DW8" t="s">
+      <c r="EB8" t="s">
         <v>147</v>
       </c>
-      <c r="DX8" t="s">
+      <c r="EC8" t="s">
         <v>148</v>
       </c>
-      <c r="DY8" t="s">
+      <c r="ED8" t="s">
         <v>149</v>
       </c>
-      <c r="DZ8" t="s">
+      <c r="EE8" t="s">
         <v>150</v>
       </c>
-      <c r="EA8" t="s">
+      <c r="EF8" t="s">
         <v>151</v>
       </c>
-      <c r="EB8" t="s">
+      <c r="EG8" t="s">
         <v>152</v>
       </c>
-      <c r="EC8" t="s">
+      <c r="EH8" t="s">
         <v>153</v>
       </c>
-      <c r="ED8" t="s">
+      <c r="EI8" t="s">
         <v>154</v>
       </c>
-      <c r="EE8" t="s">
+      <c r="EJ8" t="s">
         <v>155</v>
       </c>
-      <c r="EF8" t="s">
+      <c r="EK8" t="s">
         <v>156</v>
       </c>
-      <c r="EG8" t="s">
+      <c r="EL8" t="s">
         <v>157</v>
       </c>
-      <c r="EH8" t="s">
+      <c r="EM8" t="s">
         <v>158</v>
       </c>
-      <c r="EI8" t="s">
+      <c r="EN8" t="s">
         <v>159</v>
       </c>
-      <c r="EJ8" t="s">
+      <c r="EO8" t="s">
         <v>160</v>
       </c>
-      <c r="EK8" t="s">
+      <c r="EP8" t="s">
         <v>161</v>
       </c>
-      <c r="EL8" t="s">
+      <c r="EQ8" t="s">
         <v>162</v>
       </c>
-      <c r="EM8" t="s">
+      <c r="ER8" t="s">
         <v>163</v>
       </c>
-      <c r="EN8" t="s">
+      <c r="ES8" t="s">
         <v>164</v>
       </c>
-      <c r="EO8" t="s">
+      <c r="ET8" t="s">
         <v>165</v>
       </c>
-      <c r="EP8" t="s">
+      <c r="EU8" t="s">
         <v>166</v>
       </c>
-      <c r="EQ8" t="s">
+      <c r="EV8" t="s">
         <v>167</v>
       </c>
-      <c r="ER8" t="s">
+      <c r="EW8" t="s">
         <v>168</v>
       </c>
-      <c r="ES8" t="s">
+      <c r="EX8" t="s">
         <v>169</v>
       </c>
-      <c r="ET8" t="s">
+      <c r="EY8" t="s">
         <v>170</v>
       </c>
-      <c r="EU8" t="s">
+      <c r="EZ8" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="9" spans="1:151" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:156" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>172</v>
       </c>
@@ -6665,92 +6814,97 @@
       <c r="D9"/>
       <c r="E9"/>
       <c r="F9"/>
-      <c r="G9" t="s">
+      <c r="G9"/>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9"/>
+      <c r="L9" t="s">
         <v>1070</v>
       </c>
-      <c r="BP9" t="s">
+      <c r="BU9" t="s">
         <v>828</v>
       </c>
-      <c r="CU9" t="s">
+      <c r="CZ9" t="s">
         <v>653</v>
       </c>
-      <c r="CV9" t="s">
+      <c r="DA9" t="s">
         <v>173</v>
       </c>
-      <c r="CY9" t="s">
+      <c r="DD9" t="s">
         <v>761</v>
       </c>
-      <c r="CZ9" t="s">
+      <c r="DE9" t="s">
         <v>175</v>
       </c>
-      <c r="DA9" t="s">
+      <c r="DF9" t="s">
         <v>176</v>
       </c>
-      <c r="DB9" t="s">
+      <c r="DG9" t="s">
         <v>177</v>
       </c>
-      <c r="DC9" t="s">
+      <c r="DH9" t="s">
         <v>174</v>
       </c>
-      <c r="DD9" t="s">
+      <c r="DI9" t="s">
         <v>178</v>
       </c>
-      <c r="DE9" t="s">
+      <c r="DJ9" t="s">
         <v>178</v>
       </c>
-      <c r="DG9" t="s">
+      <c r="DL9" t="s">
         <v>179</v>
       </c>
-      <c r="DH9" t="s">
+      <c r="DM9" t="s">
         <v>180</v>
       </c>
-      <c r="DJ9" t="s">
+      <c r="DO9" t="s">
         <v>181</v>
       </c>
-      <c r="DL9" t="s">
+      <c r="DQ9" t="s">
         <v>182</v>
       </c>
-      <c r="DM9" t="s">
+      <c r="DR9" t="s">
         <v>183</v>
       </c>
-      <c r="DP9" t="s">
+      <c r="DU9" t="s">
         <v>741</v>
       </c>
-      <c r="DR9" t="s">
+      <c r="DW9" t="s">
         <v>184</v>
       </c>
-      <c r="DT9" t="s">
+      <c r="DY9" t="s">
         <v>185</v>
       </c>
-      <c r="DX9" t="s">
+      <c r="EC9" t="s">
         <v>186</v>
       </c>
-      <c r="EE9" t="s">
+      <c r="EJ9" t="s">
         <v>187</v>
       </c>
-      <c r="EF9" t="s">
+      <c r="EK9" t="s">
         <v>187</v>
       </c>
-      <c r="EH9" t="s">
+      <c r="EM9" t="s">
         <v>188</v>
       </c>
-      <c r="EK9" t="s">
+      <c r="EP9" t="s">
         <v>189</v>
       </c>
-      <c r="EM9" t="s">
+      <c r="ER9" t="s">
         <v>190</v>
       </c>
-      <c r="EN9" t="s">
+      <c r="ES9" t="s">
         <v>191</v>
       </c>
-      <c r="EQ9" t="s">
+      <c r="EV9" t="s">
         <v>192</v>
       </c>
-      <c r="ET9" t="s">
+      <c r="EY9" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="10" spans="1:151" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:156" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>194</v>
       </c>
@@ -6759,23 +6913,28 @@
       <c r="D10"/>
       <c r="E10"/>
       <c r="F10"/>
-      <c r="DK10" t="s">
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10"/>
+      <c r="DP10" t="s">
         <v>195</v>
       </c>
-      <c r="DN10" t="s">
+      <c r="DS10" t="s">
         <v>196</v>
       </c>
-      <c r="DT10" t="s">
+      <c r="DY10" t="s">
         <v>197</v>
       </c>
-      <c r="EE10" t="s">
+      <c r="EJ10" t="s">
         <v>198</v>
       </c>
-      <c r="EF10" t="s">
+      <c r="EK10" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="11" spans="1:151" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:156" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>199</v>
       </c>
@@ -6784,182 +6943,202 @@
       <c r="D11"/>
       <c r="E11"/>
       <c r="F11"/>
-      <c r="DP11" t="s">
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11"/>
+      <c r="DU11" t="s">
         <v>742</v>
       </c>
-      <c r="DR11" t="s">
+      <c r="DW11" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="12" spans="1:151" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:156" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>858</v>
       </c>
       <c r="B12" s="39"/>
       <c r="C12" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1096</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1088</v>
+      </c>
+      <c r="H12" t="s">
         <v>1085</v>
       </c>
-      <c r="D12" t="s">
+      <c r="I12" t="s">
         <v>1081</v>
       </c>
-      <c r="E12" t="s">
+      <c r="J12" t="s">
         <v>1078</v>
       </c>
-      <c r="F12" t="s">
+      <c r="K12" t="s">
         <v>1075</v>
       </c>
-      <c r="H12" t="s">
+      <c r="M12" t="s">
         <v>1067</v>
       </c>
-      <c r="I12" t="s">
+      <c r="N12" t="s">
         <v>1062</v>
       </c>
-      <c r="K12" t="s">
+      <c r="P12" t="s">
         <v>1054</v>
       </c>
-      <c r="L12" t="s">
+      <c r="Q12" t="s">
         <v>1052</v>
       </c>
-      <c r="M12" t="s">
+      <c r="R12" t="s">
         <v>1049</v>
       </c>
-      <c r="N12" t="s">
+      <c r="S12" t="s">
         <v>1046</v>
       </c>
-      <c r="O12" t="s">
+      <c r="T12" t="s">
         <v>1042</v>
       </c>
-      <c r="P12" t="s">
+      <c r="U12" t="s">
         <v>1038</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="V12" t="s">
         <v>1034</v>
       </c>
-      <c r="R12" t="s">
+      <c r="W12" t="s">
         <v>1030</v>
       </c>
-      <c r="S12" t="s">
+      <c r="X12" t="s">
         <v>1027</v>
       </c>
-      <c r="T12" t="s">
+      <c r="Y12" t="s">
         <v>1022</v>
       </c>
-      <c r="U12" t="s">
+      <c r="Z12" t="s">
         <v>1018</v>
       </c>
-      <c r="V12" t="s">
+      <c r="AA12" t="s">
         <v>1014</v>
       </c>
-      <c r="W12" t="s">
+      <c r="AB12" t="s">
         <v>1011</v>
       </c>
-      <c r="X12" t="s">
+      <c r="AC12" t="s">
         <v>1007</v>
       </c>
-      <c r="Y12" t="s">
+      <c r="AD12" t="s">
         <v>1002</v>
       </c>
-      <c r="Z12" t="s">
+      <c r="AE12" t="s">
         <v>999</v>
       </c>
-      <c r="AB12" t="s">
+      <c r="AG12" t="s">
         <v>992</v>
       </c>
-      <c r="AC12" t="s">
+      <c r="AH12" t="s">
         <v>989</v>
       </c>
-      <c r="AD12" t="s">
+      <c r="AI12" t="s">
         <v>987</v>
       </c>
-      <c r="AE12" t="s">
+      <c r="AJ12" t="s">
         <v>983</v>
       </c>
-      <c r="AG12" t="s">
+      <c r="AL12" t="s">
         <v>976</v>
       </c>
-      <c r="AH12" t="s">
+      <c r="AM12" t="s">
         <v>973</v>
       </c>
-      <c r="AI12" t="s">
+      <c r="AN12" t="s">
         <v>971</v>
       </c>
-      <c r="AJ12" t="s">
+      <c r="AO12" t="s">
         <v>967</v>
       </c>
-      <c r="AK12" t="s">
+      <c r="AP12" t="s">
         <v>964</v>
       </c>
-      <c r="AL12" t="s">
+      <c r="AQ12" t="s">
         <v>959</v>
       </c>
-      <c r="AM12" t="s">
+      <c r="AR12" t="s">
         <v>955</v>
       </c>
-      <c r="AN12" t="s">
+      <c r="AS12" t="s">
         <v>895</v>
       </c>
-      <c r="AO12" t="s">
+      <c r="AT12" t="s">
         <v>952</v>
       </c>
-      <c r="AQ12" t="s">
+      <c r="AV12" t="s">
         <v>944</v>
       </c>
-      <c r="AR12" t="s">
+      <c r="AW12" t="s">
         <v>943</v>
       </c>
-      <c r="AS12" t="s">
+      <c r="AX12" t="s">
         <v>939</v>
       </c>
-      <c r="AT12" t="s">
+      <c r="AY12" t="s">
         <v>936</v>
       </c>
-      <c r="AU12" t="s">
+      <c r="AZ12" t="s">
         <v>933</v>
       </c>
-      <c r="AV12" t="s">
+      <c r="BA12" t="s">
         <v>929</v>
       </c>
-      <c r="AW12" t="s">
+      <c r="BB12" t="s">
         <v>924</v>
       </c>
-      <c r="AY12" t="s">
+      <c r="BD12" t="s">
         <v>918</v>
       </c>
-      <c r="AZ12" t="s">
+      <c r="BE12" t="s">
         <v>915</v>
       </c>
-      <c r="BA12" t="s">
+      <c r="BF12" t="s">
         <v>911</v>
       </c>
-      <c r="BB12" t="s">
+      <c r="BG12" t="s">
         <v>908</v>
       </c>
-      <c r="BC12" t="s">
+      <c r="BH12" t="s">
         <v>904</v>
       </c>
-      <c r="BD12" t="s">
+      <c r="BI12" t="s">
         <v>901</v>
       </c>
-      <c r="BE12" t="s">
+      <c r="BJ12" t="s">
         <v>895</v>
       </c>
-      <c r="BF12" t="s">
+      <c r="BK12" t="s">
         <v>893</v>
       </c>
-      <c r="BG12" t="s">
+      <c r="BL12" t="s">
         <v>877</v>
       </c>
-      <c r="BI12" t="s">
+      <c r="BN12" t="s">
         <v>872</v>
       </c>
-      <c r="BJ12" t="s">
+      <c r="BO12" t="s">
         <v>868</v>
       </c>
-      <c r="BM12" t="s">
+      <c r="BR12" t="s">
         <v>898</v>
       </c>
     </row>
-    <row r="13" spans="1:151" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:156" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>201</v>
       </c>
@@ -6968,41 +7147,46 @@
       <c r="D13"/>
       <c r="E13"/>
       <c r="F13"/>
-      <c r="I13" t="s">
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+      <c r="K13"/>
+      <c r="N13" t="s">
         <v>1063</v>
       </c>
-      <c r="N13" t="s">
+      <c r="S13" t="s">
         <v>1043</v>
       </c>
-      <c r="AG13" t="s">
+      <c r="AL13" t="s">
         <v>975</v>
       </c>
-      <c r="AV13" t="s">
+      <c r="BA13" t="s">
         <v>928</v>
       </c>
-      <c r="BK13" t="s">
+      <c r="BP13" t="s">
         <v>848</v>
       </c>
-      <c r="BP13" t="s">
+      <c r="BU13" t="s">
         <v>827</v>
       </c>
-      <c r="BT13" t="s">
+      <c r="BY13" t="s">
         <v>817</v>
       </c>
-      <c r="BY13" t="s">
+      <c r="CD13" t="s">
         <v>802</v>
       </c>
-      <c r="BZ13" t="s">
+      <c r="CE13" t="s">
         <v>798</v>
       </c>
-      <c r="DG13" t="s">
+      <c r="DL13" t="s">
         <v>202</v>
       </c>
-      <c r="DH13" t="s">
+      <c r="DM13" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="14" spans="1:151" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:156" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>204</v>
       </c>
@@ -7011,8 +7195,13 @@
       <c r="D14"/>
       <c r="E14"/>
       <c r="F14"/>
-    </row>
-    <row r="15" spans="1:151" x14ac:dyDescent="0.25">
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+      <c r="K14"/>
+    </row>
+    <row r="15" spans="1:156" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>751</v>
       </c>
@@ -7021,8 +7210,13 @@
       <c r="D15"/>
       <c r="E15"/>
       <c r="F15"/>
-    </row>
-    <row r="16" spans="1:151" x14ac:dyDescent="0.25">
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15"/>
+    </row>
+    <row r="16" spans="1:156" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>752</v>
       </c>
@@ -7031,8 +7225,13 @@
       <c r="D16"/>
       <c r="E16"/>
       <c r="F16"/>
-    </row>
-    <row r="17" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16"/>
+    </row>
+    <row r="17" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>205</v>
       </c>
@@ -7041,8 +7240,13 @@
       <c r="D17"/>
       <c r="E17"/>
       <c r="F17"/>
-    </row>
-    <row r="18" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17"/>
+      <c r="K17"/>
+    </row>
+    <row r="18" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>206</v>
       </c>
@@ -7051,8 +7255,13 @@
       <c r="D18"/>
       <c r="E18"/>
       <c r="F18"/>
-    </row>
-    <row r="19" spans="1:90" x14ac:dyDescent="0.25">
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
+      <c r="J18"/>
+      <c r="K18"/>
+    </row>
+    <row r="19" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>758</v>
       </c>
@@ -7166,19 +7375,19 @@
         <v>960</v>
       </c>
       <c r="AM19" t="s">
-        <v>757</v>
+        <v>960</v>
       </c>
       <c r="AN19" t="s">
-        <v>757</v>
+        <v>960</v>
       </c>
       <c r="AO19" t="s">
-        <v>757</v>
+        <v>960</v>
       </c>
       <c r="AP19" t="s">
-        <v>757</v>
+        <v>960</v>
       </c>
       <c r="AQ19" t="s">
-        <v>757</v>
+        <v>960</v>
       </c>
       <c r="AR19" t="s">
         <v>757</v>
@@ -7235,7 +7444,7 @@
         <v>757</v>
       </c>
       <c r="BJ19" t="s">
-        <v>960</v>
+        <v>757</v>
       </c>
       <c r="BK19" t="s">
         <v>757</v>
@@ -7250,7 +7459,7 @@
         <v>757</v>
       </c>
       <c r="BO19" t="s">
-        <v>757</v>
+        <v>960</v>
       </c>
       <c r="BP19" t="s">
         <v>757</v>
@@ -7291,142 +7500,162 @@
       <c r="CB19" t="s">
         <v>757</v>
       </c>
+      <c r="CC19" t="s">
+        <v>757</v>
+      </c>
+      <c r="CD19" t="s">
+        <v>757</v>
+      </c>
+      <c r="CE19" t="s">
+        <v>757</v>
+      </c>
       <c r="CF19" t="s">
         <v>757</v>
       </c>
       <c r="CG19" t="s">
         <v>757</v>
       </c>
-      <c r="CH19" t="s">
-        <v>757</v>
-      </c>
-      <c r="CI19" t="s">
-        <v>757</v>
-      </c>
-      <c r="CJ19" t="s">
-        <v>757</v>
-      </c>
       <c r="CK19" t="s">
         <v>757</v>
       </c>
       <c r="CL19" t="s">
+        <v>757</v>
+      </c>
+      <c r="CM19" t="s">
+        <v>757</v>
+      </c>
+      <c r="CN19" t="s">
+        <v>757</v>
+      </c>
+      <c r="CO19" t="s">
+        <v>757</v>
+      </c>
+      <c r="CP19" t="s">
+        <v>757</v>
+      </c>
+      <c r="CQ19" t="s">
         <v>757</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="CT1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
-    <hyperlink ref="CU1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
-    <hyperlink ref="CV1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
-    <hyperlink ref="CW1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
-    <hyperlink ref="CX1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
-    <hyperlink ref="CY1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
-    <hyperlink ref="CZ1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
-    <hyperlink ref="DA1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
-    <hyperlink ref="DB1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
-    <hyperlink ref="DC1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
-    <hyperlink ref="DD1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
-    <hyperlink ref="DE1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
-    <hyperlink ref="DF1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
-    <hyperlink ref="DG1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00000F000000}"/>
-    <hyperlink ref="DH1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
-    <hyperlink ref="DI1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
-    <hyperlink ref="DJ1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000012000000}"/>
-    <hyperlink ref="DK1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
-    <hyperlink ref="DL1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
-    <hyperlink ref="DM1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000015000000}"/>
-    <hyperlink ref="DN1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000016000000}"/>
-    <hyperlink ref="DO1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000017000000}"/>
-    <hyperlink ref="DP1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000018000000}"/>
-    <hyperlink ref="DQ1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000019000000}"/>
-    <hyperlink ref="DR1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00001A000000}"/>
-    <hyperlink ref="DS1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00001B000000}"/>
-    <hyperlink ref="DT1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00001C000000}"/>
-    <hyperlink ref="DU1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00001D000000}"/>
-    <hyperlink ref="DV1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00001E000000}"/>
-    <hyperlink ref="DW1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00001F000000}"/>
-    <hyperlink ref="DX1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000020000000}"/>
-    <hyperlink ref="DY1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000021000000}"/>
-    <hyperlink ref="DZ1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000022000000}"/>
-    <hyperlink ref="EA1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000023000000}"/>
-    <hyperlink ref="EB1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000024000000}"/>
-    <hyperlink ref="EC1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000025000000}"/>
-    <hyperlink ref="ED1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000026000000}"/>
-    <hyperlink ref="EE1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000027000000}"/>
-    <hyperlink ref="EF1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000028000000}"/>
-    <hyperlink ref="EG1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000029000000}"/>
-    <hyperlink ref="EH1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00002A000000}"/>
-    <hyperlink ref="EI1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00002B000000}"/>
-    <hyperlink ref="EJ1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00002C000000}"/>
-    <hyperlink ref="EK1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00002D000000}"/>
-    <hyperlink ref="EL1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00002E000000}"/>
-    <hyperlink ref="EM1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00002F000000}"/>
-    <hyperlink ref="EN1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000030000000}"/>
-    <hyperlink ref="EO1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000031000000}"/>
-    <hyperlink ref="EP1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000032000000}"/>
-    <hyperlink ref="EQ1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000033000000}"/>
-    <hyperlink ref="ER1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000034000000}"/>
-    <hyperlink ref="ES1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000035000000}"/>
-    <hyperlink ref="ET1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000036000000}"/>
-    <hyperlink ref="EU1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000037000000}"/>
-    <hyperlink ref="CN1" location="contents!A1" display="Contents" xr:uid="{9D9CCE4A-5CD2-437E-9617-0F93011D53A3}"/>
-    <hyperlink ref="BJ1" location="contents!A1" display="Contents" xr:uid="{3FAD3FE0-AB40-48BA-AEC1-65546650B1CF}"/>
-    <hyperlink ref="BI1" location="contents!A1" display="Contents" xr:uid="{32791349-53A4-427C-89DA-522B44F1739E}"/>
-    <hyperlink ref="BH1" location="contents!A1" display="Contents" xr:uid="{697DBC3F-41A4-491A-9D08-AC96AB820264}"/>
-    <hyperlink ref="BG1" location="contents!A1" display="Contents" xr:uid="{0C6BB241-3937-42F9-A5BE-E1EACB4925BE}"/>
-    <hyperlink ref="BF1" location="contents!A1" display="Contents" xr:uid="{492D207D-CB9D-414A-8B16-8CA6B3AFB43E}"/>
-    <hyperlink ref="BE1" location="contents!A1" display="Contents" xr:uid="{8E27650F-3982-417B-BDD0-B28B6C362E3E}"/>
-    <hyperlink ref="BD1" location="contents!A1" display="Contents" xr:uid="{D75E7FCB-82AB-484B-97D3-66D5DC991F6C}"/>
-    <hyperlink ref="BC1" location="contents!A1" display="Contents" xr:uid="{BBBF3901-8142-49D3-95EA-19294D1C14EC}"/>
-    <hyperlink ref="BB1" location="contents!A1" display="Contents" xr:uid="{EC5DAE0F-8EBD-4CAA-AD9B-E50DC37655E4}"/>
-    <hyperlink ref="BA1" location="contents!A1" display="Contents" xr:uid="{38D1CC1C-0B91-4B62-AB18-77F6E128C0BB}"/>
-    <hyperlink ref="AZ1" location="contents!A1" display="Contents" xr:uid="{C32720F2-8DA3-4812-A554-165E255F238D}"/>
-    <hyperlink ref="AY1" location="contents!A1" display="Contents" xr:uid="{98E99DE4-5804-46E0-9E8B-774DCAFE93D0}"/>
-    <hyperlink ref="AX1" location="contents!A1" display="Contents" xr:uid="{C236F8FA-A1C3-479D-A295-DACDD3CDEDAD}"/>
-    <hyperlink ref="AW1" location="contents!A1" display="Contents" xr:uid="{D34314D4-D308-4397-91C7-B41BE359A27C}"/>
-    <hyperlink ref="AV1" location="contents!A1" display="Contents" xr:uid="{C93881C9-C93F-4607-A253-B00C084D10C4}"/>
-    <hyperlink ref="AU1" location="contents!A1" display="Contents" xr:uid="{A5F8BA6E-44DA-40C6-8D04-FB61815C4842}"/>
-    <hyperlink ref="AT1" location="contents!A1" display="Contents" xr:uid="{C711AA9A-F171-41FA-9793-81C0EA8638A8}"/>
-    <hyperlink ref="AS1" location="contents!A1" display="Contents" xr:uid="{29E4E036-A3A8-4A16-8E35-DF8155227347}"/>
-    <hyperlink ref="AR1" location="contents!A1" display="Contents" xr:uid="{DA6BFB54-CBD0-4DE0-AF6B-84E4C1B0D4C4}"/>
-    <hyperlink ref="AQ1" location="contents!A1" display="Contents" xr:uid="{8551A20B-581D-45C7-AD86-C130DBA4647F}"/>
-    <hyperlink ref="AP1" location="contents!A1" display="Contents" xr:uid="{698696C1-6BB2-41E8-8784-DDF8EEB80E8C}"/>
-    <hyperlink ref="AN1" location="contents!A1" display="Contents" xr:uid="{56870F7A-0500-4FAF-8398-B13E7F27905A}"/>
-    <hyperlink ref="AM1" location="contents!A1" display="Contents" xr:uid="{BDE7C4E1-7C22-4CFB-96E2-4537880BFC18}"/>
-    <hyperlink ref="AK1" location="contents!A1" display="Contents" xr:uid="{31B5305D-A644-46B4-B82A-4DE742C5A6DD}"/>
-    <hyperlink ref="AJ1" location="contents!A1" display="Contents" xr:uid="{E0129CCB-DDF6-4A3F-A1D2-91374B79CBD3}"/>
-    <hyperlink ref="AI1" location="contents!A1" display="Contents" xr:uid="{9EC926A8-52ED-4061-95AE-771DFE06BEB6}"/>
-    <hyperlink ref="AH1" location="contents!A1" display="Contents" xr:uid="{EB3805F5-FA8B-4511-B9C1-3CB5483E72F6}"/>
-    <hyperlink ref="AG1" location="contents!A1" display="Contents" xr:uid="{7844FC75-64DB-408A-B395-C73FB0D65864}"/>
-    <hyperlink ref="AF1" location="contents!A1" display="Contents" xr:uid="{D1E4A0CD-933A-4AA9-B8C6-A0D8BE111BE3}"/>
-    <hyperlink ref="AE1" location="contents!A1" display="Contents" xr:uid="{DDA73B89-9899-4392-982F-032F7CCC149D}"/>
-    <hyperlink ref="AD1" location="contents!A1" display="Contents" xr:uid="{A9E6137E-279A-4001-906A-C0AA8E7B33AE}"/>
-    <hyperlink ref="AC1" location="contents!A1" display="Contents" xr:uid="{1873EE4F-BE3C-45BA-A7A3-C8F78214A04A}"/>
-    <hyperlink ref="Z1" location="contents!A1" display="Contents" xr:uid="{908C3AEE-C418-4D1A-AD93-2FE3201711D9}"/>
-    <hyperlink ref="Y1" location="contents!A1" display="Contents" xr:uid="{1F8D91A6-14BA-4F5F-A006-601D90206D75}"/>
-    <hyperlink ref="X1" location="contents!A1" display="Contents" xr:uid="{66A7E497-1597-48BF-9ADE-E9CB32023975}"/>
-    <hyperlink ref="W1" location="contents!A1" display="Contents" xr:uid="{8AA7281B-B47A-41B6-9A4B-545337CDA33F}"/>
-    <hyperlink ref="V1" location="contents!A1" display="Contents" xr:uid="{144FDDA1-8D03-4237-8744-ADEF4FF4B900}"/>
-    <hyperlink ref="U1" location="contents!A1" display="Contents" xr:uid="{8DBEE1F7-DCF6-40EA-BC46-1A2F8C077234}"/>
-    <hyperlink ref="T1" location="contents!A1" display="Contents" xr:uid="{53B126D4-7C43-4EBE-BD0C-294C81D133C0}"/>
-    <hyperlink ref="S1" location="contents!A1" display="Contents" xr:uid="{C8B834F2-F90A-485A-819B-3AEB16B4FF49}"/>
-    <hyperlink ref="R1" location="contents!A1" display="Contents" xr:uid="{49FE4B51-07B5-4C50-A999-EE501393B22D}"/>
-    <hyperlink ref="Q1" location="contents!A1" display="Contents" xr:uid="{8FC8ACD2-5EC5-4C34-9A88-B214B5DFC201}"/>
-    <hyperlink ref="P1" location="contents!A1" display="Contents" xr:uid="{BC06316D-019D-494B-B494-20C1629E5614}"/>
-    <hyperlink ref="O1" location="contents!A1" display="Contents" xr:uid="{DEC54F1B-5A35-4242-AB85-D985BB988F9D}"/>
-    <hyperlink ref="N1" location="contents!A1" display="Contents" xr:uid="{D0D03B8A-CB9D-4898-9139-62041F31D6CA}"/>
-    <hyperlink ref="M1" location="contents!A1" display="Contents" xr:uid="{02AFCB5A-4613-4FD2-953D-792104DE4399}"/>
-    <hyperlink ref="L1" location="contents!A1" display="Contents" xr:uid="{F25254D6-D5AC-4A45-AE45-87AB44B1E07A}"/>
-    <hyperlink ref="K1" location="contents!A1" display="Contents" xr:uid="{CD337BA3-E268-4A23-B64A-07199600E796}"/>
-    <hyperlink ref="J1" location="contents!A1" display="Contents" xr:uid="{1A5108E0-AA64-4EBA-9F0D-301EB4FD4E89}"/>
-    <hyperlink ref="I1" location="contents!A1" display="Contents" xr:uid="{42F20267-FF1D-4B3A-A328-0855E66195DB}"/>
-    <hyperlink ref="H1" location="contents!A1" display="Contents" xr:uid="{12E50AB9-5C28-4140-BF75-D7E1067463CA}"/>
-    <hyperlink ref="G1" location="contents!A1" display="Contents" xr:uid="{A3B6F765-B55A-4498-B5A3-C95085FAB9D6}"/>
-    <hyperlink ref="F1" location="contents!A1" display="Contents" xr:uid="{7278A37B-C720-4573-9694-666084FF9300}"/>
-    <hyperlink ref="E1" location="contents!A1" display="Contents" xr:uid="{56D3D477-F6BC-42BE-A397-860B5B9B140B}"/>
-    <hyperlink ref="D1" location="contents!A1" display="Contents" xr:uid="{7C88203E-D4E7-4A89-B535-55F2A9D9DAE9}"/>
-    <hyperlink ref="C1" location="contents!A1" display="Contents" xr:uid="{F982AE8C-A71C-4A96-862F-E907CE672AB9}"/>
+    <hyperlink ref="CY1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="CZ1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="DA1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="DB1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="DC1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
+    <hyperlink ref="DD1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
+    <hyperlink ref="DE1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
+    <hyperlink ref="DF1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
+    <hyperlink ref="DG1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
+    <hyperlink ref="DH1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
+    <hyperlink ref="DI1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
+    <hyperlink ref="DJ1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
+    <hyperlink ref="DK1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
+    <hyperlink ref="DL1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00000F000000}"/>
+    <hyperlink ref="DM1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
+    <hyperlink ref="DN1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
+    <hyperlink ref="DO1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000012000000}"/>
+    <hyperlink ref="DP1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
+    <hyperlink ref="DQ1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
+    <hyperlink ref="DR1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000015000000}"/>
+    <hyperlink ref="DS1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000016000000}"/>
+    <hyperlink ref="DT1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000017000000}"/>
+    <hyperlink ref="DU1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000018000000}"/>
+    <hyperlink ref="DV1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000019000000}"/>
+    <hyperlink ref="DW1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00001A000000}"/>
+    <hyperlink ref="DX1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00001B000000}"/>
+    <hyperlink ref="DY1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00001C000000}"/>
+    <hyperlink ref="DZ1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00001D000000}"/>
+    <hyperlink ref="EA1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00001E000000}"/>
+    <hyperlink ref="EB1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00001F000000}"/>
+    <hyperlink ref="EC1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000020000000}"/>
+    <hyperlink ref="ED1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000021000000}"/>
+    <hyperlink ref="EE1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000022000000}"/>
+    <hyperlink ref="EF1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000023000000}"/>
+    <hyperlink ref="EG1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000024000000}"/>
+    <hyperlink ref="EH1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000025000000}"/>
+    <hyperlink ref="EI1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000026000000}"/>
+    <hyperlink ref="EJ1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000027000000}"/>
+    <hyperlink ref="EK1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000028000000}"/>
+    <hyperlink ref="EL1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000029000000}"/>
+    <hyperlink ref="EM1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00002A000000}"/>
+    <hyperlink ref="EN1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00002B000000}"/>
+    <hyperlink ref="EO1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00002C000000}"/>
+    <hyperlink ref="EP1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00002D000000}"/>
+    <hyperlink ref="EQ1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00002E000000}"/>
+    <hyperlink ref="ER1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-00002F000000}"/>
+    <hyperlink ref="ES1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000030000000}"/>
+    <hyperlink ref="ET1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000031000000}"/>
+    <hyperlink ref="EU1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000032000000}"/>
+    <hyperlink ref="EV1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000033000000}"/>
+    <hyperlink ref="EW1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000034000000}"/>
+    <hyperlink ref="EX1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000035000000}"/>
+    <hyperlink ref="EY1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000036000000}"/>
+    <hyperlink ref="EZ1" location="contents!A1" display="Contents" xr:uid="{00000000-0004-0000-0100-000037000000}"/>
+    <hyperlink ref="CS1" location="contents!A1" display="Contents" xr:uid="{9D9CCE4A-5CD2-437E-9617-0F93011D53A3}"/>
+    <hyperlink ref="BO1" location="contents!A1" display="Contents" xr:uid="{3FAD3FE0-AB40-48BA-AEC1-65546650B1CF}"/>
+    <hyperlink ref="BN1" location="contents!A1" display="Contents" xr:uid="{32791349-53A4-427C-89DA-522B44F1739E}"/>
+    <hyperlink ref="BM1" location="contents!A1" display="Contents" xr:uid="{697DBC3F-41A4-491A-9D08-AC96AB820264}"/>
+    <hyperlink ref="BL1" location="contents!A1" display="Contents" xr:uid="{0C6BB241-3937-42F9-A5BE-E1EACB4925BE}"/>
+    <hyperlink ref="BK1" location="contents!A1" display="Contents" xr:uid="{492D207D-CB9D-414A-8B16-8CA6B3AFB43E}"/>
+    <hyperlink ref="BJ1" location="contents!A1" display="Contents" xr:uid="{8E27650F-3982-417B-BDD0-B28B6C362E3E}"/>
+    <hyperlink ref="BI1" location="contents!A1" display="Contents" xr:uid="{D75E7FCB-82AB-484B-97D3-66D5DC991F6C}"/>
+    <hyperlink ref="BH1" location="contents!A1" display="Contents" xr:uid="{BBBF3901-8142-49D3-95EA-19294D1C14EC}"/>
+    <hyperlink ref="BG1" location="contents!A1" display="Contents" xr:uid="{EC5DAE0F-8EBD-4CAA-AD9B-E50DC37655E4}"/>
+    <hyperlink ref="BF1" location="contents!A1" display="Contents" xr:uid="{38D1CC1C-0B91-4B62-AB18-77F6E128C0BB}"/>
+    <hyperlink ref="BE1" location="contents!A1" display="Contents" xr:uid="{C32720F2-8DA3-4812-A554-165E255F238D}"/>
+    <hyperlink ref="BD1" location="contents!A1" display="Contents" xr:uid="{98E99DE4-5804-46E0-9E8B-774DCAFE93D0}"/>
+    <hyperlink ref="BC1" location="contents!A1" display="Contents" xr:uid="{C236F8FA-A1C3-479D-A295-DACDD3CDEDAD}"/>
+    <hyperlink ref="BB1" location="contents!A1" display="Contents" xr:uid="{D34314D4-D308-4397-91C7-B41BE359A27C}"/>
+    <hyperlink ref="BA1" location="contents!A1" display="Contents" xr:uid="{C93881C9-C93F-4607-A253-B00C084D10C4}"/>
+    <hyperlink ref="AZ1" location="contents!A1" display="Contents" xr:uid="{A5F8BA6E-44DA-40C6-8D04-FB61815C4842}"/>
+    <hyperlink ref="AY1" location="contents!A1" display="Contents" xr:uid="{C711AA9A-F171-41FA-9793-81C0EA8638A8}"/>
+    <hyperlink ref="AX1" location="contents!A1" display="Contents" xr:uid="{29E4E036-A3A8-4A16-8E35-DF8155227347}"/>
+    <hyperlink ref="AW1" location="contents!A1" display="Contents" xr:uid="{DA6BFB54-CBD0-4DE0-AF6B-84E4C1B0D4C4}"/>
+    <hyperlink ref="AV1" location="contents!A1" display="Contents" xr:uid="{8551A20B-581D-45C7-AD86-C130DBA4647F}"/>
+    <hyperlink ref="AU1" location="contents!A1" display="Contents" xr:uid="{698696C1-6BB2-41E8-8784-DDF8EEB80E8C}"/>
+    <hyperlink ref="AS1" location="contents!A1" display="Contents" xr:uid="{56870F7A-0500-4FAF-8398-B13E7F27905A}"/>
+    <hyperlink ref="AR1" location="contents!A1" display="Contents" xr:uid="{BDE7C4E1-7C22-4CFB-96E2-4537880BFC18}"/>
+    <hyperlink ref="AP1" location="contents!A1" display="Contents" xr:uid="{31B5305D-A644-46B4-B82A-4DE742C5A6DD}"/>
+    <hyperlink ref="AO1" location="contents!A1" display="Contents" xr:uid="{E0129CCB-DDF6-4A3F-A1D2-91374B79CBD3}"/>
+    <hyperlink ref="AN1" location="contents!A1" display="Contents" xr:uid="{9EC926A8-52ED-4061-95AE-771DFE06BEB6}"/>
+    <hyperlink ref="AM1" location="contents!A1" display="Contents" xr:uid="{EB3805F5-FA8B-4511-B9C1-3CB5483E72F6}"/>
+    <hyperlink ref="AL1" location="contents!A1" display="Contents" xr:uid="{7844FC75-64DB-408A-B395-C73FB0D65864}"/>
+    <hyperlink ref="AK1" location="contents!A1" display="Contents" xr:uid="{D1E4A0CD-933A-4AA9-B8C6-A0D8BE111BE3}"/>
+    <hyperlink ref="AJ1" location="contents!A1" display="Contents" xr:uid="{DDA73B89-9899-4392-982F-032F7CCC149D}"/>
+    <hyperlink ref="AI1" location="contents!A1" display="Contents" xr:uid="{A9E6137E-279A-4001-906A-C0AA8E7B33AE}"/>
+    <hyperlink ref="AH1" location="contents!A1" display="Contents" xr:uid="{1873EE4F-BE3C-45BA-A7A3-C8F78214A04A}"/>
+    <hyperlink ref="AE1" location="contents!A1" display="Contents" xr:uid="{908C3AEE-C418-4D1A-AD93-2FE3201711D9}"/>
+    <hyperlink ref="AD1" location="contents!A1" display="Contents" xr:uid="{1F8D91A6-14BA-4F5F-A006-601D90206D75}"/>
+    <hyperlink ref="AC1" location="contents!A1" display="Contents" xr:uid="{66A7E497-1597-48BF-9ADE-E9CB32023975}"/>
+    <hyperlink ref="AB1" location="contents!A1" display="Contents" xr:uid="{8AA7281B-B47A-41B6-9A4B-545337CDA33F}"/>
+    <hyperlink ref="AA1" location="contents!A1" display="Contents" xr:uid="{144FDDA1-8D03-4237-8744-ADEF4FF4B900}"/>
+    <hyperlink ref="Z1" location="contents!A1" display="Contents" xr:uid="{8DBEE1F7-DCF6-40EA-BC46-1A2F8C077234}"/>
+    <hyperlink ref="Y1" location="contents!A1" display="Contents" xr:uid="{53B126D4-7C43-4EBE-BD0C-294C81D133C0}"/>
+    <hyperlink ref="X1" location="contents!A1" display="Contents" xr:uid="{C8B834F2-F90A-485A-819B-3AEB16B4FF49}"/>
+    <hyperlink ref="W1" location="contents!A1" display="Contents" xr:uid="{49FE4B51-07B5-4C50-A999-EE501393B22D}"/>
+    <hyperlink ref="V1" location="contents!A1" display="Contents" xr:uid="{8FC8ACD2-5EC5-4C34-9A88-B214B5DFC201}"/>
+    <hyperlink ref="U1" location="contents!A1" display="Contents" xr:uid="{BC06316D-019D-494B-B494-20C1629E5614}"/>
+    <hyperlink ref="T1" location="contents!A1" display="Contents" xr:uid="{DEC54F1B-5A35-4242-AB85-D985BB988F9D}"/>
+    <hyperlink ref="S1" location="contents!A1" display="Contents" xr:uid="{D0D03B8A-CB9D-4898-9139-62041F31D6CA}"/>
+    <hyperlink ref="R1" location="contents!A1" display="Contents" xr:uid="{02AFCB5A-4613-4FD2-953D-792104DE4399}"/>
+    <hyperlink ref="Q1" location="contents!A1" display="Contents" xr:uid="{F25254D6-D5AC-4A45-AE45-87AB44B1E07A}"/>
+    <hyperlink ref="P1" location="contents!A1" display="Contents" xr:uid="{CD337BA3-E268-4A23-B64A-07199600E796}"/>
+    <hyperlink ref="O1" location="contents!A1" display="Contents" xr:uid="{1A5108E0-AA64-4EBA-9F0D-301EB4FD4E89}"/>
+    <hyperlink ref="N1" location="contents!A1" display="Contents" xr:uid="{42F20267-FF1D-4B3A-A328-0855E66195DB}"/>
+    <hyperlink ref="M1" location="contents!A1" display="Contents" xr:uid="{12E50AB9-5C28-4140-BF75-D7E1067463CA}"/>
+    <hyperlink ref="L1" location="contents!A1" display="Contents" xr:uid="{A3B6F765-B55A-4498-B5A3-C95085FAB9D6}"/>
+    <hyperlink ref="K1" location="contents!A1" display="Contents" xr:uid="{7278A37B-C720-4573-9694-666084FF9300}"/>
+    <hyperlink ref="J1" location="contents!A1" display="Contents" xr:uid="{56D3D477-F6BC-42BE-A397-860B5B9B140B}"/>
+    <hyperlink ref="I1" location="contents!A1" display="Contents" xr:uid="{7C88203E-D4E7-4A89-B535-55F2A9D9DAE9}"/>
+    <hyperlink ref="H1" location="contents!A1" display="Contents" xr:uid="{F982AE8C-A71C-4A96-862F-E907CE672AB9}"/>
+    <hyperlink ref="G1" location="contents!A1" display="Contents" xr:uid="{AC9D2412-B8B7-453C-9F7A-984ABF953609}"/>
+    <hyperlink ref="F1" location="contents!A1" display="Contents" xr:uid="{B586AB8F-DB90-4340-977E-9C4F0ADE5FDA}"/>
+    <hyperlink ref="E1" location="contents!A1" display="Contents" xr:uid="{1ECE4D3B-A461-4861-8A43-80D857B2B193}"/>
+    <hyperlink ref="D1" location="contents!A1" display="Contents" xr:uid="{3F57916A-A0C4-4D2C-90B6-2BBCF2618A3A}"/>
+    <hyperlink ref="C1" location="contents!A1" display="Contents" xr:uid="{3A54CD37-79F5-49E1-B4BC-54A2300FC2CC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
